--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -63,22 +63,34 @@
     <x:t>BY</x:t>
   </x:si>
   <x:si>
+    <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDISSA ABASTAS AMANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEW</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brgy 4, City Of Koronadal (Capital), South Cotabato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26-1RTG-X-06965</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1403-812</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cashier edge</x:t>
+  </x:si>
+  <x:si>
     <x:t>Commercial Radio Operator Certificate (RENEWAL)</x:t>
   </x:si>
   <x:si>
-    <x:t>EDISSA ABASTAS AMANTE</x:t>
-  </x:si>
-  <x:si>
     <x:t>REN</x:t>
   </x:si>
   <x:si>
-    <x:t>Brgy 4, City Of Koronadal (Capital), South Cotabato</x:t>
-  </x:si>
-  <x:si>
     <x:t>61-3-2026-1402-290</x:t>
-  </x:si>
-  <x:si>
-    <x:t>cashier edge</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -411,7 +423,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -437,13 +449,10 @@
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -526,12 +535,12 @@
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -943,94 +952,128 @@
       <x:c r="E6" s="11" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="n">
-        <x:v>123456789</x:v>
+      <x:c r="F6" s="11" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H6" s="12">
-        <x:v>46091.059537037</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46050</x:v>
+        <x:v>46091.1148611111</x:v>
+      </x:c>
+      <x:c r="I6" s="12">
+        <x:v>46091.143125</x:v>
       </x:c>
       <x:c r="J6" s="11" t="n">
-        <x:v>165163</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>300</x:v>
+        <x:v>125646</x:v>
+      </x:c>
+      <x:c r="K6" s="13" t="n">
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L6" s="12">
-        <x:v>46091.0629861111</x:v>
+        <x:v>46091.1453125</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="N6" s="7" t="s"/>
       <x:c r="O6" s="9" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="8" t="s"/>
-      <x:c r="C7" s="8" t="s"/>
-      <x:c r="D7" s="8" t="s"/>
-      <x:c r="E7" s="8" t="s"/>
-      <x:c r="F7" s="8" t="s"/>
-      <x:c r="G7" s="8" t="s"/>
-      <x:c r="H7" s="8" t="s"/>
-      <x:c r="I7" s="8" t="s"/>
-      <x:c r="J7" s="8" t="s"/>
-      <x:c r="K7" s="8" t="s"/>
-      <x:c r="L7" s="8" t="s"/>
-      <x:c r="M7" s="8" t="s"/>
+      <x:c r="B7" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="n">
+        <x:v>123456789</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H7" s="12">
+        <x:v>46091.059537037</x:v>
+      </x:c>
+      <x:c r="I7" s="14">
+        <x:v>46050</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="n">
+        <x:v>165163</x:v>
+      </x:c>
+      <x:c r="K7" s="13" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="L7" s="12">
+        <x:v>46091.0629861111</x:v>
+      </x:c>
+      <x:c r="M7" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="N7" s="7" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C9" s="16" t="s"/>
-      <x:c r="D9" s="16" t="s"/>
-      <x:c r="E9" s="17" t="s"/>
-      <x:c r="F9" s="17" t="s"/>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C10" s="16" t="s"/>
+      <x:c r="D10" s="16" t="s"/>
+      <x:c r="E10" s="17" t="s"/>
+      <x:c r="F10" s="17" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B10" s="18" t="s">
+    <x:row r="11" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B11" s="18" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="19" t="s"/>
+      <x:c r="F11" s="20" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B12" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="21" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C10" s="19" t="s"/>
-      <x:c r="D10" s="19" t="s"/>
-      <x:c r="E10" s="19" t="s"/>
-      <x:c r="F10" s="20" t="s">
-        <x:v>21</x:v>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B11" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C11" s="22" t="s"/>
-      <x:c r="D11" s="22" t="s"/>
-      <x:c r="E11" s="22" t="s"/>
-      <x:c r="F11" s="23" t="n">
-        <x:v>1</x:v>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B12" s="24" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C12" s="25" t="s"/>
-      <x:c r="D12" s="25" t="s"/>
-      <x:c r="E12" s="25" t="s"/>
-      <x:c r="F12" s="26" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2011,13 +2054,14 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="6">
+  <x:mergeCells count="7">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B9:F9"/>
-    <x:mergeCell ref="B10:E10"/>
+    <x:mergeCell ref="B10:F10"/>
     <x:mergeCell ref="B11:E11"/>
     <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -9,58 +9,22 @@
     <x:sheet name="March 2026" sheetId="7" r:id="rId7"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="Applicants">Sheet1!$A$6:$M$7</x:definedName>
+    <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
     <x:definedName name="summary">#REF!</x:definedName>
   </x:definedNames>
   <x:calcPr/>
   <x:extLst>
     <x:ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="M1zy22YtJ+TLWEM7ow84Ac98JQFmbAbmONakZm1eVcw="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="6Gqj+nP2ZfjBIlYJvjiPFyqmWD9usEriw94U1uDhyO0="/>
     </x:ext>
   </x:extLst>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <x:si>
-    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Application Type</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COMPANY NAME / NAME</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STATUS(NEW/REN/DUP)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULL ADDRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PERMIT NO.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REFERENCE NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE OF FILING</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXPIRATION DATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OR NUMBER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMOUNT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DATE PAID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BY</x:t>
+    <x:t>{{Name}}</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -139,12 +103,6 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13.0"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
@@ -155,16 +113,30 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:sz val="13.0"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Calibri"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -180,13 +152,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -217,12 +182,12 @@
   <x:borders count="14">
     <x:border/>
     <x:border>
-      <x:left style="thin">
-        <x:color rgb="FF000000"/>
-      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF000000"/>
+      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
@@ -234,14 +199,14 @@
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
-      <x:top style="thin">
-        <x:color rgb="FF000000"/>
-      </x:top>
       <x:bottom style="thin">
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
     <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF000000"/>
+      </x:left>
       <x:right style="thin">
         <x:color rgb="FF000000"/>
       </x:right>
@@ -423,7 +388,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="23">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -434,160 +399,186 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="top" wrapText="0" shrinkToFit="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -851,226 +842,228 @@
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
-      <x:c r="A3" s="2" t="s"/>
-      <x:c r="B3" s="2">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="3">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s"/>
-      <x:c r="D3" s="2" t="s"/>
-      <x:c r="E3" s="2" t="s"/>
-      <x:c r="F3" s="2" t="s"/>
-      <x:c r="G3" s="2" t="s"/>
-      <x:c r="H3" s="2" t="s"/>
-      <x:c r="I3" s="2" t="s"/>
-      <x:c r="J3" s="2" t="s"/>
-      <x:c r="K3" s="2" t="s"/>
-      <x:c r="L3" s="2" t="s"/>
-      <x:c r="M3" s="2" t="s"/>
-      <x:c r="N3" s="2" t="s"/>
+      <x:c r="C3" s="3" t="s"/>
+      <x:c r="D3" s="3" t="s"/>
+      <x:c r="E3" s="3" t="s"/>
+      <x:c r="F3" s="3" t="s"/>
+      <x:c r="G3" s="3" t="s"/>
+      <x:c r="H3" s="3" t="s"/>
+      <x:c r="I3" s="3" t="s"/>
+      <x:c r="J3" s="3" t="s"/>
+      <x:c r="K3" s="3" t="s"/>
+      <x:c r="L3" s="3" t="s"/>
+      <x:c r="M3" s="3" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
     </x:row>
     <x:row r="4" spans="1:28">
-      <x:c r="A4" s="2" t="s"/>
-      <x:c r="B4" s="2" t="s"/>
-      <x:c r="C4" s="2" t="s"/>
-      <x:c r="D4" s="2" t="s"/>
-      <x:c r="E4" s="2" t="s"/>
-      <x:c r="F4" s="2" t="s"/>
-      <x:c r="G4" s="2" t="s"/>
-      <x:c r="H4" s="2" t="s"/>
-      <x:c r="I4" s="2" t="s"/>
-      <x:c r="J4" s="2" t="s"/>
-      <x:c r="K4" s="2" t="s"/>
-      <x:c r="L4" s="2" t="s"/>
-      <x:c r="M4" s="2" t="s"/>
-      <x:c r="N4" s="2" t="s"/>
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="3" t="s"/>
+      <x:c r="C4" s="3" t="s"/>
+      <x:c r="D4" s="3" t="s"/>
+      <x:c r="E4" s="3" t="s"/>
+      <x:c r="F4" s="3" t="s"/>
+      <x:c r="G4" s="3" t="s"/>
+      <x:c r="H4" s="3" t="s"/>
+      <x:c r="I4" s="3" t="s"/>
+      <x:c r="J4" s="3" t="s"/>
+      <x:c r="K4" s="3" t="s"/>
+      <x:c r="L4" s="3" t="s"/>
+      <x:c r="M4" s="3" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A5" s="3" t="s"/>
-      <x:c r="B5" s="10" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="10" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="10" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H5" s="10" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I5" s="10" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J5" s="10" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K5" s="10" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L5" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M5" s="10" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s"/>
-      <x:c r="O5" s="6" t="s"/>
-      <x:c r="P5" s="6" t="s"/>
-      <x:c r="Q5" s="6" t="s"/>
-      <x:c r="R5" s="6" t="s"/>
-      <x:c r="S5" s="6" t="s"/>
-      <x:c r="T5" s="6" t="s"/>
-      <x:c r="U5" s="6" t="s"/>
-      <x:c r="V5" s="6" t="s"/>
-      <x:c r="W5" s="6" t="s"/>
-      <x:c r="X5" s="6" t="s"/>
-      <x:c r="Y5" s="6" t="s"/>
-      <x:c r="Z5" s="6" t="s"/>
-      <x:c r="AA5" s="6" t="s"/>
-      <x:c r="AB5" s="6" t="s"/>
+    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="B5" s="10" t="s"/>
+      <x:c r="C5" s="10" t="s"/>
+      <x:c r="D5" s="10" t="s"/>
+      <x:c r="E5" s="10" t="s"/>
+      <x:c r="F5" s="10" t="s"/>
+      <x:c r="G5" s="10" t="s"/>
+      <x:c r="H5" s="10" t="s"/>
+      <x:c r="I5" s="10" t="s"/>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
+      <x:c r="L5" s="10" t="s"/>
+      <x:c r="M5" s="10" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A6" s="7" t="s"/>
       <x:c r="B6" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>15</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G6" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="12">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H6" s="13">
         <x:v>46091.1148611111</x:v>
       </x:c>
-      <x:c r="I6" s="12">
+      <x:c r="I6" s="13">
         <x:v>46091.143125</x:v>
       </x:c>
-      <x:c r="J6" s="11" t="n">
+      <x:c r="J6" s="12" t="n">
         <x:v>125646</x:v>
       </x:c>
-      <x:c r="K6" s="13" t="n">
+      <x:c r="K6" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L6" s="12">
+      <x:c r="L6" s="15">
         <x:v>46091.1453125</x:v>
       </x:c>
       <x:c r="M6" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N6" s="7" t="s"/>
-      <x:c r="O6" s="9" t="s"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="A7" s="7" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="n">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="16" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C7" s="16" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="16" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E7" s="16" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="16" t="n">
         <x:v>123456789</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H7" s="12">
+      <x:c r="G7" s="16" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H7" s="17">
         <x:v>46091.059537037</x:v>
       </x:c>
-      <x:c r="I7" s="14">
+      <x:c r="I7" s="18">
         <x:v>46050</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="n">
+      <x:c r="J7" s="16" t="n">
         <x:v>165163</x:v>
       </x:c>
-      <x:c r="K7" s="13" t="n">
+      <x:c r="K7" s="19" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L7" s="12">
+      <x:c r="L7" s="17">
         <x:v>46091.0629861111</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="N7" s="7" t="s"/>
+      <x:c r="M7" s="16" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="9" t="s"/>
+      <x:c r="C8" s="9" t="s"/>
+      <x:c r="D8" s="9" t="s"/>
+      <x:c r="E8" s="9" t="s"/>
+      <x:c r="F8" s="9" t="s"/>
+      <x:c r="G8" s="9" t="s"/>
+      <x:c r="H8" s="9" t="s"/>
+      <x:c r="I8" s="9" t="s"/>
+      <x:c r="J8" s="9" t="s"/>
+      <x:c r="K8" s="9" t="s"/>
+      <x:c r="L8" s="9" t="s"/>
+      <x:c r="M8" s="9" t="s"/>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="15" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="s"/>
-      <x:c r="D10" s="16" t="s"/>
-      <x:c r="E10" s="17" t="s"/>
-      <x:c r="F10" s="17" t="s"/>
+      <x:c r="B10" s="20" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C10" s="21" t="s"/>
+      <x:c r="D10" s="21" t="s"/>
+      <x:c r="E10" s="22" t="s"/>
+      <x:c r="F10" s="22" t="s"/>
     </x:row>
     <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="18" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="19" t="s"/>
-      <x:c r="F11" s="20" t="s">
-        <x:v>25</x:v>
+      <x:c r="B11" s="23" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="C11" s="24" t="s"/>
+      <x:c r="D11" s="24" t="s"/>
+      <x:c r="E11" s="24" t="s"/>
+      <x:c r="F11" s="25" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="n">
+      <x:c r="B12" s="26" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="27" t="s"/>
+      <x:c r="D12" s="27" t="s"/>
+      <x:c r="E12" s="27" t="s"/>
+      <x:c r="F12" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="n">
+      <x:c r="B13" s="26" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C13" s="27" t="s"/>
+      <x:c r="D13" s="27" t="s"/>
+      <x:c r="E13" s="27" t="s"/>
+      <x:c r="F13" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
+      <x:c r="B14" s="29" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s"/>
+      <x:c r="D14" s="30" t="s"/>
+      <x:c r="E14" s="30" t="s"/>
+      <x:c r="F14" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <x:si>
-    <x:t>{{Name}}</x:t>
+    <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -1014,61 +1014,61 @@
       <x:c r="L9" s="9" t="s"/>
       <x:c r="M9" s="9" t="s"/>
     </x:row>
-    <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="20" t="s">
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="20" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C10" s="21" t="s"/>
-      <x:c r="D10" s="21" t="s"/>
-      <x:c r="E10" s="22" t="s"/>
-      <x:c r="F10" s="22" t="s"/>
+      <x:c r="C12" s="21" t="s"/>
+      <x:c r="D12" s="21" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="22" t="s"/>
     </x:row>
-    <x:row r="11" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B11" s="23" t="s">
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="23" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C11" s="24" t="s"/>
-      <x:c r="D11" s="24" t="s"/>
-      <x:c r="E11" s="24" t="s"/>
-      <x:c r="F11" s="25" t="s">
+      <x:c r="C13" s="24" t="s"/>
+      <x:c r="D13" s="24" t="s"/>
+      <x:c r="E13" s="24" t="s"/>
+      <x:c r="F13" s="25" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B12" s="26" t="s">
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="26" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C12" s="27" t="s"/>
-      <x:c r="D12" s="27" t="s"/>
-      <x:c r="E12" s="27" t="s"/>
-      <x:c r="F12" s="28" t="n">
+      <x:c r="C14" s="27" t="s"/>
+      <x:c r="D14" s="27" t="s"/>
+      <x:c r="E14" s="27" t="s"/>
+      <x:c r="F14" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="26" t="s">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="26" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C13" s="27" t="s"/>
-      <x:c r="D13" s="27" t="s"/>
-      <x:c r="E13" s="27" t="s"/>
-      <x:c r="F13" s="28" t="n">
+      <x:c r="C15" s="27" t="s"/>
+      <x:c r="D15" s="27" t="s"/>
+      <x:c r="E15" s="27" t="s"/>
+      <x:c r="F15" s="28" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="29" t="s">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="29" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s"/>
-      <x:c r="D14" s="30" t="s"/>
-      <x:c r="E14" s="30" t="s"/>
-      <x:c r="F14" s="31" t="n">
+      <x:c r="C16" s="30" t="s"/>
+      <x:c r="D16" s="30" t="s"/>
+      <x:c r="E16" s="30" t="s"/>
+      <x:c r="F16" s="31" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2047,14 +2047,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
-    <x:mergeCell ref="B1:M2"/>
-    <x:mergeCell ref="B3:M3"/>
-    <x:mergeCell ref="B10:F10"/>
-    <x:mergeCell ref="B11:E11"/>
-    <x:mergeCell ref="B12:E12"/>
+  <x:mergeCells count="8">
+    <x:mergeCell ref="B1:M1"/>
+    <x:mergeCell ref="B2:M2"/>
+    <x:mergeCell ref="B3:M4"/>
+    <x:mergeCell ref="B12:F12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -463,7 +463,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -499,39 +499,43 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -905,7 +909,7 @@
       <x:c r="AA5" s="5" t="s"/>
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
-    <x:row r="6" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="B6" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -945,7 +949,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>8</x:v>
@@ -985,87 +989,87 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s"/>
-      <x:c r="C8" s="9" t="s"/>
-      <x:c r="D8" s="9" t="s"/>
-      <x:c r="E8" s="9" t="s"/>
-      <x:c r="F8" s="9" t="s"/>
-      <x:c r="G8" s="9" t="s"/>
-      <x:c r="H8" s="9" t="s"/>
-      <x:c r="I8" s="9" t="s"/>
-      <x:c r="J8" s="9" t="s"/>
-      <x:c r="K8" s="9" t="s"/>
-      <x:c r="L8" s="9" t="s"/>
-      <x:c r="M8" s="9" t="s"/>
+      <x:c r="B8" s="20" t="s"/>
+      <x:c r="C8" s="20" t="s"/>
+      <x:c r="D8" s="20" t="s"/>
+      <x:c r="E8" s="20" t="s"/>
+      <x:c r="F8" s="20" t="s"/>
+      <x:c r="G8" s="20" t="s"/>
+      <x:c r="H8" s="20" t="s"/>
+      <x:c r="I8" s="20" t="s"/>
+      <x:c r="J8" s="20" t="s"/>
+      <x:c r="K8" s="20" t="s"/>
+      <x:c r="L8" s="20" t="s"/>
+      <x:c r="M8" s="20" t="s"/>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="20" t="s"/>
+      <x:c r="C9" s="20" t="s"/>
+      <x:c r="D9" s="20" t="s"/>
+      <x:c r="E9" s="20" t="s"/>
+      <x:c r="F9" s="20" t="s"/>
+      <x:c r="G9" s="20" t="s"/>
+      <x:c r="H9" s="20" t="s"/>
+      <x:c r="I9" s="20" t="s"/>
+      <x:c r="J9" s="20" t="s"/>
+      <x:c r="K9" s="20" t="s"/>
+      <x:c r="L9" s="20" t="s"/>
+      <x:c r="M9" s="20" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="21" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="23" t="s"/>
+      <x:c r="F12" s="23" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="24" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="27" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="26" t="s">
+      <x:c r="B15" s="27" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C15" s="27" t="s"/>
-      <x:c r="D15" s="27" t="s"/>
-      <x:c r="E15" s="27" t="s"/>
-      <x:c r="F15" s="28" t="n">
+      <x:c r="C15" s="28" t="s"/>
+      <x:c r="D15" s="28" t="s"/>
+      <x:c r="E15" s="28" t="s"/>
+      <x:c r="F15" s="29" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="29" t="s">
+      <x:c r="B16" s="30" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="30" t="s"/>
-      <x:c r="D16" s="30" t="s"/>
-      <x:c r="E16" s="30" t="s"/>
-      <x:c r="F16" s="31" t="n">
+      <x:c r="C16" s="31" t="s"/>
+      <x:c r="D16" s="31" t="s"/>
+      <x:c r="E16" s="31" t="s"/>
+      <x:c r="F16" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -879,7 +879,7 @@
       <x:c r="M4" s="3" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
-    <x:row r="5" spans="1:28" ht="15" customHeight="1">
+    <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
       <x:c r="B5" s="10" t="s"/>
       <x:c r="C5" s="10" t="s"/>
@@ -949,7 +949,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="16" t="s">
         <x:v>8</x:v>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -22,9 +22,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Application Type</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COMPANY NAME / NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS(NEW/REN/DUP)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULL ADDRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PERMIT NO.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REFERENCE NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE OF FILING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRATION DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OR NUMBER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMOUNT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DATE PAID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BY</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -121,22 +157,14 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -152,6 +180,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -388,7 +423,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -399,71 +434,65 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -494,95 +523,71 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -881,18 +886,6 @@
     </x:row>
     <x:row r="5" spans="1:28">
       <x:c r="A5" s="4" t="s"/>
-      <x:c r="B5" s="10" t="s"/>
-      <x:c r="C5" s="10" t="s"/>
-      <x:c r="D5" s="10" t="s"/>
-      <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="10" t="s"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="10" t="s"/>
-      <x:c r="J5" s="10" t="s"/>
-      <x:c r="K5" s="10" t="s"/>
-      <x:c r="L5" s="10" t="s"/>
-      <x:c r="M5" s="10" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -910,166 +903,178 @@
       <x:c r="AB5" s="5" t="s"/>
     </x:row>
     <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B6" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H6" s="13">
-        <x:v>46091.1148611111</x:v>
-      </x:c>
-      <x:c r="I6" s="13">
-        <x:v>46091.143125</x:v>
-      </x:c>
-      <x:c r="J6" s="12" t="n">
-        <x:v>125646</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L6" s="15">
-        <x:v>46091.1453125</x:v>
-      </x:c>
-      <x:c r="M6" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="16" t="s">
+      <x:c r="B7" s="10" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="10" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C7" s="16" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="16" t="s">
+      <x:c r="J7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E7" s="16" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F7" s="16" t="n">
-        <x:v>123456789</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="s">
+      <x:c r="K7" s="10" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H7" s="17">
-        <x:v>46091.059537037</x:v>
-      </x:c>
-      <x:c r="I7" s="18">
-        <x:v>46050</x:v>
-      </x:c>
-      <x:c r="J7" s="16" t="n">
-        <x:v>165163</x:v>
-      </x:c>
-      <x:c r="K7" s="19" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="L7" s="17">
-        <x:v>46091.0629861111</x:v>
-      </x:c>
-      <x:c r="M7" s="16" t="s">
-        <x:v>7</x:v>
+      <x:c r="L7" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="10" t="s">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="20" t="s"/>
-      <x:c r="C8" s="20" t="s"/>
-      <x:c r="D8" s="20" t="s"/>
-      <x:c r="E8" s="20" t="s"/>
-      <x:c r="F8" s="20" t="s"/>
-      <x:c r="G8" s="20" t="s"/>
-      <x:c r="H8" s="20" t="s"/>
-      <x:c r="I8" s="20" t="s"/>
-      <x:c r="J8" s="20" t="s"/>
-      <x:c r="K8" s="20" t="s"/>
-      <x:c r="L8" s="20" t="s"/>
-      <x:c r="M8" s="20" t="s"/>
+      <x:c r="B8" s="11" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="12">
+        <x:v>46091.1148611111</x:v>
+      </x:c>
+      <x:c r="I8" s="12">
+        <x:v>46091.143125</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="n">
+        <x:v>125646</x:v>
+      </x:c>
+      <x:c r="K8" s="13" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="12">
+        <x:v>46091.1453125</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="20" t="s"/>
-      <x:c r="C9" s="20" t="s"/>
-      <x:c r="D9" s="20" t="s"/>
-      <x:c r="E9" s="20" t="s"/>
-      <x:c r="F9" s="20" t="s"/>
-      <x:c r="G9" s="20" t="s"/>
-      <x:c r="H9" s="20" t="s"/>
-      <x:c r="I9" s="20" t="s"/>
-      <x:c r="J9" s="20" t="s"/>
-      <x:c r="K9" s="20" t="s"/>
-      <x:c r="L9" s="20" t="s"/>
-      <x:c r="M9" s="20" t="s"/>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="11" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="n">
+        <x:v>123456789</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H9" s="12">
+        <x:v>46091.059537037</x:v>
+      </x:c>
+      <x:c r="I9" s="14">
+        <x:v>46050</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="n">
+        <x:v>165163</x:v>
+      </x:c>
+      <x:c r="K9" s="13" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="L9" s="12">
+        <x:v>46091.0629861111</x:v>
+      </x:c>
+      <x:c r="M9" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="21" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="23" t="s"/>
-      <x:c r="F12" s="23" t="s"/>
+      <x:c r="B12" s="15" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C12" s="16" t="s"/>
+      <x:c r="D12" s="16" t="s"/>
+      <x:c r="E12" s="17" t="s"/>
+      <x:c r="F12" s="17" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="24" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="s">
-        <x:v>13</x:v>
+      <x:c r="B13" s="18" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C13" s="19" t="s"/>
+      <x:c r="D13" s="19" t="s"/>
+      <x:c r="E13" s="19" t="s"/>
+      <x:c r="F13" s="20" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="27" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
+      <x:c r="B14" s="21" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="27" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C15" s="28" t="s"/>
-      <x:c r="D15" s="28" t="s"/>
-      <x:c r="E15" s="28" t="s"/>
-      <x:c r="F15" s="29" t="n">
+      <x:c r="B15" s="21" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="30" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C16" s="31" t="s"/>
-      <x:c r="D16" s="31" t="s"/>
-      <x:c r="E16" s="31" t="s"/>
-      <x:c r="F16" s="32" t="n">
+      <x:c r="B16" s="24" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -423,11 +423,14 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="23">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -492,7 +495,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -522,6 +525,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -836,7 +843,9 @@
     </x:row>
     <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="1" t="s"/>
+      <x:c r="B2" s="10">
+        <x:v>46082</x:v>
+      </x:c>
       <x:c r="C2" s="1" t="s"/>
       <x:c r="D2" s="1" t="s"/>
       <x:c r="E2" s="1" t="s"/>
@@ -908,173 +917,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="10" t="s">
+      <x:c r="B7" s="11" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
+      <x:c r="C7" s="11" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="10" t="s">
+      <x:c r="D7" s="11" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="10" t="s">
+      <x:c r="E7" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="s">
+      <x:c r="F7" s="11" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="10" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="10" t="s">
+      <x:c r="H7" s="11" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="10" t="s">
+      <x:c r="I7" s="11" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="10" t="s">
+      <x:c r="J7" s="11" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="10" t="s">
+      <x:c r="K7" s="11" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="10" t="s">
+      <x:c r="L7" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="10" t="s">
+      <x:c r="M7" s="11" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="11" t="s">
+      <x:c r="B8" s="12" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="s">
+      <x:c r="C8" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="s">
+      <x:c r="D8" s="12" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="s">
+      <x:c r="E8" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="s">
+      <x:c r="F8" s="12" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="11" t="s">
+      <x:c r="G8" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="12">
+      <x:c r="H8" s="13">
         <x:v>46091.1148611111</x:v>
       </x:c>
-      <x:c r="I8" s="12">
+      <x:c r="I8" s="13">
         <x:v>46091.143125</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="n">
+      <x:c r="J8" s="12" t="n">
         <x:v>125646</x:v>
       </x:c>
-      <x:c r="K8" s="13" t="n">
+      <x:c r="K8" s="14" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="12">
+      <x:c r="L8" s="13">
         <x:v>46091.1453125</x:v>
       </x:c>
-      <x:c r="M8" s="11" t="s">
+      <x:c r="M8" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="11" t="s">
+      <x:c r="B9" s="12" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C9" s="11" t="s">
+      <x:c r="C9" s="12" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="s">
+      <x:c r="D9" s="12" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="E9" s="11" t="s">
+      <x:c r="E9" s="12" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="n">
+      <x:c r="F9" s="12" t="n">
         <x:v>123456789</x:v>
       </x:c>
-      <x:c r="G9" s="11" t="s">
+      <x:c r="G9" s="12" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="H9" s="12">
+      <x:c r="H9" s="13">
         <x:v>46091.059537037</x:v>
       </x:c>
-      <x:c r="I9" s="14">
+      <x:c r="I9" s="15">
         <x:v>46050</x:v>
       </x:c>
-      <x:c r="J9" s="11" t="n">
+      <x:c r="J9" s="12" t="n">
         <x:v>165163</x:v>
       </x:c>
-      <x:c r="K9" s="13" t="n">
+      <x:c r="K9" s="14" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L9" s="12">
+      <x:c r="L9" s="13">
         <x:v>46091.0629861111</x:v>
       </x:c>
-      <x:c r="M9" s="11" t="s">
+      <x:c r="M9" s="12" t="s">
         <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="15" t="s">
+      <x:c r="B12" s="16" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C12" s="16" t="s"/>
-      <x:c r="D12" s="16" t="s"/>
-      <x:c r="E12" s="17" t="s"/>
-      <x:c r="F12" s="17" t="s"/>
+      <x:c r="C12" s="17" t="s"/>
+      <x:c r="D12" s="17" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="18" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="18" t="s">
+      <x:c r="B13" s="19" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C13" s="19" t="s"/>
-      <x:c r="D13" s="19" t="s"/>
-      <x:c r="E13" s="19" t="s"/>
-      <x:c r="F13" s="20" t="s">
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="20" t="s"/>
+      <x:c r="F13" s="21" t="s">
         <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="21" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="23" t="n">
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="21" t="s">
+      <x:c r="B15" s="22" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="n">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="24" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -22,9 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>X | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -112,7 +115,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="14">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -152,6 +155,22 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="16"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF0000FF"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -423,12 +442,15 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -446,56 +468,56 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -526,75 +548,79 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -823,40 +849,40 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:28" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="1" t="s">
+      <x:c r="B1" s="10" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C1" s="1" t="s"/>
-      <x:c r="D1" s="1" t="s"/>
-      <x:c r="E1" s="1" t="s"/>
-      <x:c r="F1" s="1" t="s"/>
-      <x:c r="G1" s="1" t="s"/>
-      <x:c r="H1" s="1" t="s"/>
-      <x:c r="I1" s="1" t="s"/>
-      <x:c r="J1" s="1" t="s"/>
-      <x:c r="K1" s="1" t="s"/>
-      <x:c r="L1" s="1" t="s"/>
-      <x:c r="M1" s="1" t="s"/>
+      <x:c r="C1" s="10" t="s"/>
+      <x:c r="D1" s="10" t="s"/>
+      <x:c r="E1" s="10" t="s"/>
+      <x:c r="F1" s="10" t="s"/>
+      <x:c r="G1" s="10" t="s"/>
+      <x:c r="H1" s="10" t="s"/>
+      <x:c r="I1" s="10" t="s"/>
+      <x:c r="J1" s="10" t="s"/>
+      <x:c r="K1" s="10" t="s"/>
+      <x:c r="L1" s="10" t="s"/>
+      <x:c r="M1" s="10" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="2" spans="1:28" ht="22" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="10">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s"/>
-      <x:c r="D2" s="1" t="s"/>
-      <x:c r="E2" s="1" t="s"/>
-      <x:c r="F2" s="1" t="s"/>
-      <x:c r="G2" s="1" t="s"/>
-      <x:c r="H2" s="1" t="s"/>
-      <x:c r="I2" s="1" t="s"/>
-      <x:c r="J2" s="1" t="s"/>
-      <x:c r="K2" s="1" t="s"/>
-      <x:c r="L2" s="1" t="s"/>
-      <x:c r="M2" s="1" t="s"/>
+      <x:c r="B2" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="s"/>
+      <x:c r="D2" s="11" t="s"/>
+      <x:c r="E2" s="11" t="s"/>
+      <x:c r="F2" s="11" t="s"/>
+      <x:c r="G2" s="11" t="s"/>
+      <x:c r="H2" s="11" t="s"/>
+      <x:c r="I2" s="11" t="s"/>
+      <x:c r="J2" s="11" t="s"/>
+      <x:c r="K2" s="11" t="s"/>
+      <x:c r="L2" s="11" t="s"/>
+      <x:c r="M2" s="11" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
     <x:row r="3" spans="1:28">
@@ -917,173 +943,173 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="s">
+      <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="s">
+      <x:c r="C7" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="11" t="s">
+      <x:c r="D7" s="12" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="11" t="s">
+      <x:c r="E7" s="12" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="s">
+      <x:c r="F7" s="12" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="11" t="s">
+      <x:c r="G7" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="11" t="s">
+      <x:c r="H7" s="12" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="11" t="s">
+      <x:c r="I7" s="12" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="11" t="s">
+      <x:c r="J7" s="12" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="11" t="s">
+      <x:c r="K7" s="12" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="11" t="s">
+      <x:c r="L7" s="12" t="s">
         <x:v>12</x:v>
+      </x:c>
+      <x:c r="M7" s="12" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="12" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="12" t="s">
+      <x:c r="B8" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="12" t="s">
+      <x:c r="C8" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="12" t="s">
+      <x:c r="D8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="12" t="s">
+      <x:c r="E8" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="12" t="s">
+      <x:c r="F8" s="13" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="13">
+      <x:c r="G8" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="H8" s="14">
         <x:v>46091.1148611111</x:v>
       </x:c>
-      <x:c r="I8" s="13">
+      <x:c r="I8" s="14">
         <x:v>46091.143125</x:v>
       </x:c>
-      <x:c r="J8" s="12" t="n">
+      <x:c r="J8" s="13" t="n">
         <x:v>125646</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="n">
+      <x:c r="K8" s="15" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="13">
+      <x:c r="L8" s="14">
         <x:v>46091.1453125</x:v>
       </x:c>
-      <x:c r="M8" s="12" t="s">
-        <x:v>19</x:v>
+      <x:c r="M8" s="13" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="12" t="s">
+      <x:c r="B9" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="13" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E9" s="13" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="n">
+        <x:v>123456789</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H9" s="14">
+        <x:v>46091.059537037</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46050</x:v>
+      </x:c>
+      <x:c r="J9" s="13" t="n">
+        <x:v>165163</x:v>
+      </x:c>
+      <x:c r="K9" s="15" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="L9" s="14">
+        <x:v>46091.0629861111</x:v>
+      </x:c>
+      <x:c r="M9" s="13" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="12" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E9" s="12" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F9" s="12" t="n">
-        <x:v>123456789</x:v>
-      </x:c>
-      <x:c r="G9" s="12" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H9" s="13">
-        <x:v>46091.059537037</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46050</x:v>
-      </x:c>
-      <x:c r="J9" s="12" t="n">
-        <x:v>165163</x:v>
-      </x:c>
-      <x:c r="K9" s="14" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="L9" s="13">
-        <x:v>46091.0629861111</x:v>
-      </x:c>
-      <x:c r="M9" s="12" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="16" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s"/>
-      <x:c r="D12" s="17" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="18" t="s"/>
+      <x:c r="B12" s="17" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="s"/>
+      <x:c r="D12" s="18" t="s"/>
+      <x:c r="E12" s="19" t="s"/>
+      <x:c r="F12" s="19" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="19" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="20" t="s"/>
-      <x:c r="F13" s="21" t="s">
+      <x:c r="B13" s="20" t="s">
         <x:v>25</x:v>
+      </x:c>
+      <x:c r="C13" s="21" t="s"/>
+      <x:c r="D13" s="21" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="22" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="22" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="n">
+      <x:c r="B14" s="23" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C14" s="24" t="s"/>
+      <x:c r="D14" s="24" t="s"/>
+      <x:c r="E14" s="24" t="s"/>
+      <x:c r="F14" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="n">
+      <x:c r="B15" s="23" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C15" s="24" t="s"/>
+      <x:c r="D15" s="24" t="s"/>
+      <x:c r="E15" s="24" t="s"/>
+      <x:c r="F15" s="25" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
+      <x:c r="B16" s="26" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C16" s="27" t="s"/>
+      <x:c r="D16" s="27" t="s"/>
+      <x:c r="E16" s="27" t="s"/>
+      <x:c r="F16" s="28" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -64,6 +64,42 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ApplicationType}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Name}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Status}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Address}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PermitNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ReferenceNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DateOfFiling}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ExpirationDate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORNumber}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Amount}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.DatePaid}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -112,10 +148,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="3">
     <x:numFmt numFmtId="164" formatCode="mmmm yyyy"/>
+    <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="14">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -160,7 +198,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="16"/>
-      <x:color rgb="FF0000FF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -168,15 +206,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF0000FF"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FFFFFFFF"/>
+      <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -184,7 +214,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -199,13 +229,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -442,20 +465,20 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -468,56 +491,59 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -548,79 +574,87 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="22" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -849,74 +883,72 @@
     <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:28" ht="28" customHeight="1">
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s"/>
-      <x:c r="B1" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="s"/>
-      <x:c r="D1" s="10" t="s"/>
-      <x:c r="E1" s="10" t="s"/>
-      <x:c r="F1" s="10" t="s"/>
-      <x:c r="G1" s="10" t="s"/>
-      <x:c r="H1" s="10" t="s"/>
-      <x:c r="I1" s="10" t="s"/>
-      <x:c r="J1" s="10" t="s"/>
-      <x:c r="K1" s="10" t="s"/>
-      <x:c r="L1" s="10" t="s"/>
-      <x:c r="M1" s="10" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
       <x:c r="N1" s="1" t="s"/>
     </x:row>
-    <x:row r="2" spans="1:28" ht="22" customHeight="1">
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s"/>
-      <x:c r="B2" s="11" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="s"/>
-      <x:c r="D2" s="11" t="s"/>
-      <x:c r="E2" s="11" t="s"/>
-      <x:c r="F2" s="11" t="s"/>
-      <x:c r="G2" s="11" t="s"/>
-      <x:c r="H2" s="11" t="s"/>
-      <x:c r="I2" s="11" t="s"/>
-      <x:c r="J2" s="11" t="s"/>
-      <x:c r="K2" s="11" t="s"/>
-      <x:c r="L2" s="11" t="s"/>
-      <x:c r="M2" s="11" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
       <x:c r="N2" s="1" t="s"/>
     </x:row>
-    <x:row r="3" spans="1:28">
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
       <x:c r="A3" s="3" t="s"/>
-      <x:c r="B3" s="3">
-        <x:v>46082</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s"/>
-      <x:c r="D3" s="3" t="s"/>
-      <x:c r="E3" s="3" t="s"/>
-      <x:c r="F3" s="3" t="s"/>
-      <x:c r="G3" s="3" t="s"/>
-      <x:c r="H3" s="3" t="s"/>
-      <x:c r="I3" s="3" t="s"/>
-      <x:c r="J3" s="3" t="s"/>
-      <x:c r="K3" s="3" t="s"/>
-      <x:c r="L3" s="3" t="s"/>
-      <x:c r="M3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
       <x:c r="N3" s="3" t="s"/>
     </x:row>
-    <x:row r="4" spans="1:28">
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="3" t="s"/>
-      <x:c r="C4" s="3" t="s"/>
-      <x:c r="D4" s="3" t="s"/>
-      <x:c r="E4" s="3" t="s"/>
-      <x:c r="F4" s="3" t="s"/>
-      <x:c r="G4" s="3" t="s"/>
-      <x:c r="H4" s="3" t="s"/>
-      <x:c r="I4" s="3" t="s"/>
-      <x:c r="J4" s="3" t="s"/>
-      <x:c r="K4" s="3" t="s"/>
-      <x:c r="L4" s="3" t="s"/>
-      <x:c r="M4" s="3" t="s"/>
+      <x:c r="B4" s="11" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
     <x:row r="5" spans="1:28">
@@ -941,7 +973,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -981,140 +1013,190 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="13" t="s">
+      <x:c r="B8" s="9" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="s">
+      <x:c r="C8" s="9" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="13" t="s">
+      <x:c r="D8" s="9" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="13" t="s">
+      <x:c r="E8" s="9" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="13" t="s">
+      <x:c r="F8" s="9" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="13" t="s">
+      <x:c r="G8" s="9" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="14">
+      <x:c r="H8" s="9" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I8" s="9" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="J8" s="9" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="K8" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L8" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="M8" s="9" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15" customHeight="1">
+      <x:c r="B9" s="13" t="s"/>
+      <x:c r="C9" s="13" t="s"/>
+      <x:c r="D9" s="13" t="s"/>
+      <x:c r="E9" s="13" t="s"/>
+      <x:c r="F9" s="13" t="s"/>
+      <x:c r="G9" s="13" t="s"/>
+      <x:c r="H9" s="13" t="s"/>
+      <x:c r="I9" s="13" t="s"/>
+      <x:c r="J9" s="13" t="s"/>
+      <x:c r="K9" s="13" t="s"/>
+      <x:c r="L9" s="13" t="s"/>
+      <x:c r="M9" s="13" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B10" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="14" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H10" s="16">
         <x:v>46091.1148611111</x:v>
       </x:c>
-      <x:c r="I8" s="14">
+      <x:c r="I10" s="16">
         <x:v>46091.143125</x:v>
       </x:c>
-      <x:c r="J8" s="13" t="n">
+      <x:c r="J10" s="15" t="n">
         <x:v>125646</x:v>
       </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="14">
+      <x:c r="L10" s="18">
         <x:v>46091.1453125</x:v>
       </x:c>
-      <x:c r="M8" s="13" t="s">
-        <x:v>20</x:v>
+      <x:c r="M10" s="14" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B9" s="13" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C9" s="13" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D9" s="13" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E9" s="13" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="13" t="n">
+    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B11" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C11" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E11" s="14" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="n">
         <x:v>123456789</x:v>
       </x:c>
-      <x:c r="G9" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H9" s="14">
+      <x:c r="G11" s="14" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H11" s="16">
         <x:v>46091.059537037</x:v>
       </x:c>
-      <x:c r="I9" s="16">
+      <x:c r="I11" s="16">
         <x:v>46050</x:v>
       </x:c>
-      <x:c r="J9" s="13" t="n">
+      <x:c r="J11" s="15" t="n">
         <x:v>165163</x:v>
       </x:c>
-      <x:c r="K9" s="15" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L9" s="14">
+      <x:c r="L11" s="18">
         <x:v>46091.0629861111</x:v>
       </x:c>
-      <x:c r="M9" s="13" t="s">
-        <x:v>20</x:v>
+      <x:c r="M11" s="14" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="17" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="18" t="s"/>
-      <x:c r="D12" s="18" t="s"/>
-      <x:c r="E12" s="19" t="s"/>
-      <x:c r="F12" s="19" t="s"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="19" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="s"/>
+      <x:c r="D14" s="20" t="s"/>
+      <x:c r="E14" s="21" t="s"/>
+      <x:c r="F14" s="21" t="s"/>
     </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="20" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C13" s="21" t="s"/>
-      <x:c r="D13" s="21" t="s"/>
-      <x:c r="E13" s="21" t="s"/>
-      <x:c r="F13" s="22" t="s">
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="22" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="s">
+        <x:v>38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="25" t="s">
         <x:v>26</x:v>
       </x:c>
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="23" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C14" s="24" t="s"/>
-      <x:c r="D14" s="24" t="s"/>
-      <x:c r="E14" s="24" t="s"/>
-      <x:c r="F14" s="25" t="n">
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="25" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="23" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C15" s="24" t="s"/>
-      <x:c r="D15" s="24" t="s"/>
-      <x:c r="E15" s="24" t="s"/>
-      <x:c r="F15" s="25" t="n">
-        <x:v>1</x:v>
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="28" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="26" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C16" s="27" t="s"/>
-      <x:c r="D16" s="27" t="s"/>
-      <x:c r="E16" s="27" t="s"/>
-      <x:c r="F16" s="28" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2092,14 +2174,14 @@
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:mergeCells count="8">
-    <x:mergeCell ref="B1:M1"/>
-    <x:mergeCell ref="B2:M2"/>
-    <x:mergeCell ref="B3:M4"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -64,42 +64,6 @@
   </x:si>
   <x:si>
     <x:t>BY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ApplicationType}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Name}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Status}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Address}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.PermitNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ReferenceNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DateOfFiling}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ExpirationDate}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORNumber}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.Amount}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.DatePaid}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{item.ORBy}}</x:t>
   </x:si>
   <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
@@ -153,7 +117,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -197,7 +161,7 @@
     <x:font>
       <x:b/>
       <x:vertAlign val="baseline"/>
-      <x:sz val="16"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
@@ -206,7 +170,7 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
@@ -214,7 +178,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
+      <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -229,6 +193,13 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -465,7 +436,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -473,12 +444,12 @@
     <x:xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -491,13 +462,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -527,10 +492,13 @@
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -543,7 +511,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -574,24 +542,16 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="bottom" wrapText="0" shrinkToFit="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -606,10 +566,6 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -634,15 +590,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -973,7 +929,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -1013,187 +969,137 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="15.75" customHeight="1">
+    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="9" t="s">
+      <x:c r="B8" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="9" t="s">
+      <x:c r="C8" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="9" t="s">
+      <x:c r="D8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="9" t="s">
+      <x:c r="E8" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="9" t="s">
+      <x:c r="F8" s="13" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="9" t="s">
+      <x:c r="G8" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="9" t="s">
+      <x:c r="H8" s="14">
+        <x:v>46091.1148611111</x:v>
+      </x:c>
+      <x:c r="I8" s="14">
+        <x:v>46091.143125</x:v>
+      </x:c>
+      <x:c r="J8" s="13" t="n">
+        <x:v>125646</x:v>
+      </x:c>
+      <x:c r="K8" s="15" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="L8" s="14">
+        <x:v>46091.1453125</x:v>
+      </x:c>
+      <x:c r="M8" s="13" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I8" s="9" t="s">
+    </x:row>
+    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+      <x:c r="B9" s="13" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="J8" s="9" t="s">
+      <x:c r="C9" s="13" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="13" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="K8" s="9" t="s">
+      <x:c r="E9" s="13" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="n">
+        <x:v>123456789</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="L8" s="9" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="M8" s="9" t="s">
-        <x:v>25</x:v>
+      <x:c r="H9" s="14">
+        <x:v>46091.059537037</x:v>
+      </x:c>
+      <x:c r="I9" s="14">
+        <x:v>46050</x:v>
+      </x:c>
+      <x:c r="J9" s="13" t="n">
+        <x:v>165163</x:v>
+      </x:c>
+      <x:c r="K9" s="15" t="n">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="L9" s="14">
+        <x:v>46091.0629861111</x:v>
+      </x:c>
+      <x:c r="M9" s="13" t="s">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="15" customHeight="1">
-      <x:c r="B9" s="13" t="s"/>
-      <x:c r="C9" s="13" t="s"/>
-      <x:c r="D9" s="13" t="s"/>
-      <x:c r="E9" s="13" t="s"/>
-      <x:c r="F9" s="13" t="s"/>
-      <x:c r="G9" s="13" t="s"/>
-      <x:c r="H9" s="13" t="s"/>
-      <x:c r="I9" s="13" t="s"/>
-      <x:c r="J9" s="13" t="s"/>
-      <x:c r="K9" s="13" t="s"/>
-      <x:c r="L9" s="13" t="s"/>
-      <x:c r="M9" s="13" t="s"/>
-    </x:row>
-    <x:row r="10" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B10" s="14" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C10" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D10" s="15" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E10" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F10" s="14" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G10" s="14" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46091.1148611111</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46091.143125</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>125646</x:v>
-      </x:c>
-      <x:c r="K10" s="17" t="n">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="L10" s="18">
-        <x:v>46091.1453125</x:v>
-      </x:c>
-      <x:c r="M10" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28" ht="16.798828" customHeight="1">
-      <x:c r="B11" s="14" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C11" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F11" s="14" t="n">
-        <x:v>123456789</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46091.059537037</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46050</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="n">
-        <x:v>165163</x:v>
-      </x:c>
-      <x:c r="K11" s="17" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="L11" s="18">
-        <x:v>46091.0629861111</x:v>
-      </x:c>
-      <x:c r="M11" s="14" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="19" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C14" s="20" t="s"/>
-      <x:c r="D14" s="20" t="s"/>
-      <x:c r="E14" s="21" t="s"/>
-      <x:c r="F14" s="21" t="s"/>
+      <x:c r="B14" s="16" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="s"/>
+      <x:c r="D14" s="17" t="s"/>
+      <x:c r="E14" s="18" t="s"/>
+      <x:c r="F14" s="18" t="s"/>
     </x:row>
     <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="s">
-        <x:v>38</x:v>
+      <x:c r="B15" s="19" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="s"/>
+      <x:c r="D15" s="20" t="s"/>
+      <x:c r="E15" s="20" t="s"/>
+      <x:c r="F15" s="21" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
+      <x:c r="B16" s="22" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C16" s="23" t="s"/>
+      <x:c r="D16" s="23" t="s"/>
+      <x:c r="E16" s="23" t="s"/>
+      <x:c r="F16" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="25" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C17" s="26" t="s"/>
-      <x:c r="D17" s="26" t="s"/>
-      <x:c r="E17" s="26" t="s"/>
-      <x:c r="F17" s="27" t="n">
+      <x:c r="B17" s="22" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C17" s="23" t="s"/>
+      <x:c r="D17" s="23" t="s"/>
+      <x:c r="E17" s="23" t="s"/>
+      <x:c r="F17" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="28" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C18" s="29" t="s"/>
-      <x:c r="D18" s="29" t="s"/>
-      <x:c r="E18" s="29" t="s"/>
-      <x:c r="F18" s="30" t="n">
+      <x:c r="B18" s="25" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C18" s="26" t="s"/>
+      <x:c r="D18" s="26" t="s"/>
+      <x:c r="E18" s="26" t="s"/>
+      <x:c r="F18" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -1048,61 +1048,61 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="16" t="s">
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="16" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="C14" s="17" t="s"/>
-      <x:c r="D14" s="17" t="s"/>
-      <x:c r="E14" s="18" t="s"/>
-      <x:c r="F14" s="18" t="s"/>
+      <x:c r="C12" s="17" t="s"/>
+      <x:c r="D12" s="17" t="s"/>
+      <x:c r="E12" s="18" t="s"/>
+      <x:c r="F12" s="18" t="s"/>
     </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="19" t="s">
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="19" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C15" s="20" t="s"/>
-      <x:c r="D15" s="20" t="s"/>
-      <x:c r="E15" s="20" t="s"/>
-      <x:c r="F15" s="21" t="s">
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="20" t="s"/>
+      <x:c r="F13" s="21" t="s">
         <x:v>26</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="22" t="s">
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="22" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C16" s="23" t="s"/>
-      <x:c r="D16" s="23" t="s"/>
-      <x:c r="E16" s="23" t="s"/>
-      <x:c r="F16" s="24" t="n">
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="22" t="s">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="22" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C17" s="23" t="s"/>
-      <x:c r="D17" s="23" t="s"/>
-      <x:c r="E17" s="23" t="s"/>
-      <x:c r="F17" s="24" t="n">
+      <x:c r="C15" s="23" t="s"/>
+      <x:c r="D15" s="23" t="s"/>
+      <x:c r="E15" s="23" t="s"/>
+      <x:c r="F15" s="24" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="25" t="s">
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="25" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C18" s="26" t="s"/>
-      <x:c r="D18" s="26" t="s"/>
-      <x:c r="E18" s="26" t="s"/>
-      <x:c r="F18" s="27" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2083,11 +2083,11 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B14:F14"/>
+    <x:mergeCell ref="B12:F12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -84,6 +84,9 @@
     <x:t>61-3-2026-1403-812</x:t>
   </x:si>
   <x:si>
+    <x:t>125646</x:t>
+  </x:si>
+  <x:si>
     <x:t>cashier edge</x:t>
   </x:si>
   <x:si>
@@ -93,7 +96,13 @@
     <x:t>REN</x:t>
   </x:si>
   <x:si>
+    <x:t>123456789</x:t>
+  </x:si>
+  <x:si>
     <x:t>61-3-2026-1402-290</x:t>
+  </x:si>
+  <x:si>
+    <x:t>165163</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -117,7 +126,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -178,7 +187,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -193,13 +202,6 @@
       <x:b/>
       <x:vertAlign val="baseline"/>
       <x:sz val="14"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Arial"/>
-      <x:family val="2"/>
-    </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
       <x:family val="2"/>
@@ -436,7 +438,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="25">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -492,13 +494,10 @@
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -511,7 +510,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -555,6 +554,10 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -566,6 +569,10 @@
       <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -590,15 +597,15 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -977,7 +984,7 @@
       <x:c r="C8" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="13" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E8" s="13" t="s">
@@ -989,115 +996,115 @@
       <x:c r="G8" s="13" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="14">
-        <x:v>46091.1148611111</x:v>
-      </x:c>
-      <x:c r="I8" s="14">
-        <x:v>46091.143125</x:v>
-      </x:c>
-      <x:c r="J8" s="13" t="n">
-        <x:v>125646</x:v>
-      </x:c>
-      <x:c r="K8" s="15" t="n">
+      <x:c r="H8" s="15">
+        <x:v>46091.1148722454</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46091.1431335995</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="14">
-        <x:v>46091.1453125</x:v>
+      <x:c r="L8" s="17">
+        <x:v>46091.1453198032</x:v>
       </x:c>
       <x:c r="M8" s="13" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
       <x:c r="B9" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C9" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D9" s="13" t="s">
-        <x:v>22</x:v>
+      <x:c r="D9" s="14" t="s">
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E9" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F9" s="13" t="n">
-        <x:v>123456789</x:v>
+      <x:c r="F9" s="13" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G9" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H9" s="14">
-        <x:v>46091.059537037</x:v>
-      </x:c>
-      <x:c r="I9" s="14">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
+        <x:v>46091.0595425347</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
         <x:v>46050</x:v>
       </x:c>
-      <x:c r="J9" s="13" t="n">
-        <x:v>165163</x:v>
-      </x:c>
-      <x:c r="K9" s="15" t="n">
+      <x:c r="J9" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L9" s="14">
-        <x:v>46091.0629861111</x:v>
+      <x:c r="L9" s="17">
+        <x:v>46091.0629955324</x:v>
       </x:c>
       <x:c r="M9" s="13" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="16" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="s"/>
-      <x:c r="D12" s="17" t="s"/>
-      <x:c r="E12" s="18" t="s"/>
-      <x:c r="F12" s="18" t="s"/>
+      <x:c r="B12" s="18" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="20" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="19" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C13" s="20" t="s"/>
-      <x:c r="D13" s="20" t="s"/>
-      <x:c r="E13" s="20" t="s"/>
-      <x:c r="F13" s="21" t="s">
-        <x:v>26</x:v>
+      <x:c r="B13" s="21" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="s">
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="22" t="s">
+      <x:c r="B14" s="24" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="23" t="s"/>
-      <x:c r="D14" s="23" t="s"/>
-      <x:c r="E14" s="23" t="s"/>
-      <x:c r="F14" s="24" t="n">
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="22" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C15" s="23" t="s"/>
-      <x:c r="D15" s="23" t="s"/>
-      <x:c r="E15" s="23" t="s"/>
-      <x:c r="F15" s="24" t="n">
+      <x:c r="B15" s="24" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="25" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C16" s="26" t="s"/>
-      <x:c r="D16" s="26" t="s"/>
-      <x:c r="E16" s="26" t="s"/>
-      <x:c r="F16" s="27" t="n">
+      <x:c r="B16" s="27" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -936,7 +936,7 @@
       <x:c r="N6" s="6" t="s"/>
       <x:c r="O6" s="7" t="s"/>
     </x:row>
-    <x:row r="7" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
         <x:v>2</x:v>
@@ -976,7 +976,7 @@
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
-    <x:row r="8" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
         <x:v>14</x:v>
@@ -1015,7 +1015,7 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:28" ht="16.798828" customHeight="1">
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="13" t="s">
         <x:v>22</x:v>
       </x:c>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -103,6 +103,27 @@
   </x:si>
   <x:si>
     <x:t>165163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Permit to PURCHASE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VV SECURITY AGENCY,INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOOR #12 CALAMANSI DRIVE, CARMEN, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P-PUR-JJ-00016-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1417-424</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1489952</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CHERYL MAY DELOSO</x:t>
   </x:si>
   <x:si>
     <x:t>SUMMARY</x:t>
@@ -1053,42 +1074,67 @@
         <x:v>21</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="s"/>
+      <x:c r="E10" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F10" s="13" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="13" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H10" s="15">
+        <x:v>46107.3002695255</x:v>
+      </x:c>
+      <x:c r="I10" s="15">
+        <x:v>46107.3002866435</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="K10" s="16" t="n">
+        <x:v>2790</x:v>
+      </x:c>
+      <x:c r="L10" s="17">
+        <x:v>46111.2756475347</x:v>
+      </x:c>
+      <x:c r="M10" s="13" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="18" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="20" t="s"/>
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="18" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C13" s="19" t="s"/>
+      <x:c r="D13" s="19" t="s"/>
+      <x:c r="E13" s="20" t="s"/>
+      <x:c r="F13" s="20" t="s"/>
     </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="21" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
-        <x:v>1</x:v>
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="21" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="23" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
       <x:c r="B15" s="24" t="s">
-        <x:v>22</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="25" t="s"/>
       <x:c r="D15" s="25" t="s"/>
@@ -1097,19 +1143,39 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="27" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
-        <x:v>2</x:v>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="24" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="24" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="27" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C18" s="28" t="s"/>
+      <x:c r="D18" s="28" t="s"/>
+      <x:c r="E18" s="28" t="s"/>
+      <x:c r="F18" s="29" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
@@ -2086,15 +2152,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -22,12 +22,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>X | March 2026</x:t>
   </x:si>
   <x:si>
     <x:t>Application Type</x:t>
@@ -919,8 +916,8 @@
     </x:row>
     <x:row r="4" spans="1:28" ht="22" customHeight="1">
       <x:c r="A4" s="3" t="s"/>
-      <x:c r="B4" s="11" t="s">
-        <x:v>1</x:v>
+      <x:c r="B4" s="11">
+        <x:v>46082</x:v>
       </x:c>
       <x:c r="C4" s="11" t="s"/>
       <x:c r="D4" s="11" t="s"/>
@@ -960,62 +957,62 @@
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
       <x:c r="B7" s="12" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="s">
+      <x:c r="D7" s="12" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="s">
+      <x:c r="E7" s="12" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="s">
+      <x:c r="F7" s="12" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="s">
+      <x:c r="G7" s="12" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="s">
+      <x:c r="H7" s="12" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="s">
+      <x:c r="I7" s="12" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="s">
+      <x:c r="J7" s="12" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="s">
+      <x:c r="K7" s="12" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="12" t="s">
+      <x:c r="L7" s="12" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="12" t="s">
+      <x:c r="M7" s="12" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="M7" s="12" t="s">
-        <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
       <x:c r="B8" s="13" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C8" s="13" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="E8" s="13" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="13" t="s">
+      <x:c r="F8" s="13" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="13" t="s">
+      <x:c r="G8" s="13" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="G8" s="13" t="s">
-        <x:v>19</x:v>
       </x:c>
       <x:c r="H8" s="15">
         <x:v>46091.1148722454</x:v>
@@ -1024,7 +1021,7 @@
         <x:v>46091.1431335995</x:v>
       </x:c>
       <x:c r="J8" s="14" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
         <x:v>210</x:v>
@@ -1033,27 +1030,27 @@
         <x:v>46091.1453198032</x:v>
       </x:c>
       <x:c r="M8" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="13" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C9" s="13" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="E9" s="13" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E9" s="13" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="13" t="s">
+      <x:c r="G9" s="13" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="G9" s="13" t="s">
-        <x:v>25</x:v>
       </x:c>
       <x:c r="H9" s="15">
         <x:v>46091.0595425347</x:v>
@@ -1062,7 +1059,7 @@
         <x:v>46050</x:v>
       </x:c>
       <x:c r="J9" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="K9" s="16" t="n">
         <x:v>300</x:v>
@@ -1071,25 +1068,25 @@
         <x:v>46091.0629955324</x:v>
       </x:c>
       <x:c r="M9" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="13" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="13" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="D10" s="14" t="s"/>
       <x:c r="E10" s="13" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F10" s="13" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="F10" s="13" t="s">
+      <x:c r="G10" s="13" t="s">
         <x:v>30</x:v>
-      </x:c>
-      <x:c r="G10" s="13" t="s">
-        <x:v>31</x:v>
       </x:c>
       <x:c r="H10" s="15">
         <x:v>46107.3002695255</x:v>
@@ -1098,7 +1095,7 @@
         <x:v>46107.3002866435</x:v>
       </x:c>
       <x:c r="J10" s="14" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="K10" s="16" t="n">
         <x:v>2790</x:v>
@@ -1107,14 +1104,14 @@
         <x:v>46111.2756475347</x:v>
       </x:c>
       <x:c r="M10" s="13" t="s">
-        <x:v>33</x:v>
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="18" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C13" s="19" t="s"/>
       <x:c r="D13" s="19" t="s"/>
@@ -1123,18 +1120,18 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
       <x:c r="B14" s="21" t="s">
-        <x:v>35</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C14" s="22" t="s"/>
       <x:c r="D14" s="22" t="s"/>
       <x:c r="E14" s="22" t="s"/>
       <x:c r="F14" s="23" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
       <x:c r="B15" s="24" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C15" s="25" t="s"/>
       <x:c r="D15" s="25" t="s"/>
@@ -1145,7 +1142,7 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
       <x:c r="B16" s="24" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C16" s="25" t="s"/>
       <x:c r="D16" s="25" t="s"/>
@@ -1156,7 +1153,7 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
       <x:c r="B17" s="24" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C17" s="25" t="s"/>
       <x:c r="D17" s="25" t="s"/>
@@ -1167,7 +1164,7 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
       <x:c r="B18" s="27" t="s">
-        <x:v>37</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C18" s="28" t="s"/>
       <x:c r="D18" s="28" t="s"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -7,6 +7,7 @@
   </x:bookViews>
   <x:sheets>
     <x:sheet name="March 2026" sheetId="7" r:id="rId7"/>
+    <x:sheet name="April 2026" sheetId="8" r:id="rId8"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="Applicants">Sheet1!$A$8:$M$9</x:definedName>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -133,6 +134,24 @@
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAISANO CITY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CM RECTO AVE., CORRALES EXTN.,, BRGY. 25, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-21-04-454</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1412-703</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518165</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -144,7 +163,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -224,6 +243,13 @@
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="12"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
   </x:fonts>
   <x:fills count="5">
     <x:fill>
@@ -456,7 +482,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -527,8 +553,20 @@
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="33">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -637,6 +675,18 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -2173,4 +2223,1258 @@
   </x:headerFooter>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="0" summaryRight="0"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:AB993"/>
+  <x:sheetFormatPr defaultColWidth="13.340625" defaultRowHeight="15" customHeight="1"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3.38" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="21.25" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="24.13" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="21" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18.25" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.75" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="23.13" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.5" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18.75" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="16.38" style="0" customWidth="1"/>
+    <x:col min="12" max="13" width="13.88" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="2.38" style="0" customWidth="1"/>
+    <x:col min="15" max="28" width="12.63" style="0" hidden="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A1" s="1" t="s"/>
+      <x:c r="B1" s="1" t="s"/>
+      <x:c r="C1" s="1" t="s"/>
+      <x:c r="D1" s="1" t="s"/>
+      <x:c r="E1" s="1" t="s"/>
+      <x:c r="F1" s="1" t="s"/>
+      <x:c r="G1" s="1" t="s"/>
+      <x:c r="H1" s="1" t="s"/>
+      <x:c r="I1" s="1" t="s"/>
+      <x:c r="J1" s="1" t="s"/>
+      <x:c r="K1" s="1" t="s"/>
+      <x:c r="L1" s="1" t="s"/>
+      <x:c r="M1" s="1" t="s"/>
+      <x:c r="N1" s="1" t="s"/>
+    </x:row>
+    <x:row r="2" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="A2" s="1" t="s"/>
+      <x:c r="B2" s="1" t="s"/>
+      <x:c r="C2" s="1" t="s"/>
+      <x:c r="D2" s="1" t="s"/>
+      <x:c r="E2" s="1" t="s"/>
+      <x:c r="F2" s="1" t="s"/>
+      <x:c r="G2" s="1" t="s"/>
+      <x:c r="H2" s="1" t="s"/>
+      <x:c r="I2" s="1" t="s"/>
+      <x:c r="J2" s="1" t="s"/>
+      <x:c r="K2" s="1" t="s"/>
+      <x:c r="L2" s="1" t="s"/>
+      <x:c r="M2" s="1" t="s"/>
+      <x:c r="N2" s="1" t="s"/>
+    </x:row>
+    <x:row r="3" spans="1:28" ht="28" customHeight="1">
+      <x:c r="A3" s="3" t="s"/>
+      <x:c r="B3" s="10" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s"/>
+      <x:c r="D3" s="10" t="s"/>
+      <x:c r="E3" s="10" t="s"/>
+      <x:c r="F3" s="10" t="s"/>
+      <x:c r="G3" s="10" t="s"/>
+      <x:c r="H3" s="10" t="s"/>
+      <x:c r="I3" s="10" t="s"/>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
+      <x:c r="L3" s="10" t="s"/>
+      <x:c r="M3" s="10" t="s"/>
+      <x:c r="N3" s="3" t="s"/>
+    </x:row>
+    <x:row r="4" spans="1:28" ht="22" customHeight="1">
+      <x:c r="A4" s="3" t="s"/>
+      <x:c r="B4" s="11">
+        <x:v>46113</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s"/>
+      <x:c r="D4" s="11" t="s"/>
+      <x:c r="E4" s="11" t="s"/>
+      <x:c r="F4" s="11" t="s"/>
+      <x:c r="G4" s="11" t="s"/>
+      <x:c r="H4" s="11" t="s"/>
+      <x:c r="I4" s="11" t="s"/>
+      <x:c r="J4" s="11" t="s"/>
+      <x:c r="K4" s="11" t="s"/>
+      <x:c r="L4" s="11" t="s"/>
+      <x:c r="M4" s="11" t="s"/>
+      <x:c r="N4" s="3" t="s"/>
+    </x:row>
+    <x:row r="5" spans="1:28">
+      <x:c r="A5" s="4" t="s"/>
+      <x:c r="N5" s="4" t="s"/>
+      <x:c r="O5" s="5" t="s"/>
+      <x:c r="P5" s="5" t="s"/>
+      <x:c r="Q5" s="5" t="s"/>
+      <x:c r="R5" s="5" t="s"/>
+      <x:c r="S5" s="5" t="s"/>
+      <x:c r="T5" s="5" t="s"/>
+      <x:c r="U5" s="5" t="s"/>
+      <x:c r="V5" s="5" t="s"/>
+      <x:c r="W5" s="5" t="s"/>
+      <x:c r="X5" s="5" t="s"/>
+      <x:c r="Y5" s="5" t="s"/>
+      <x:c r="Z5" s="5" t="s"/>
+      <x:c r="AA5" s="5" t="s"/>
+      <x:c r="AB5" s="5" t="s"/>
+    </x:row>
+    <x:row r="6" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="N6" s="6" t="s"/>
+      <x:c r="O6" s="7" t="s"/>
+    </x:row>
+    <x:row r="7" spans="1:28" ht="20" customHeight="1">
+      <x:c r="A7" s="6" t="s"/>
+      <x:c r="B7" s="12" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="12" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D7" s="12" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="12" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F7" s="12" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G7" s="12" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H7" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I7" s="12" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J7" s="12" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K7" s="12" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L7" s="12" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M7" s="12" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N7" s="6" t="s"/>
+    </x:row>
+    <x:row r="8" spans="1:28" ht="30" customHeight="1">
+      <x:c r="A8" s="6" t="s"/>
+      <x:c r="B8" s="30" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C8" s="30" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D8" s="30" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E8" s="30" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F8" s="30" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G8" s="30" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H8" s="31">
+        <x:v>46105.3461754861</x:v>
+      </x:c>
+      <x:c r="I8" s="31">
+        <x:v>46137</x:v>
+      </x:c>
+      <x:c r="J8" s="30" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="K8" s="32" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="31">
+        <x:v>46120.2790231597</x:v>
+      </x:c>
+      <x:c r="M8" s="30" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
+      <x:c r="B9" s="9" t="s"/>
+      <x:c r="C9" s="9" t="s"/>
+      <x:c r="D9" s="9" t="s"/>
+      <x:c r="E9" s="9" t="s"/>
+      <x:c r="F9" s="9" t="s"/>
+      <x:c r="G9" s="9" t="s"/>
+      <x:c r="H9" s="9" t="s"/>
+      <x:c r="I9" s="9" t="s"/>
+      <x:c r="J9" s="9" t="s"/>
+      <x:c r="K9" s="9" t="s"/>
+      <x:c r="L9" s="9" t="s"/>
+      <x:c r="M9" s="9" t="s"/>
+    </x:row>
+    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="18" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="s"/>
+      <x:c r="D11" s="19" t="s"/>
+      <x:c r="E11" s="20" t="s"/>
+      <x:c r="F11" s="20" t="s"/>
+    </x:row>
+    <x:row r="12" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B12" s="21" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C12" s="22" t="s"/>
+      <x:c r="D12" s="22" t="s"/>
+      <x:c r="E12" s="22" t="s"/>
+      <x:c r="F12" s="23" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B13" s="24" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s"/>
+      <x:c r="D13" s="25" t="s"/>
+      <x:c r="E13" s="25" t="s"/>
+      <x:c r="F13" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B14" s="27" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="28" t="s"/>
+      <x:c r="D14" s="28" t="s"/>
+      <x:c r="E14" s="28" t="s"/>
+      <x:c r="F14" s="29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="44" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="45" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="46" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="47" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="48" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="49" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="50" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="51" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="52" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="53" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="54" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="55" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="56" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="57" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="58" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="59" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="60" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="61" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="62" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="63" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="64" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="65" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="66" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="67" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="68" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="69" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="70" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="71" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="72" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="73" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="74" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="75" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="76" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="77" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="78" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="79" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="80" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="81" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="82" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="83" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="84" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="85" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="86" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="87" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="88" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="89" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="90" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="91" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="92" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="93" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="94" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="95" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="96" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="97" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="98" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="99" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="100" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="101" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="102" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="103" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="104" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="105" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="106" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="107" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="108" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="109" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="110" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="111" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="112" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="113" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="114" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="115" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="116" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="117" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="118" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="119" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="120" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="121" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="122" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="123" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="124" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="125" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="126" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="127" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="128" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="129" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="130" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="131" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="132" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="133" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="134" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="135" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="136" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="137" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="138" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="139" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="140" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="141" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="142" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="143" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="144" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="145" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="146" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="147" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="148" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="149" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="150" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="151" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="152" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="153" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="154" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="155" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="156" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="157" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="158" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="159" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="160" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="161" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="162" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="163" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="164" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="165" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="166" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="167" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="168" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="169" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="170" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="171" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="172" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="173" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="174" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="175" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="176" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="177" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="178" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="179" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="180" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="181" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="182" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="183" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="184" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="185" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="186" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="187" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="188" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="189" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="190" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="191" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="192" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="193" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="194" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="195" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="196" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="197" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="198" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="199" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="200" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="201" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="202" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="203" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="204" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="205" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="206" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="207" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="208" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="209" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="210" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="211" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="212" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="213" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="214" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="215" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="216" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="217" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="218" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="219" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="220" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="221" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="222" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="223" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="224" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="225" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="226" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="227" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="228" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="229" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="230" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="231" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="232" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="233" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="234" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="235" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="236" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="237" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="238" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="239" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="240" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="241" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="242" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="243" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="244" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="245" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="246" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="247" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="248" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="249" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="250" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="251" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="252" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="253" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="254" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="255" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="256" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="257" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="258" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="259" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="260" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="261" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="262" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="263" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="264" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="265" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="266" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="267" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="268" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="269" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="270" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="271" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="272" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="273" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="274" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="275" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="276" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="277" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="278" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="279" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="280" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="281" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="282" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="283" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="284" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="285" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="286" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="287" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="288" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="289" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="290" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="291" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="292" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="293" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="294" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="295" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="296" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="297" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="298" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="299" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="300" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="301" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="302" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="303" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="304" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="305" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="306" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="307" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="308" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="309" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="310" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="311" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="312" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="313" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="314" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="315" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="316" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="317" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="318" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="319" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="320" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="321" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="322" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="323" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="324" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="325" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="326" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="327" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="328" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="329" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="330" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="331" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="332" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="333" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="334" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="335" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="336" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="337" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="338" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="339" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="340" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="341" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="342" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="343" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="344" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="345" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="346" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="347" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="348" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="349" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="350" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="351" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="352" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="353" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="354" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="355" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="356" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="357" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="358" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="359" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="360" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="361" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="362" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="363" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="364" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="365" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="366" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="367" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="368" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="369" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="370" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="371" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="372" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="373" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="374" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="375" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="376" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="377" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="378" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="379" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="380" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="381" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="382" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="383" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="384" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="385" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="386" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="387" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="388" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="389" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="390" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="391" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="392" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="393" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="394" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="395" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="396" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="397" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="398" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="399" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="400" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="401" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="402" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="403" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="404" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="405" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="406" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="407" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="408" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="409" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="410" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="411" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="412" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="413" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="414" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="415" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="416" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="417" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="418" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="419" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="420" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="421" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="422" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="423" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="424" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="425" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="426" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="427" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="428" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="429" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="430" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="431" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="432" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="433" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="434" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="435" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="436" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="437" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="438" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="439" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="440" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="441" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="442" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="443" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="444" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="445" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="446" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="447" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="448" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="449" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="450" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="451" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="452" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="453" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="454" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="455" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="456" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="457" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="458" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="459" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="460" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="461" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="462" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="463" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="464" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="465" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="466" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="467" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="468" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="469" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="470" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="471" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="472" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="473" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="474" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="475" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="476" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="477" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="478" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="479" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="480" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="481" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="482" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="483" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="484" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="485" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="486" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="487" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="488" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="489" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="490" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="491" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="492" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="493" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="494" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="495" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="496" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="497" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="498" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="499" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="500" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="501" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="502" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="503" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="504" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="505" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="506" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="507" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="508" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="509" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="510" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="511" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="512" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="513" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="514" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="515" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="516" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="517" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="518" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="519" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="520" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="521" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="522" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="523" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="524" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="525" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="526" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="527" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="528" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="529" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="530" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="531" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="532" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="533" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="534" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="535" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="536" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="537" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="538" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="539" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="540" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="541" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="542" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="543" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="544" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="545" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="546" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="547" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="548" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="549" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="550" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="551" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="552" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="553" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="554" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="555" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="556" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="557" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="558" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="559" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="560" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="561" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="562" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="563" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="564" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="565" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="566" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="567" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="568" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="569" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="570" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="571" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="572" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="573" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="574" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="575" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="576" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="577" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="578" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="579" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="580" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="581" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="582" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="583" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="584" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="585" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="586" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="587" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="588" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="589" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="590" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="591" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="592" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="593" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="594" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="595" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="596" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="597" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="598" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="599" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="600" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="601" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="602" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="603" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="604" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="605" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="606" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="607" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="608" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="609" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="610" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="611" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="612" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="613" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="614" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="615" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="616" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="617" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="618" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="619" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="620" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="621" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="622" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="623" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="624" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="625" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="626" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="627" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="628" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="629" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="630" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="631" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="632" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="633" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="634" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="635" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="636" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="637" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="638" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="639" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="640" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="641" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="642" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="643" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="644" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="645" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="646" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="647" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="648" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="649" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="650" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="651" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="652" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="653" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="654" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="655" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="656" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="657" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="658" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="659" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="660" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="661" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="662" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="663" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="664" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="665" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="666" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="667" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="668" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="669" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="670" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="671" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="672" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="673" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="674" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="675" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="676" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="677" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="678" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="679" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="680" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="681" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="682" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="683" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="684" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="685" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="686" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="687" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="688" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="689" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="690" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="691" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="692" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="693" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="694" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="695" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="696" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="697" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="698" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="699" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="700" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="701" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="702" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="703" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="704" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="705" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="706" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="707" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="708" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="709" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="710" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="711" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="712" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="713" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="714" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="715" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="716" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="717" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="718" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="719" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="720" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="721" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="722" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="723" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="724" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="725" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="726" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="727" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="728" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="729" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="730" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="731" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="732" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="733" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="734" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="735" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="736" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="737" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="738" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="739" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="740" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="741" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="742" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="743" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="744" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="745" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="746" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="747" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="748" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="749" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="750" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="751" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="752" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="753" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="754" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="755" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="756" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="757" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="758" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="759" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="760" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="761" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="762" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="763" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="764" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="765" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="766" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="767" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="768" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="769" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="770" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="771" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="772" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="773" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="774" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="775" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="776" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="777" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="778" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="779" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="780" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="781" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="782" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="783" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="784" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="785" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="786" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="787" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="788" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="789" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="790" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="791" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="792" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="793" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="794" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="795" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="796" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="797" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="798" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="799" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="800" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="801" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="802" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="803" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="804" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="805" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="806" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="807" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="808" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="809" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="810" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="811" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="812" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="813" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="814" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="815" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="816" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="817" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="818" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="819" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="820" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="821" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="822" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="823" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="824" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="825" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="826" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="827" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="828" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="829" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="830" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="831" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="832" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="833" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="834" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="835" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="836" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="837" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="838" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="839" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="840" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="841" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="842" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="843" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="844" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="845" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="846" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="847" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="848" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="849" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="850" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="851" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="852" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="853" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="854" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="855" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="856" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="857" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="858" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="859" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="860" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="861" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="862" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="863" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="864" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="865" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="866" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="867" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="868" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="869" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="870" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="871" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="872" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="873" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="874" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="875" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="876" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="877" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="878" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="879" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="880" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="881" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="882" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="883" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="884" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="885" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="886" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="887" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="888" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="889" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="890" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="891" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="892" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="893" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="894" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="895" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="896" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="897" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="898" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="899" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="900" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="901" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="902" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="903" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="904" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="905" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="906" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="907" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="908" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="909" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="910" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="911" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="912" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="913" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="914" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="915" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="916" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="917" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="918" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="919" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="920" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="921" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="922" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="923" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="924" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="925" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="926" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="927" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="928" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="929" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="930" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="931" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="932" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="933" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="934" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="935" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="936" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="937" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="938" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="939" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="940" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="941" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="942" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="943" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="944" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="945" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="946" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="947" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="948" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="949" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="950" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="951" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="952" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="953" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="954" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="955" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="956" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="957" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="958" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="959" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="960" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="961" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="962" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="963" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="964" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="965" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="966" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="967" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="968" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="969" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="970" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="971" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="972" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="973" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="974" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="975" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="976" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="977" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="978" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="979" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="980" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="981" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="982" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="983" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="984" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="985" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="986" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="987" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="988" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="989" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="990" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="991" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="B1:M2"/>
+    <x:mergeCell ref="B3:M3"/>
+    <x:mergeCell ref="B4:M4"/>
+    <x:mergeCell ref="B11:F11"/>
+    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B14:E14"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="1" alignWithMargins="1">
+    <x:oddHeader/>
+    <x:oddFooter/>
+    <x:evenHeader/>
+    <x:evenFooter/>
+    <x:firstHeader/>
+    <x:firstFooter/>
+  </x:headerFooter>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -134,6 +134,24 @@
   </x:si>
   <x:si>
     <x:t>TOTAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dealer Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIDMARK WEST, INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MVVL3 K1 3RD FLOOR GAISANO CITY, Poblacion, City Of Valencia, Bukidnon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-24-04-516</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1421-158</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518169</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
@@ -163,7 +181,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -243,13 +261,6 @@
       <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
-    <x:font>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
-    </x:font>
   </x:fonts>
   <x:fills count="5">
     <x:fill>
@@ -482,7 +493,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="28">
+  <x:cellStyleXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -553,20 +564,8 @@
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="33">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -675,18 +674,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -2381,102 +2368,136 @@
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="30" t="s">
+      <x:c r="B8" s="13" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C8" s="30" t="s">
+      <x:c r="C8" s="13" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="s">
+      <x:c r="D8" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="E8" s="13" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="F8" s="13" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="G8" s="13" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="H8" s="31">
+      <x:c r="H8" s="15">
+        <x:v>46112.0874409838</x:v>
+      </x:c>
+      <x:c r="I8" s="15">
+        <x:v>46134</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="K8" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L8" s="17">
+        <x:v>46125.1598529398</x:v>
+      </x:c>
+      <x:c r="M8" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B9" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E9" s="13" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G9" s="13" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H9" s="15">
         <x:v>46105.3461754861</x:v>
       </x:c>
-      <x:c r="I8" s="31">
+      <x:c r="I9" s="15">
         <x:v>46137</x:v>
       </x:c>
-      <x:c r="J8" s="30" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
+      <x:c r="J9" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K9" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L8" s="31">
+      <x:c r="L9" s="17">
         <x:v>46120.2790231597</x:v>
       </x:c>
-      <x:c r="M8" s="30" t="s">
+      <x:c r="M9" s="13" t="s">
         <x:v>32</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28" ht="15.75" customHeight="1">
-      <x:c r="B9" s="9" t="s"/>
-      <x:c r="C9" s="9" t="s"/>
-      <x:c r="D9" s="9" t="s"/>
-      <x:c r="E9" s="9" t="s"/>
-      <x:c r="F9" s="9" t="s"/>
-      <x:c r="G9" s="9" t="s"/>
-      <x:c r="H9" s="9" t="s"/>
-      <x:c r="I9" s="9" t="s"/>
-      <x:c r="J9" s="9" t="s"/>
-      <x:c r="K9" s="9" t="s"/>
-      <x:c r="L9" s="9" t="s"/>
-      <x:c r="M9" s="9" t="s"/>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="18" t="s">
+    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="18" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C11" s="19" t="s"/>
-      <x:c r="D11" s="19" t="s"/>
-      <x:c r="E11" s="20" t="s"/>
-      <x:c r="F11" s="20" t="s"/>
+      <x:c r="C12" s="19" t="s"/>
+      <x:c r="D12" s="19" t="s"/>
+      <x:c r="E12" s="20" t="s"/>
+      <x:c r="F12" s="20" t="s"/>
     </x:row>
-    <x:row r="12" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B12" s="21" t="s">
+    <x:row r="13" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B13" s="21" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="s"/>
-      <x:c r="D12" s="22" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="23" t="s">
+      <x:c r="C13" s="22" t="s"/>
+      <x:c r="D13" s="22" t="s"/>
+      <x:c r="E13" s="22" t="s"/>
+      <x:c r="F13" s="23" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B13" s="24" t="s">
+    <x:row r="14" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B14" s="24" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s"/>
-      <x:c r="D13" s="25" t="s"/>
-      <x:c r="E13" s="25" t="s"/>
-      <x:c r="F13" s="26" t="n">
+      <x:c r="C14" s="25" t="s"/>
+      <x:c r="D14" s="25" t="s"/>
+      <x:c r="E14" s="25" t="s"/>
+      <x:c r="F14" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B14" s="27" t="s">
+    <x:row r="15" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B15" s="24" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="s"/>
+      <x:c r="D15" s="25" t="s"/>
+      <x:c r="E15" s="25" t="s"/>
+      <x:c r="F15" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B16" s="27" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C14" s="28" t="s"/>
-      <x:c r="D14" s="28" t="s"/>
-      <x:c r="E14" s="28" t="s"/>
-      <x:c r="F14" s="29" t="n">
-        <x:v>1</x:v>
+      <x:c r="C16" s="28" t="s"/>
+      <x:c r="D16" s="28" t="s"/>
+      <x:c r="E16" s="28" t="s"/>
+      <x:c r="F16" s="29" t="n">
+        <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="16" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3455,14 +3476,15 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="7">
+  <x:mergeCells count="8">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B11:F11"/>
-    <x:mergeCell ref="B12:E12"/>
+    <x:mergeCell ref="B12:F12"/>
     <x:mergeCell ref="B13:E13"/>
     <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B15:E15"/>
+    <x:mergeCell ref="B16:E16"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -137,6 +137,21 @@
   </x:si>
   <x:si>
     <x:t>Dealer Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMCOR INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sta cecilia National highway, Gusa, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01359</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1425-830</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518175</x:t>
   </x:si>
   <x:si>
     <x:t>SOLIDMARK WEST, INC.</x:t>
@@ -2387,19 +2402,19 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H8" s="15">
-        <x:v>46112.0874409838</x:v>
+        <x:v>46125.3390388079</x:v>
       </x:c>
       <x:c r="I8" s="15">
-        <x:v>46134</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J8" s="14" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L8" s="17">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46125.3538272917</x:v>
       </x:c>
       <x:c r="M8" s="13" t="s">
         <x:v>32</x:v>
@@ -2407,98 +2422,135 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="s">
         <x:v>43</x:v>
-      </x:c>
-      <x:c r="C9" s="13" t="s">
-        <x:v>44</x:v>
       </x:c>
       <x:c r="D9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E9" s="13" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F9" s="13" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="F9" s="13" t="s">
+      <x:c r="G9" s="13" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="G9" s="13" t="s">
+      <x:c r="H9" s="15">
+        <x:v>46112.0874409838</x:v>
+      </x:c>
+      <x:c r="I9" s="15">
+        <x:v>46134</x:v>
+      </x:c>
+      <x:c r="J9" s="14" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="H9" s="15">
-        <x:v>46105.3461754861</x:v>
-      </x:c>
-      <x:c r="I9" s="15">
-        <x:v>46137</x:v>
-      </x:c>
-      <x:c r="J9" s="14" t="s">
-        <x:v>48</x:v>
       </x:c>
       <x:c r="K9" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L9" s="17">
-        <x:v>46120.2790231597</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M9" s="13" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="10" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B10" s="13" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E10" s="13" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F10" s="13" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G10" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H10" s="15">
+        <x:v>46105.3461754861</x:v>
+      </x:c>
+      <x:c r="I10" s="15">
+        <x:v>46137</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="K10" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L10" s="17">
+        <x:v>46120.2790231597</x:v>
+      </x:c>
+      <x:c r="M10" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="18" t="s">
+    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="18" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C12" s="19" t="s"/>
-      <x:c r="D12" s="19" t="s"/>
-      <x:c r="E12" s="20" t="s"/>
-      <x:c r="F12" s="20" t="s"/>
+      <x:c r="C13" s="19" t="s"/>
+      <x:c r="D13" s="19" t="s"/>
+      <x:c r="E13" s="20" t="s"/>
+      <x:c r="F13" s="20" t="s"/>
     </x:row>
-    <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="21" t="s">
+    <x:row r="14" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B14" s="21" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C13" s="22" t="s"/>
-      <x:c r="D13" s="22" t="s"/>
-      <x:c r="E13" s="22" t="s"/>
-      <x:c r="F13" s="23" t="s">
+      <x:c r="C14" s="22" t="s"/>
+      <x:c r="D14" s="22" t="s"/>
+      <x:c r="E14" s="22" t="s"/>
+      <x:c r="F14" s="23" t="s">
         <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="24" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C14" s="25" t="s"/>
-      <x:c r="D14" s="25" t="s"/>
-      <x:c r="E14" s="25" t="s"/>
-      <x:c r="F14" s="26" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
       <x:c r="B15" s="24" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C15" s="25" t="s"/>
       <x:c r="D15" s="25" t="s"/>
       <x:c r="E15" s="25" t="s"/>
       <x:c r="F15" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B16" s="24" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="s"/>
+      <x:c r="D16" s="25" t="s"/>
+      <x:c r="E16" s="25" t="s"/>
+      <x:c r="F16" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B16" s="27" t="s">
+    <x:row r="17" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B17" s="27" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C16" s="28" t="s"/>
-      <x:c r="D16" s="28" t="s"/>
-      <x:c r="E16" s="28" t="s"/>
-      <x:c r="F16" s="29" t="n">
-        <x:v>2</x:v>
+      <x:c r="C17" s="28" t="s"/>
+      <x:c r="D17" s="28" t="s"/>
+      <x:c r="E17" s="28" t="s"/>
+      <x:c r="F17" s="29" t="n">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3480,11 +3532,11 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B12:F12"/>
-    <x:mergeCell ref="B13:E13"/>
+    <x:mergeCell ref="B13:F13"/>
     <x:mergeCell ref="B14:E14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
+    <x:mergeCell ref="B17:E17"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -185,6 +185,21 @@
   </x:si>
   <x:si>
     <x:t>1518165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TECHNOMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>385 Jr Borja St. Aguinaldo, 32, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX - MRR-10 - 04 - 326</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1429-808</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518180</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2496,62 +2511,99 @@
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="11" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B11" s="13" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E11" s="13" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G11" s="13" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H11" s="15">
+        <x:v>46126.2873086111</x:v>
+      </x:c>
+      <x:c r="I11" s="15">
+        <x:v>46130</x:v>
+      </x:c>
+      <x:c r="J11" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="K11" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L11" s="17">
+        <x:v>46127.0949605556</x:v>
+      </x:c>
+      <x:c r="M11" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="18" t="s">
+    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="14" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B14" s="18" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C13" s="19" t="s"/>
-      <x:c r="D13" s="19" t="s"/>
-      <x:c r="E13" s="20" t="s"/>
-      <x:c r="F13" s="20" t="s"/>
+      <x:c r="C14" s="19" t="s"/>
+      <x:c r="D14" s="19" t="s"/>
+      <x:c r="E14" s="20" t="s"/>
+      <x:c r="F14" s="20" t="s"/>
     </x:row>
-    <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="21" t="s">
+    <x:row r="15" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B15" s="21" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="23" t="s">
+      <x:c r="C15" s="22" t="s"/>
+      <x:c r="D15" s="22" t="s"/>
+      <x:c r="E15" s="22" t="s"/>
+      <x:c r="F15" s="23" t="s">
         <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="24" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
       <x:c r="B16" s="24" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C16" s="25" t="s"/>
       <x:c r="D16" s="25" t="s"/>
       <x:c r="E16" s="25" t="s"/>
       <x:c r="F16" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B17" s="27" t="s">
+    <x:row r="17" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B17" s="24" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="s"/>
+      <x:c r="D17" s="25" t="s"/>
+      <x:c r="E17" s="25" t="s"/>
+      <x:c r="F17" s="26" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B18" s="27" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C17" s="28" t="s"/>
-      <x:c r="D17" s="28" t="s"/>
-      <x:c r="E17" s="28" t="s"/>
-      <x:c r="F17" s="29" t="n">
-        <x:v>3</x:v>
+      <x:c r="C18" s="28" t="s"/>
+      <x:c r="D18" s="28" t="s"/>
+      <x:c r="E18" s="28" t="s"/>
+      <x:c r="F18" s="29" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3532,11 +3584,11 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B13:F13"/>
-    <x:mergeCell ref="B14:E14"/>
+    <x:mergeCell ref="B14:F14"/>
     <x:mergeCell ref="B15:E15"/>
     <x:mergeCell ref="B16:E16"/>
     <x:mergeCell ref="B17:E17"/>
+    <x:mergeCell ref="B18:E18"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -154,6 +154,21 @@
     <x:t>1518175</x:t>
   </x:si>
   <x:si>
+    <x:t>INTERPACE CORPORATION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WEST WING LKKS CENTER, Barangay LAPASAN, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14-REDP-CAG-01346</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1430-046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518191</x:t>
+  </x:si>
+  <x:si>
     <x:t>SOLIDMARK WEST, INC.</x:t>
   </x:si>
   <x:si>
@@ -169,6 +184,21 @@
     <x:t>1518169</x:t>
   </x:si>
   <x:si>
+    <x:t>UNIPACE CORPORATION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CM RECTO AVE., CORRALES EXTN.,, Barangay 26, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14-REDP-CAG-01347</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1432-214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518189</x:t>
+  </x:si>
+  <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
@@ -187,6 +217,18 @@
     <x:t>1518165</x:t>
   </x:si>
   <x:si>
+    <x:t>WEST WING LKKS CENTER, Barangay 31, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-10-07-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1428-833</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518192</x:t>
+  </x:si>
+  <x:si>
     <x:t>TECHNOMART</x:t>
   </x:si>
   <x:si>
@@ -200,6 +242,27 @@
   </x:si>
   <x:si>
     <x:t>1518180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTICH STREET, Barangay 04, City Of Malaybalay (Capital), Bukidnon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-13-06-152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1433-178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-10-06-128</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1431-363</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518190</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2455,19 +2518,19 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H9" s="15">
-        <x:v>46112.0874409838</x:v>
+        <x:v>46126.2900560185</x:v>
       </x:c>
       <x:c r="I9" s="15">
-        <x:v>46134</x:v>
+        <x:v>46162</x:v>
       </x:c>
       <x:c r="J9" s="14" t="s">
         <x:v>47</x:v>
       </x:c>
       <x:c r="K9" s="16" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L9" s="17">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M9" s="13" t="s">
         <x:v>32</x:v>
@@ -2475,37 +2538,37 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C10" s="13" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="C10" s="13" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="D10" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E10" s="13" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="F10" s="13" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="F10" s="13" t="s">
+      <x:c r="G10" s="13" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="G10" s="13" t="s">
+      <x:c r="H10" s="15">
+        <x:v>46112.0874409838</x:v>
+      </x:c>
+      <x:c r="I10" s="15">
+        <x:v>46134</x:v>
+      </x:c>
+      <x:c r="J10" s="14" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="H10" s="15">
-        <x:v>46105.3461754861</x:v>
-      </x:c>
-      <x:c r="I10" s="15">
-        <x:v>46137</x:v>
-      </x:c>
-      <x:c r="J10" s="14" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="K10" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L10" s="17">
-        <x:v>46120.2790231597</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M10" s="13" t="s">
         <x:v>32</x:v>
@@ -2513,102 +2576,287 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="13" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C11" s="13" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D11" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E11" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F11" s="13" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="F11" s="13" t="s">
+      <x:c r="G11" s="13" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="G11" s="13" t="s">
+      <x:c r="H11" s="15">
+        <x:v>46126.3116678125</x:v>
+      </x:c>
+      <x:c r="I11" s="15">
+        <x:v>46196</x:v>
+      </x:c>
+      <x:c r="J11" s="14" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="H11" s="15">
-        <x:v>46126.2873086111</x:v>
-      </x:c>
-      <x:c r="I11" s="15">
-        <x:v>46130</x:v>
-      </x:c>
-      <x:c r="J11" s="14" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="K11" s="16" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L11" s="17">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M11" s="13" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="13" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="12" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B12" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D12" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E12" s="13" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G12" s="13" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H12" s="15">
+        <x:v>46105.3461754861</x:v>
+      </x:c>
+      <x:c r="I12" s="15">
+        <x:v>46137</x:v>
+      </x:c>
+      <x:c r="J12" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="K12" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L12" s="17">
+        <x:v>46120.2790231597</x:v>
+      </x:c>
+      <x:c r="M12" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B13" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D13" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G13" s="13" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H13" s="15">
+        <x:v>46126.2721295949</x:v>
+      </x:c>
+      <x:c r="I13" s="15">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="J13" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="K13" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L13" s="17">
+        <x:v>46128.1955625</x:v>
+      </x:c>
+      <x:c r="M13" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="18" t="s">
+      <x:c r="B14" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D14" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F14" s="13" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G14" s="13" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H14" s="15">
+        <x:v>46126.2873086111</x:v>
+      </x:c>
+      <x:c r="I14" s="15">
+        <x:v>46130</x:v>
+      </x:c>
+      <x:c r="J14" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="K14" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L14" s="17">
+        <x:v>46127.0949605556</x:v>
+      </x:c>
+      <x:c r="M14" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B15" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D15" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H15" s="15">
+        <x:v>46126.3215783912</x:v>
+      </x:c>
+      <x:c r="I15" s="15">
+        <x:v>46198</x:v>
+      </x:c>
+      <x:c r="J15" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="K15" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L15" s="17">
+        <x:v>46128.1824279398</x:v>
+      </x:c>
+      <x:c r="M15" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B16" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D16" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H16" s="15">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I16" s="15">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J16" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="K16" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L16" s="17">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M16" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="18" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C14" s="19" t="s"/>
-      <x:c r="D14" s="19" t="s"/>
-      <x:c r="E14" s="20" t="s"/>
-      <x:c r="F14" s="20" t="s"/>
+      <x:c r="C19" s="19" t="s"/>
+      <x:c r="D19" s="19" t="s"/>
+      <x:c r="E19" s="20" t="s"/>
+      <x:c r="F19" s="20" t="s"/>
     </x:row>
-    <x:row r="15" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B15" s="21" t="s">
+    <x:row r="20" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B20" s="21" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C15" s="22" t="s"/>
-      <x:c r="D15" s="22" t="s"/>
-      <x:c r="E15" s="22" t="s"/>
-      <x:c r="F15" s="23" t="s">
+      <x:c r="C20" s="22" t="s"/>
+      <x:c r="D20" s="22" t="s"/>
+      <x:c r="E20" s="22" t="s"/>
+      <x:c r="F20" s="23" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="24" t="s">
+    <x:row r="21" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B21" s="24" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="n">
-        <x:v>2</x:v>
+      <x:c r="C21" s="25" t="s"/>
+      <x:c r="D21" s="25" t="s"/>
+      <x:c r="E21" s="25" t="s"/>
+      <x:c r="F21" s="26" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="24" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C17" s="25" t="s"/>
-      <x:c r="D17" s="25" t="s"/>
-      <x:c r="E17" s="25" t="s"/>
-      <x:c r="F17" s="26" t="n">
-        <x:v>2</x:v>
+    <x:row r="22" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B22" s="24" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C22" s="25" t="s"/>
+      <x:c r="D22" s="25" t="s"/>
+      <x:c r="E22" s="25" t="s"/>
+      <x:c r="F22" s="26" t="n">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="27" t="s">
+    <x:row r="23" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B23" s="27" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C18" s="28" t="s"/>
-      <x:c r="D18" s="28" t="s"/>
-      <x:c r="E18" s="28" t="s"/>
-      <x:c r="F18" s="29" t="n">
-        <x:v>4</x:v>
+      <x:c r="C23" s="28" t="s"/>
+      <x:c r="D23" s="28" t="s"/>
+      <x:c r="E23" s="28" t="s"/>
+      <x:c r="F23" s="29" t="n">
+        <x:v>9</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3584,11 +3832,11 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B14:F14"/>
-    <x:mergeCell ref="B15:E15"/>
-    <x:mergeCell ref="B16:E16"/>
-    <x:mergeCell ref="B17:E17"/>
-    <x:mergeCell ref="B18:E18"/>
+    <x:mergeCell ref="B19:F19"/>
+    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B23:E23"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -152,6 +152,21 @@
   </x:si>
   <x:si>
     <x:t>1518175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMCOR INCORPORATED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JVR BLDG J.R BORJA ST., BARANGAY 32, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">18-REDP-CAG-01365 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1434-610</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518195</x:t>
   </x:si>
   <x:si>
     <x:t>INTERPACE CORPORATION</x:t>
@@ -2518,10 +2533,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H9" s="15">
-        <x:v>46126.2900560185</x:v>
+        <x:v>46128.1699027199</x:v>
       </x:c>
       <x:c r="I9" s="15">
-        <x:v>46162</x:v>
+        <x:v>46136</x:v>
       </x:c>
       <x:c r="J9" s="14" t="s">
         <x:v>47</x:v>
@@ -2530,7 +2545,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L9" s="17">
-        <x:v>46128.194732662</x:v>
+        <x:v>46128.349008206</x:v>
       </x:c>
       <x:c r="M9" s="13" t="s">
         <x:v>32</x:v>
@@ -2556,19 +2571,19 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="15">
-        <x:v>46112.0874409838</x:v>
+        <x:v>46126.2900560185</x:v>
       </x:c>
       <x:c r="I10" s="15">
-        <x:v>46134</x:v>
+        <x:v>46162</x:v>
       </x:c>
       <x:c r="J10" s="14" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="K10" s="16" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L10" s="17">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M10" s="13" t="s">
         <x:v>32</x:v>
@@ -2594,19 +2609,19 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="H11" s="15">
-        <x:v>46126.3116678125</x:v>
+        <x:v>46112.0874409838</x:v>
       </x:c>
       <x:c r="I11" s="15">
-        <x:v>46196</x:v>
+        <x:v>46134</x:v>
       </x:c>
       <x:c r="J11" s="14" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="K11" s="16" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L11" s="17">
-        <x:v>46128.191368669</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M11" s="13" t="s">
         <x:v>32</x:v>
@@ -2614,37 +2629,37 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="13" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="C12" s="13" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="D12" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E12" s="13" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="F12" s="13" t="s">
+      <x:c r="G12" s="13" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G12" s="13" t="s">
+      <x:c r="H12" s="15">
+        <x:v>46126.3116678125</x:v>
+      </x:c>
+      <x:c r="I12" s="15">
+        <x:v>46196</x:v>
+      </x:c>
+      <x:c r="J12" s="14" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="H12" s="15">
-        <x:v>46105.3461754861</x:v>
-      </x:c>
-      <x:c r="I12" s="15">
-        <x:v>46137</x:v>
-      </x:c>
-      <x:c r="J12" s="14" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="K12" s="16" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L12" s="17">
-        <x:v>46120.2790231597</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M12" s="13" t="s">
         <x:v>32</x:v>
@@ -2652,37 +2667,37 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="13" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C13" s="13" t="s">
-        <x:v>43</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D13" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E13" s="13" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F13" s="13" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G13" s="13" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H13" s="15">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46105.3461754861</x:v>
       </x:c>
       <x:c r="I13" s="15">
-        <x:v>46224</x:v>
+        <x:v>46137</x:v>
       </x:c>
       <x:c r="J13" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="K13" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="17">
-        <x:v>46128.1955625</x:v>
+        <x:v>46120.2790231597</x:v>
       </x:c>
       <x:c r="M13" s="13" t="s">
         <x:v>32</x:v>
@@ -2690,10 +2705,10 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="13" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C14" s="13" t="s">
-        <x:v>68</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D14" s="14" t="s">
         <x:v>22</x:v>
@@ -2708,10 +2723,10 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="H14" s="15">
-        <x:v>46126.2873086111</x:v>
+        <x:v>46126.2721295949</x:v>
       </x:c>
       <x:c r="I14" s="15">
-        <x:v>46130</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="J14" s="14" t="s">
         <x:v>72</x:v>
@@ -2720,7 +2735,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="17">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M14" s="13" t="s">
         <x:v>32</x:v>
@@ -2728,37 +2743,37 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="13" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C15" s="13" t="s">
-        <x:v>53</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D15" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E15" s="13" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F15" s="13" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G15" s="13" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H15" s="15">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I15" s="15">
-        <x:v>46198</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J15" s="14" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="K15" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="17">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M15" s="13" t="s">
         <x:v>32</x:v>
@@ -2766,78 +2781,105 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="13" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="C16" s="13" t="s">
-        <x:v>53</x:v>
       </x:c>
       <x:c r="D16" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E16" s="13" t="s">
-        <x:v>54</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F16" s="13" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G16" s="13" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H16" s="15">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46126.3215783912</x:v>
       </x:c>
       <x:c r="I16" s="15">
-        <x:v>46189</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="J16" s="14" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K16" s="16" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="17">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46128.1824279398</x:v>
       </x:c>
       <x:c r="M16" s="13" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="17" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B17" s="13" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D17" s="14" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H17" s="15">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I17" s="15">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J17" s="14" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="K17" s="16" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L17" s="17">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M17" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="19" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B19" s="18" t="s">
+    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="18" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C19" s="19" t="s"/>
-      <x:c r="D19" s="19" t="s"/>
-      <x:c r="E19" s="20" t="s"/>
-      <x:c r="F19" s="20" t="s"/>
+      <x:c r="C20" s="19" t="s"/>
+      <x:c r="D20" s="19" t="s"/>
+      <x:c r="E20" s="20" t="s"/>
+      <x:c r="F20" s="20" t="s"/>
     </x:row>
-    <x:row r="20" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B20" s="21" t="s">
+    <x:row r="21" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B21" s="21" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C20" s="22" t="s"/>
-      <x:c r="D20" s="22" t="s"/>
-      <x:c r="E20" s="22" t="s"/>
-      <x:c r="F20" s="23" t="s">
+      <x:c r="C21" s="22" t="s"/>
+      <x:c r="D21" s="22" t="s"/>
+      <x:c r="E21" s="22" t="s"/>
+      <x:c r="F21" s="23" t="s">
         <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B21" s="24" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C21" s="25" t="s"/>
-      <x:c r="D21" s="25" t="s"/>
-      <x:c r="E21" s="25" t="s"/>
-      <x:c r="F21" s="26" t="n">
-        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
       <x:c r="B22" s="24" t="s">
-        <x:v>58</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C22" s="25" t="s"/>
       <x:c r="D22" s="25" t="s"/>
@@ -2846,18 +2888,28 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B23" s="27" t="s">
+    <x:row r="23" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B23" s="24" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C23" s="25" t="s"/>
+      <x:c r="D23" s="25" t="s"/>
+      <x:c r="E23" s="25" t="s"/>
+      <x:c r="F23" s="26" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B24" s="27" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C23" s="28" t="s"/>
-      <x:c r="D23" s="28" t="s"/>
-      <x:c r="E23" s="28" t="s"/>
-      <x:c r="F23" s="29" t="n">
-        <x:v>9</x:v>
+      <x:c r="C24" s="28" t="s"/>
+      <x:c r="D24" s="28" t="s"/>
+      <x:c r="E24" s="28" t="s"/>
+      <x:c r="F24" s="29" t="n">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3832,11 +3884,11 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B19:F19"/>
-    <x:mergeCell ref="B20:E20"/>
+    <x:mergeCell ref="B20:F20"/>
     <x:mergeCell ref="B21:E21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B24:E24"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -335,7 +335,7 @@
       <x:vertAlign val="baseline"/>
       <x:sz val="12"/>
       <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
+      <x:name val="Arial"/>
       <x:family val="2"/>
     </x:font>
     <x:font>
@@ -601,7 +601,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="24">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -612,7 +612,10 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -673,7 +676,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -708,7 +711,11 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -1064,17 +1071,17 @@
       <x:c r="B4" s="11">
         <x:v>46082</x:v>
       </x:c>
-      <x:c r="C4" s="11" t="s"/>
-      <x:c r="D4" s="11" t="s"/>
-      <x:c r="E4" s="11" t="s"/>
-      <x:c r="F4" s="11" t="s"/>
-      <x:c r="G4" s="11" t="s"/>
-      <x:c r="H4" s="11" t="s"/>
-      <x:c r="I4" s="11" t="s"/>
-      <x:c r="J4" s="11" t="s"/>
-      <x:c r="K4" s="11" t="s"/>
-      <x:c r="L4" s="11" t="s"/>
-      <x:c r="M4" s="11" t="s"/>
+      <x:c r="C4" s="12" t="s"/>
+      <x:c r="D4" s="12" t="s"/>
+      <x:c r="E4" s="12" t="s"/>
+      <x:c r="F4" s="12" t="s"/>
+      <x:c r="G4" s="12" t="s"/>
+      <x:c r="H4" s="12" t="s"/>
+      <x:c r="I4" s="12" t="s"/>
+      <x:c r="J4" s="12" t="s"/>
+      <x:c r="K4" s="12" t="s"/>
+      <x:c r="L4" s="12" t="s"/>
+      <x:c r="M4" s="12" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
     <x:row r="5" spans="1:28">
@@ -1101,220 +1108,220 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="12" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="12" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="12" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="12" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="13" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E8" s="13" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F8" s="13" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="G8" s="13" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="H8" s="16">
         <x:v>46091.1148722454</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I8" s="16">
         <x:v>46091.1431335995</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="L8" s="17">
+      <x:c r="L8" s="18">
         <x:v>46091.1453198032</x:v>
       </x:c>
-      <x:c r="M8" s="13" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="13" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C9" s="13" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E9" s="13" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="F9" s="13" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G9" s="13" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="H9" s="15">
+      <x:c r="H9" s="16">
         <x:v>46091.0595425347</x:v>
       </x:c>
-      <x:c r="I9" s="15">
+      <x:c r="I9" s="16">
         <x:v>46050</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>300</x:v>
       </x:c>
-      <x:c r="L9" s="17">
+      <x:c r="L9" s="18">
         <x:v>46091.0629955324</x:v>
       </x:c>
-      <x:c r="M9" s="13" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="13" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C10" s="13" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="D10" s="14" t="s"/>
-      <x:c r="E10" s="13" t="s">
+      <x:c r="D10" s="15" t="s"/>
+      <x:c r="E10" s="14" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="F10" s="13" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="G10" s="13" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="H10" s="15">
+      <x:c r="H10" s="16">
         <x:v>46107.3002695255</x:v>
       </x:c>
-      <x:c r="I10" s="15">
+      <x:c r="I10" s="16">
         <x:v>46107.3002866435</x:v>
       </x:c>
-      <x:c r="J10" s="14" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="K10" s="16" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>2790</x:v>
       </x:c>
-      <x:c r="L10" s="17">
+      <x:c r="L10" s="18">
         <x:v>46111.2756475347</x:v>
       </x:c>
-      <x:c r="M10" s="13" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="18" t="s">
+      <x:c r="B13" s="19" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C13" s="19" t="s"/>
-      <x:c r="D13" s="19" t="s"/>
-      <x:c r="E13" s="20" t="s"/>
-      <x:c r="F13" s="20" t="s"/>
+      <x:c r="C13" s="20" t="s"/>
+      <x:c r="D13" s="20" t="s"/>
+      <x:c r="E13" s="21" t="s"/>
+      <x:c r="F13" s="21" t="s"/>
     </x:row>
     <x:row r="14" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B14" s="21" t="s">
+      <x:c r="B14" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C14" s="22" t="s"/>
-      <x:c r="D14" s="22" t="s"/>
-      <x:c r="E14" s="22" t="s"/>
-      <x:c r="F14" s="23" t="s">
+      <x:c r="C14" s="23" t="s"/>
+      <x:c r="D14" s="23" t="s"/>
+      <x:c r="E14" s="23" t="s"/>
+      <x:c r="F14" s="24" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B15" s="24" t="s">
+      <x:c r="B15" s="25" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C15" s="25" t="s"/>
-      <x:c r="D15" s="25" t="s"/>
-      <x:c r="E15" s="25" t="s"/>
-      <x:c r="F15" s="26" t="n">
+      <x:c r="C15" s="26" t="s"/>
+      <x:c r="D15" s="26" t="s"/>
+      <x:c r="E15" s="26" t="s"/>
+      <x:c r="F15" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B16" s="24" t="s">
+      <x:c r="B16" s="25" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C16" s="25" t="s"/>
-      <x:c r="D16" s="25" t="s"/>
-      <x:c r="E16" s="25" t="s"/>
-      <x:c r="F16" s="26" t="n">
+      <x:c r="C16" s="26" t="s"/>
+      <x:c r="D16" s="26" t="s"/>
+      <x:c r="E16" s="26" t="s"/>
+      <x:c r="F16" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B17" s="24" t="s">
+      <x:c r="B17" s="25" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C17" s="25" t="s"/>
-      <x:c r="D17" s="25" t="s"/>
-      <x:c r="E17" s="25" t="s"/>
-      <x:c r="F17" s="26" t="n">
+      <x:c r="C17" s="26" t="s"/>
+      <x:c r="D17" s="26" t="s"/>
+      <x:c r="E17" s="26" t="s"/>
+      <x:c r="F17" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B18" s="27" t="s">
+      <x:c r="B18" s="28" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C18" s="28" t="s"/>
-      <x:c r="D18" s="28" t="s"/>
-      <x:c r="E18" s="28" t="s"/>
-      <x:c r="F18" s="29" t="n">
+      <x:c r="C18" s="29" t="s"/>
+      <x:c r="D18" s="29" t="s"/>
+      <x:c r="E18" s="29" t="s"/>
+      <x:c r="F18" s="30" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -2399,17 +2406,17 @@
       <x:c r="B4" s="11">
         <x:v>46113</x:v>
       </x:c>
-      <x:c r="C4" s="11" t="s"/>
-      <x:c r="D4" s="11" t="s"/>
-      <x:c r="E4" s="11" t="s"/>
-      <x:c r="F4" s="11" t="s"/>
-      <x:c r="G4" s="11" t="s"/>
-      <x:c r="H4" s="11" t="s"/>
-      <x:c r="I4" s="11" t="s"/>
-      <x:c r="J4" s="11" t="s"/>
-      <x:c r="K4" s="11" t="s"/>
-      <x:c r="L4" s="11" t="s"/>
-      <x:c r="M4" s="11" t="s"/>
+      <x:c r="C4" s="12" t="s"/>
+      <x:c r="D4" s="12" t="s"/>
+      <x:c r="E4" s="12" t="s"/>
+      <x:c r="F4" s="12" t="s"/>
+      <x:c r="G4" s="12" t="s"/>
+      <x:c r="H4" s="12" t="s"/>
+      <x:c r="I4" s="12" t="s"/>
+      <x:c r="J4" s="12" t="s"/>
+      <x:c r="K4" s="12" t="s"/>
+      <x:c r="L4" s="12" t="s"/>
+      <x:c r="M4" s="12" t="s"/>
       <x:c r="N4" s="3" t="s"/>
     </x:row>
     <x:row r="5" spans="1:28">
@@ -2436,477 +2443,477 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="12" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C7" s="12" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D7" s="12" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="E7" s="12" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F7" s="12" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G7" s="12" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="12" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I7" s="12" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J7" s="12" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K7" s="12" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L7" s="12" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="M7" s="12" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="13" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C8" s="13" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E8" s="13" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F8" s="13" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="G8" s="13" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="H8" s="15">
+      <x:c r="H8" s="16">
         <x:v>46125.3390388079</x:v>
       </x:c>
-      <x:c r="I8" s="15">
+      <x:c r="I8" s="16">
         <x:v>46135</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="K8" s="16" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L8" s="17">
+      <x:c r="L8" s="18">
         <x:v>46125.3538272917</x:v>
       </x:c>
-      <x:c r="M8" s="13" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="13" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C9" s="13" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E9" s="13" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="F9" s="13" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G9" s="13" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="H9" s="15">
+      <x:c r="H9" s="16">
         <x:v>46128.1699027199</x:v>
       </x:c>
-      <x:c r="I9" s="15">
+      <x:c r="I9" s="16">
         <x:v>46136</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="K9" s="16" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L9" s="17">
+      <x:c r="L9" s="18">
         <x:v>46128.349008206</x:v>
       </x:c>
-      <x:c r="M9" s="13" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B10" s="13" t="s">
+      <x:c r="B10" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C10" s="13" t="s">
+      <x:c r="C10" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D10" s="14" t="s">
+      <x:c r="D10" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E10" s="13" t="s">
+      <x:c r="E10" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F10" s="13" t="s">
+      <x:c r="F10" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G10" s="13" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="H10" s="15">
+      <x:c r="H10" s="16">
         <x:v>46126.2900560185</x:v>
       </x:c>
-      <x:c r="I10" s="15">
+      <x:c r="I10" s="16">
         <x:v>46162</x:v>
       </x:c>
-      <x:c r="J10" s="14" t="s">
+      <x:c r="J10" s="15" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="K10" s="16" t="n">
+      <x:c r="K10" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L10" s="17">
+      <x:c r="L10" s="18">
         <x:v>46128.194732662</x:v>
       </x:c>
-      <x:c r="M10" s="13" t="s">
+      <x:c r="M10" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B11" s="13" t="s">
+      <x:c r="B11" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C11" s="13" t="s">
+      <x:c r="C11" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D11" s="14" t="s">
+      <x:c r="D11" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E11" s="13" t="s">
+      <x:c r="E11" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="F11" s="13" t="s">
+      <x:c r="F11" s="14" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G11" s="13" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H11" s="15">
+      <x:c r="H11" s="16">
         <x:v>46112.0874409838</x:v>
       </x:c>
-      <x:c r="I11" s="15">
+      <x:c r="I11" s="16">
         <x:v>46134</x:v>
       </x:c>
-      <x:c r="J11" s="14" t="s">
+      <x:c r="J11" s="15" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="K11" s="16" t="n">
+      <x:c r="K11" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L11" s="17">
+      <x:c r="L11" s="18">
         <x:v>46125.1598529398</x:v>
       </x:c>
-      <x:c r="M11" s="13" t="s">
+      <x:c r="M11" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="13" t="s">
+      <x:c r="B12" s="14" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C12" s="13" t="s">
+      <x:c r="C12" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D12" s="14" t="s">
+      <x:c r="D12" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E12" s="13" t="s">
+      <x:c r="E12" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="F12" s="13" t="s">
+      <x:c r="F12" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G12" s="13" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="H12" s="15">
+      <x:c r="H12" s="16">
         <x:v>46126.3116678125</x:v>
       </x:c>
-      <x:c r="I12" s="15">
+      <x:c r="I12" s="16">
         <x:v>46196</x:v>
       </x:c>
-      <x:c r="J12" s="14" t="s">
+      <x:c r="J12" s="15" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="K12" s="16" t="n">
+      <x:c r="K12" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
-      <x:c r="L12" s="17">
+      <x:c r="L12" s="18">
         <x:v>46128.191368669</x:v>
       </x:c>
-      <x:c r="M12" s="13" t="s">
+      <x:c r="M12" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B13" s="13" t="s">
+      <x:c r="B13" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C13" s="13" t="s">
+      <x:c r="C13" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D13" s="14" t="s">
+      <x:c r="D13" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E13" s="13" t="s">
+      <x:c r="E13" s="14" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="F13" s="13" t="s">
+      <x:c r="F13" s="14" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G13" s="13" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="H13" s="15">
+      <x:c r="H13" s="16">
         <x:v>46105.3461754861</x:v>
       </x:c>
-      <x:c r="I13" s="15">
+      <x:c r="I13" s="16">
         <x:v>46137</x:v>
       </x:c>
-      <x:c r="J13" s="14" t="s">
+      <x:c r="J13" s="15" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="K13" s="16" t="n">
+      <x:c r="K13" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L13" s="17">
+      <x:c r="L13" s="18">
         <x:v>46120.2790231597</x:v>
       </x:c>
-      <x:c r="M13" s="13" t="s">
+      <x:c r="M13" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B14" s="13" t="s">
+      <x:c r="B14" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C14" s="13" t="s">
+      <x:c r="C14" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="D14" s="14" t="s">
+      <x:c r="D14" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E14" s="13" t="s">
+      <x:c r="E14" s="14" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="F14" s="13" t="s">
+      <x:c r="F14" s="14" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G14" s="13" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="H14" s="15">
+      <x:c r="H14" s="16">
         <x:v>46126.2721295949</x:v>
       </x:c>
-      <x:c r="I14" s="15">
+      <x:c r="I14" s="16">
         <x:v>46224</x:v>
       </x:c>
-      <x:c r="J14" s="14" t="s">
+      <x:c r="J14" s="15" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="K14" s="16" t="n">
+      <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L14" s="17">
+      <x:c r="L14" s="18">
         <x:v>46128.1955625</x:v>
       </x:c>
-      <x:c r="M14" s="13" t="s">
+      <x:c r="M14" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B15" s="13" t="s">
+      <x:c r="B15" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C15" s="13" t="s">
+      <x:c r="C15" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="D15" s="14" t="s">
+      <x:c r="D15" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E15" s="13" t="s">
+      <x:c r="E15" s="14" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="F15" s="13" t="s">
+      <x:c r="F15" s="14" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="G15" s="13" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="H15" s="15">
+      <x:c r="H15" s="16">
         <x:v>46126.2873086111</x:v>
       </x:c>
-      <x:c r="I15" s="15">
+      <x:c r="I15" s="16">
         <x:v>46130</x:v>
       </x:c>
-      <x:c r="J15" s="14" t="s">
+      <x:c r="J15" s="15" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="K15" s="16" t="n">
+      <x:c r="K15" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L15" s="17">
+      <x:c r="L15" s="18">
         <x:v>46127.0949605556</x:v>
       </x:c>
-      <x:c r="M15" s="13" t="s">
+      <x:c r="M15" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B16" s="13" t="s">
+      <x:c r="B16" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C16" s="13" t="s">
+      <x:c r="C16" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D16" s="14" t="s">
+      <x:c r="D16" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E16" s="13" t="s">
+      <x:c r="E16" s="14" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="F16" s="13" t="s">
+      <x:c r="F16" s="14" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G16" s="13" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="H16" s="15">
+      <x:c r="H16" s="16">
         <x:v>46126.3215783912</x:v>
       </x:c>
-      <x:c r="I16" s="15">
+      <x:c r="I16" s="16">
         <x:v>46198</x:v>
       </x:c>
-      <x:c r="J16" s="14" t="s">
+      <x:c r="J16" s="15" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="K16" s="16" t="n">
+      <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L16" s="17">
+      <x:c r="L16" s="18">
         <x:v>46128.1824279398</x:v>
       </x:c>
-      <x:c r="M16" s="13" t="s">
+      <x:c r="M16" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B17" s="13" t="s">
+      <x:c r="B17" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C17" s="13" t="s">
+      <x:c r="C17" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D17" s="14" t="s">
+      <x:c r="D17" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="E17" s="13" t="s">
+      <x:c r="E17" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="F17" s="13" t="s">
+      <x:c r="F17" s="14" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="G17" s="13" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="H17" s="15">
+      <x:c r="H17" s="16">
         <x:v>46126.3072273495</x:v>
       </x:c>
-      <x:c r="I17" s="15">
+      <x:c r="I17" s="16">
         <x:v>46189</x:v>
       </x:c>
-      <x:c r="J17" s="14" t="s">
+      <x:c r="J17" s="15" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="K17" s="16" t="n">
+      <x:c r="K17" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
-      <x:c r="L17" s="17">
+      <x:c r="L17" s="18">
         <x:v>46128.1930397685</x:v>
       </x:c>
-      <x:c r="M17" s="13" t="s">
+      <x:c r="M17" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="18" t="s">
+      <x:c r="B20" s="19" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C20" s="19" t="s"/>
-      <x:c r="D20" s="19" t="s"/>
-      <x:c r="E20" s="20" t="s"/>
-      <x:c r="F20" s="20" t="s"/>
+      <x:c r="C20" s="20" t="s"/>
+      <x:c r="D20" s="20" t="s"/>
+      <x:c r="E20" s="21" t="s"/>
+      <x:c r="F20" s="21" t="s"/>
     </x:row>
     <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="21" t="s">
+      <x:c r="B21" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C21" s="22" t="s"/>
-      <x:c r="D21" s="22" t="s"/>
-      <x:c r="E21" s="22" t="s"/>
-      <x:c r="F21" s="23" t="s">
+      <x:c r="C21" s="23" t="s"/>
+      <x:c r="D21" s="23" t="s"/>
+      <x:c r="E21" s="23" t="s"/>
+      <x:c r="F21" s="24" t="s">
         <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="24" t="s">
+      <x:c r="B22" s="25" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C22" s="25" t="s"/>
-      <x:c r="D22" s="25" t="s"/>
-      <x:c r="E22" s="25" t="s"/>
-      <x:c r="F22" s="26" t="n">
+      <x:c r="C22" s="26" t="s"/>
+      <x:c r="D22" s="26" t="s"/>
+      <x:c r="E22" s="26" t="s"/>
+      <x:c r="F22" s="27" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="24" t="s">
+      <x:c r="B23" s="25" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C23" s="25" t="s"/>
-      <x:c r="D23" s="25" t="s"/>
-      <x:c r="E23" s="25" t="s"/>
-      <x:c r="F23" s="26" t="n">
+      <x:c r="C23" s="26" t="s"/>
+      <x:c r="D23" s="26" t="s"/>
+      <x:c r="E23" s="26" t="s"/>
+      <x:c r="F23" s="27" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="27" t="s">
+      <x:c r="B24" s="28" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C24" s="28" t="s"/>
-      <x:c r="D24" s="28" t="s"/>
-      <x:c r="E24" s="28" t="s"/>
-      <x:c r="F24" s="29" t="n">
+      <x:c r="C24" s="29" t="s"/>
+      <x:c r="D24" s="29" t="s"/>
+      <x:c r="E24" s="29" t="s"/>
+      <x:c r="F24" s="30" t="n">
         <x:v>10</x:v>
       </x:c>
     </x:row>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -212,6 +212,15 @@
   </x:si>
   <x:si>
     <x:t>1518189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/PUR-JJ-00018-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1422-426</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518202</x:t>
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
@@ -2674,37 +2683,35 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C13" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s"/>
+      <x:c r="E13" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C13" s="14" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D13" s="15" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E13" s="14" t="s">
+      <x:c r="H13" s="16">
+        <x:v>46120.3579437153</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46120.3579643171</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46105.3461754861</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46137</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>2790</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46120.2790231597</x:v>
+        <x:v>46132.2453653241</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>32</x:v>
@@ -2712,37 +2719,37 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="H14" s="16">
+        <x:v>46105.3461754861</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46137</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
         <x:v>71</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46126.2721295949</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46224</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46120.2790231597</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>32</x:v>
@@ -2750,37 +2757,37 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G15" s="14" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="H15" s="16">
+        <x:v>46126.2721295949</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46126.2873086111</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46130</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>32</x:v>
@@ -2788,37 +2795,37 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="H16" s="16">
+        <x:v>46126.2873086111</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46130</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46126.3215783912</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46198</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>32</x:v>
@@ -2826,7 +2833,7 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
         <x:v>58</x:v>
@@ -2835,7 +2842,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
-        <x:v>59</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
         <x:v>82</x:v>
@@ -2844,10 +2851,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46126.3215783912</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46189</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
         <x:v>84</x:v>
@@ -2856,48 +2863,75 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46128.1824279398</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="18" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B18" s="14" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C18" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E18" s="14" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G18" s="14" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H18" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L18" s="18">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M18" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
     <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="20" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B20" s="19" t="s">
+    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="19" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C20" s="20" t="s"/>
-      <x:c r="D20" s="20" t="s"/>
-      <x:c r="E20" s="21" t="s"/>
-      <x:c r="F20" s="21" t="s"/>
+      <x:c r="C21" s="20" t="s"/>
+      <x:c r="D21" s="20" t="s"/>
+      <x:c r="E21" s="21" t="s"/>
+      <x:c r="F21" s="21" t="s"/>
     </x:row>
-    <x:row r="21" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B21" s="22" t="s">
+    <x:row r="22" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B22" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C21" s="23" t="s"/>
-      <x:c r="D21" s="23" t="s"/>
-      <x:c r="E21" s="23" t="s"/>
-      <x:c r="F21" s="24" t="s">
+      <x:c r="C22" s="23" t="s"/>
+      <x:c r="D22" s="23" t="s"/>
+      <x:c r="E22" s="23" t="s"/>
+      <x:c r="F22" s="24" t="s">
         <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B22" s="25" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C22" s="26" t="s"/>
-      <x:c r="D22" s="26" t="s"/>
-      <x:c r="E22" s="26" t="s"/>
-      <x:c r="F22" s="27" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:28" ht="18" customHeight="1">
       <x:c r="B23" s="25" t="s">
-        <x:v>63</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C23" s="26" t="s"/>
       <x:c r="D23" s="26" t="s"/>
@@ -2906,19 +2940,39 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B24" s="28" t="s">
+    <x:row r="24" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B24" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C24" s="26" t="s"/>
+      <x:c r="D24" s="26" t="s"/>
+      <x:c r="E24" s="26" t="s"/>
+      <x:c r="F24" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B25" s="25" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C25" s="26" t="s"/>
+      <x:c r="D25" s="26" t="s"/>
+      <x:c r="E25" s="26" t="s"/>
+      <x:c r="F25" s="27" t="n">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B26" s="28" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C24" s="29" t="s"/>
-      <x:c r="D24" s="29" t="s"/>
-      <x:c r="E24" s="29" t="s"/>
-      <x:c r="F24" s="30" t="n">
-        <x:v>10</x:v>
+      <x:c r="C26" s="29" t="s"/>
+      <x:c r="D26" s="29" t="s"/>
+      <x:c r="E26" s="29" t="s"/>
+      <x:c r="F26" s="30" t="n">
+        <x:v>11</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3887,15 +3941,16 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="8">
+  <x:mergeCells count="9">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B20:F20"/>
-    <x:mergeCell ref="B21:E21"/>
+    <x:mergeCell ref="B21:F21"/>
     <x:mergeCell ref="B22:E22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
+    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B26:E26"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -140,6 +140,18 @@
   </x:si>
   <x:si>
     <x:t>EMCOR INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P-3 NATIONAL HIGHWAY, POBLACION, Alubijid, Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01362</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1444-814</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518210 A</x:t>
   </x:si>
   <x:si>
     <x:t>Sta cecilia National highway, Gusa, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
@@ -2511,7 +2523,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46125.3390388079</x:v>
+        <x:v>46132.2785644329</x:v>
       </x:c>
       <x:c r="I8" s="16">
         <x:v>46135</x:v>
@@ -2523,7 +2535,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46125.3538272917</x:v>
+        <x:v>46133.1152077083</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>32</x:v>
@@ -2534,34 +2546,34 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F9" s="14" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="F9" s="14" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="G9" s="14" t="s">
+      <x:c r="H9" s="16">
+        <x:v>46125.3390388079</x:v>
+      </x:c>
+      <x:c r="I9" s="16">
+        <x:v>46135</x:v>
+      </x:c>
+      <x:c r="J9" s="15" t="s">
         <x:v>46</x:v>
-      </x:c>
-      <x:c r="H9" s="16">
-        <x:v>46128.1699027199</x:v>
-      </x:c>
-      <x:c r="I9" s="16">
-        <x:v>46136</x:v>
-      </x:c>
-      <x:c r="J9" s="15" t="s">
-        <x:v>47</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46128.349008206</x:v>
+        <x:v>46125.3538272917</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>32</x:v>
@@ -2572,34 +2584,34 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="16">
+        <x:v>46128.1699027199</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46136</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46126.2900560185</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46162</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>52</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46128.194732662</x:v>
+        <x:v>46128.349008206</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>32</x:v>
@@ -2610,34 +2622,34 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="H11" s="16">
+        <x:v>46126.2900560185</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46162</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46112.0874409838</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46134</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>32</x:v>
@@ -2648,34 +2660,34 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="H12" s="16">
+        <x:v>46112.0874409838</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46134</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46126.3116678125</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46196</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46128.191368669</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>32</x:v>
@@ -2683,35 +2695,37 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="s"/>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D13" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>28</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46120.3579437153</x:v>
+        <x:v>46126.3116678125</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46120.3579643171</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>2790</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46132.2453653241</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>32</x:v>
@@ -2719,37 +2733,35 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s"/>
+      <x:c r="E14" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="D14" s="15" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E14" s="14" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="H14" s="16">
+        <x:v>46120.3579437153</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46120.3579643171</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46105.3461754861</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46137</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>2790</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46120.2790231597</x:v>
+        <x:v>46132.2453653241</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>32</x:v>
@@ -2757,10 +2769,10 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>22</x:v>
@@ -2775,10 +2787,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46105.3461754861</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46224</x:v>
+        <x:v>46137</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
         <x:v>75</x:v>
@@ -2787,7 +2799,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46120.2790231597</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>32</x:v>
@@ -2795,37 +2807,37 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>76</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="H16" s="16">
+        <x:v>46126.2721295949</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
         <x:v>79</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46126.2873086111</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46130</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>80</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>32</x:v>
@@ -2833,10 +2845,10 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>22</x:v>
@@ -2851,10 +2863,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46198</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
         <x:v>84</x:v>
@@ -2863,7 +2875,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>32</x:v>
@@ -2871,109 +2883,146 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E18" s="14" t="s">
-        <x:v>59</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G18" s="14" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46126.3215783912</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46189</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46128.1824279398</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="19" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B19" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C19" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E19" s="14" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G19" s="14" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H19" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="K19" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L19" s="18">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M19" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
     <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="21" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B21" s="19" t="s">
+    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="19" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C21" s="20" t="s"/>
-      <x:c r="D21" s="20" t="s"/>
-      <x:c r="E21" s="21" t="s"/>
-      <x:c r="F21" s="21" t="s"/>
+      <x:c r="C22" s="20" t="s"/>
+      <x:c r="D22" s="20" t="s"/>
+      <x:c r="E22" s="21" t="s"/>
+      <x:c r="F22" s="21" t="s"/>
     </x:row>
-    <x:row r="22" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B22" s="22" t="s">
+    <x:row r="23" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B23" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C22" s="23" t="s"/>
-      <x:c r="D22" s="23" t="s"/>
-      <x:c r="E22" s="23" t="s"/>
-      <x:c r="F22" s="24" t="s">
+      <x:c r="C23" s="23" t="s"/>
+      <x:c r="D23" s="23" t="s"/>
+      <x:c r="E23" s="23" t="s"/>
+      <x:c r="F23" s="24" t="s">
         <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B23" s="25" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C23" s="26" t="s"/>
-      <x:c r="D23" s="26" t="s"/>
-      <x:c r="E23" s="26" t="s"/>
-      <x:c r="F23" s="27" t="n">
-        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:28" ht="18" customHeight="1">
       <x:c r="B24" s="25" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C24" s="26" t="s"/>
       <x:c r="D24" s="26" t="s"/>
       <x:c r="E24" s="26" t="s"/>
       <x:c r="F24" s="27" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
       <x:c r="B25" s="25" t="s">
-        <x:v>66</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C25" s="26" t="s"/>
       <x:c r="D25" s="26" t="s"/>
       <x:c r="E25" s="26" t="s"/>
       <x:c r="F25" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B26" s="25" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C26" s="26" t="s"/>
+      <x:c r="D26" s="26" t="s"/>
+      <x:c r="E26" s="26" t="s"/>
+      <x:c r="F26" s="27" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B26" s="28" t="s">
+    <x:row r="27" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B27" s="28" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C26" s="29" t="s"/>
-      <x:c r="D26" s="29" t="s"/>
-      <x:c r="E26" s="29" t="s"/>
-      <x:c r="F26" s="30" t="n">
-        <x:v>11</x:v>
+      <x:c r="C27" s="29" t="s"/>
+      <x:c r="D27" s="29" t="s"/>
+      <x:c r="E27" s="29" t="s"/>
+      <x:c r="F27" s="30" t="n">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3945,12 +3994,12 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B21:F21"/>
-    <x:mergeCell ref="B22:E22"/>
+    <x:mergeCell ref="B22:F22"/>
     <x:mergeCell ref="B23:E23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
+    <x:mergeCell ref="B27:E27"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -179,6 +179,21 @@
   </x:si>
   <x:si>
     <x:t>1518195</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMCOR, INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hannah Shangrila Bldg. Zone 1B, Iponan, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19-REDP-CAG-01364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1448-935</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518223 A</x:t>
   </x:si>
   <x:si>
     <x:t>INTERPACE CORPORATION</x:t>
@@ -2637,10 +2652,10 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46126.2900560185</x:v>
+        <x:v>46133.2374101505</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46162</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
         <x:v>56</x:v>
@@ -2649,7 +2664,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46128.194732662</x:v>
+        <x:v>46134.0815209838</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>32</x:v>
@@ -2675,19 +2690,19 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46112.0874409838</x:v>
+        <x:v>46126.2900560185</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46134</x:v>
+        <x:v>46162</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>32</x:v>
@@ -2713,19 +2728,19 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46126.3116678125</x:v>
+        <x:v>46112.0874409838</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46196</x:v>
+        <x:v>46134</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
         <x:v>66</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46128.191368669</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>32</x:v>
@@ -2733,35 +2748,37 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D14" s="15" t="s"/>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>28</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46120.3579437153</x:v>
+        <x:v>46126.3116678125</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46120.3579643171</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>2790</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46132.2453653241</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>32</x:v>
@@ -2769,37 +2786,35 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>70</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>22</x:v>
-      </x:c>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s"/>
       <x:c r="E15" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="H15" s="16">
+        <x:v>46120.3579437153</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46120.3579643171</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46105.3461754861</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46137</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>2790</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46120.2790231597</x:v>
+        <x:v>46132.2453653241</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>32</x:v>
@@ -2807,37 +2822,37 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F16" s="14" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G16" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46105.3461754861</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46224</x:v>
+        <x:v>46137</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46120.2790231597</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>32</x:v>
@@ -2845,10 +2860,10 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>80</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>22</x:v>
@@ -2863,10 +2878,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46126.2873086111</x:v>
+        <x:v>46126.2721295949</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46130</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
         <x:v>84</x:v>
@@ -2875,7 +2890,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>32</x:v>
@@ -2883,37 +2898,37 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E18" s="14" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G18" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46198</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>32</x:v>
@@ -2921,109 +2936,146 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E19" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F19" s="14" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G19" s="14" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46126.3215783912</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46189</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46128.1824279398</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="20" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B20" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F20" s="14" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G20" s="14" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H20" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I20" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="K20" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L20" s="18">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M20" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
     <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B22" s="19" t="s">
+    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="19" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C22" s="20" t="s"/>
-      <x:c r="D22" s="20" t="s"/>
-      <x:c r="E22" s="21" t="s"/>
-      <x:c r="F22" s="21" t="s"/>
-    </x:row>
-    <x:row r="23" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B23" s="22" t="s">
+      <x:c r="C23" s="20" t="s"/>
+      <x:c r="D23" s="20" t="s"/>
+      <x:c r="E23" s="21" t="s"/>
+      <x:c r="F23" s="21" t="s"/>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B24" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C23" s="23" t="s"/>
-      <x:c r="D23" s="23" t="s"/>
-      <x:c r="E23" s="23" t="s"/>
-      <x:c r="F23" s="24" t="s">
+      <x:c r="C24" s="23" t="s"/>
+      <x:c r="D24" s="23" t="s"/>
+      <x:c r="E24" s="23" t="s"/>
+      <x:c r="F24" s="24" t="s">
         <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B24" s="25" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C24" s="26" t="s"/>
-      <x:c r="D24" s="26" t="s"/>
-      <x:c r="E24" s="26" t="s"/>
-      <x:c r="F24" s="27" t="n">
-        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:28" ht="18" customHeight="1">
       <x:c r="B25" s="25" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C25" s="26" t="s"/>
       <x:c r="D25" s="26" t="s"/>
       <x:c r="E25" s="26" t="s"/>
       <x:c r="F25" s="27" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:28" ht="18" customHeight="1">
       <x:c r="B26" s="25" t="s">
-        <x:v>70</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C26" s="26" t="s"/>
       <x:c r="D26" s="26" t="s"/>
       <x:c r="E26" s="26" t="s"/>
       <x:c r="F26" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B27" s="25" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C27" s="26" t="s"/>
+      <x:c r="D27" s="26" t="s"/>
+      <x:c r="E27" s="26" t="s"/>
+      <x:c r="F27" s="27" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B27" s="28" t="s">
+    <x:row r="28" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B28" s="28" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C27" s="29" t="s"/>
-      <x:c r="D27" s="29" t="s"/>
-      <x:c r="E27" s="29" t="s"/>
-      <x:c r="F27" s="30" t="n">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C28" s="29" t="s"/>
+      <x:c r="D28" s="29" t="s"/>
+      <x:c r="E28" s="29" t="s"/>
+      <x:c r="F28" s="30" t="n">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
     <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
@@ -3994,12 +4046,12 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B22:F22"/>
-    <x:mergeCell ref="B23:E23"/>
+    <x:mergeCell ref="B23:F23"/>
     <x:mergeCell ref="B24:E24"/>
     <x:mergeCell ref="B25:E25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B28:E28"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -154,6 +154,18 @@
     <x:t>1518210 A</x:t>
   </x:si>
   <x:si>
+    <x:t>NADAL BDLG NATIONAL HIGHWAY, BARANGAY 3, Gingoog City, Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01361</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1436-764</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518230 A</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sta cecilia National highway, Gusa, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
   </x:si>
   <x:si>
@@ -278,6 +290,21 @@
   </x:si>
   <x:si>
     <x:t>1518192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIDMARK WEST, INC. - ROBINSONS VALENCIA SES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Robinson's Place, Bagontaas, City Of Valencia, Bukidnon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-18-12-410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1424-309</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518227 A</x:t>
   </x:si>
   <x:si>
     <x:t>TECHNOMART</x:t>
@@ -2576,7 +2603,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46125.3390388079</x:v>
+        <x:v>46128.2089466088</x:v>
       </x:c>
       <x:c r="I9" s="16">
         <x:v>46135</x:v>
@@ -2588,7 +2615,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46125.3538272917</x:v>
+        <x:v>46134.3002672917</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>32</x:v>
@@ -2599,34 +2626,34 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F10" s="14" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="F10" s="14" t="s">
+      <x:c r="G10" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="G10" s="14" t="s">
+      <x:c r="H10" s="16">
+        <x:v>46125.3390388079</x:v>
+      </x:c>
+      <x:c r="I10" s="16">
+        <x:v>46135</x:v>
+      </x:c>
+      <x:c r="J10" s="15" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="H10" s="16">
-        <x:v>46128.1699027199</x:v>
-      </x:c>
-      <x:c r="I10" s="16">
-        <x:v>46136</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46128.349008206</x:v>
+        <x:v>46125.3538272917</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>32</x:v>
@@ -2637,34 +2664,34 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F11" s="14" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="F11" s="14" t="s">
+      <x:c r="G11" s="14" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="G11" s="14" t="s">
+      <x:c r="H11" s="16">
+        <x:v>46128.1699027199</x:v>
+      </x:c>
+      <x:c r="I11" s="16">
+        <x:v>46136</x:v>
+      </x:c>
+      <x:c r="J11" s="15" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="H11" s="16">
-        <x:v>46133.2374101505</x:v>
-      </x:c>
-      <x:c r="I11" s="16">
-        <x:v>46135</x:v>
-      </x:c>
-      <x:c r="J11" s="15" t="s">
-        <x:v>56</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46134.0815209838</x:v>
+        <x:v>46128.349008206</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>32</x:v>
@@ -2675,34 +2702,34 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F12" s="14" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="F12" s="14" t="s">
+      <x:c r="G12" s="14" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G12" s="14" t="s">
+      <x:c r="H12" s="16">
+        <x:v>46133.2374101505</x:v>
+      </x:c>
+      <x:c r="I12" s="16">
+        <x:v>46135</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="s">
         <x:v>60</x:v>
-      </x:c>
-      <x:c r="H12" s="16">
-        <x:v>46126.2900560185</x:v>
-      </x:c>
-      <x:c r="I12" s="16">
-        <x:v>46162</x:v>
-      </x:c>
-      <x:c r="J12" s="15" t="s">
-        <x:v>61</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46128.194732662</x:v>
+        <x:v>46134.0815209838</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>32</x:v>
@@ -2713,34 +2740,34 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
+      <x:c r="H13" s="16">
+        <x:v>46126.2900560185</x:v>
+      </x:c>
+      <x:c r="I13" s="16">
+        <x:v>46162</x:v>
+      </x:c>
+      <x:c r="J13" s="15" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="H13" s="16">
-        <x:v>46112.0874409838</x:v>
-      </x:c>
-      <x:c r="I13" s="16">
-        <x:v>46134</x:v>
-      </x:c>
-      <x:c r="J13" s="15" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="K13" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>32</x:v>
@@ -2751,34 +2778,34 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="H14" s="16">
+        <x:v>46112.0874409838</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46134</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46126.3116678125</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46196</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46128.191368669</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>32</x:v>
@@ -2786,35 +2813,37 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D15" s="15" t="s"/>
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>28</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46120.3579437153</x:v>
+        <x:v>46126.3116678125</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46120.3579643171</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>2790</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46132.2453653241</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>32</x:v>
@@ -2822,37 +2851,35 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>75</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s"/>
+      <x:c r="E16" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="H16" s="16">
+        <x:v>46120.3579437153</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46120.3579643171</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46105.3461754861</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46137</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="K16" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>2790</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46120.2790231597</x:v>
+        <x:v>46132.2453653241</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>32</x:v>
@@ -2860,10 +2887,10 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>57</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>22</x:v>
@@ -2878,10 +2905,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46105.3461754861</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46224</x:v>
+        <x:v>46137</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
         <x:v>84</x:v>
@@ -2890,7 +2917,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46120.2790231597</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>32</x:v>
@@ -2898,37 +2925,37 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>85</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E18" s="14" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="s">
+      <x:c r="H18" s="16">
+        <x:v>46126.2721295949</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
         <x:v>88</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46126.2873086111</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46130</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>89</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>32</x:v>
@@ -2936,10 +2963,10 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
         <x:v>22</x:v>
@@ -2954,10 +2981,10 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46125.335903912</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46198</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
         <x:v>93</x:v>
@@ -2966,7 +2993,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46134.2685065741</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>32</x:v>
@@ -2974,110 +3001,184 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E20" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F20" s="14" t="s">
-        <x:v>94</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G20" s="14" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>46189</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="22" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="23" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B23" s="19" t="s">
+    <x:row r="21" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B21" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C21" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E21" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G21" s="14" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H21" s="16">
+        <x:v>46126.3215783912</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46198</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="K21" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L21" s="18">
+        <x:v>46128.1824279398</x:v>
+      </x:c>
+      <x:c r="M21" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B22" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="H22" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="K22" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L22" s="18">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B25" s="19" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C23" s="20" t="s"/>
-      <x:c r="D23" s="20" t="s"/>
-      <x:c r="E23" s="21" t="s"/>
-      <x:c r="F23" s="21" t="s"/>
-    </x:row>
-    <x:row r="24" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B24" s="22" t="s">
+      <x:c r="C25" s="20" t="s"/>
+      <x:c r="D25" s="20" t="s"/>
+      <x:c r="E25" s="21" t="s"/>
+      <x:c r="F25" s="21" t="s"/>
+    </x:row>
+    <x:row r="26" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B26" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C24" s="23" t="s"/>
-      <x:c r="D24" s="23" t="s"/>
-      <x:c r="E24" s="23" t="s"/>
-      <x:c r="F24" s="24" t="s">
+      <x:c r="C26" s="23" t="s"/>
+      <x:c r="D26" s="23" t="s"/>
+      <x:c r="E26" s="23" t="s"/>
+      <x:c r="F26" s="24" t="s">
         <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B25" s="25" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C25" s="26" t="s"/>
-      <x:c r="D25" s="26" t="s"/>
-      <x:c r="E25" s="26" t="s"/>
-      <x:c r="F25" s="27" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B26" s="25" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C26" s="26" t="s"/>
-      <x:c r="D26" s="26" t="s"/>
-      <x:c r="E26" s="26" t="s"/>
-      <x:c r="F26" s="27" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:28" ht="18" customHeight="1">
       <x:c r="B27" s="25" t="s">
-        <x:v>75</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C27" s="26" t="s"/>
       <x:c r="D27" s="26" t="s"/>
       <x:c r="E27" s="26" t="s"/>
       <x:c r="F27" s="27" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B28" s="28" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B28" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C28" s="26" t="s"/>
+      <x:c r="D28" s="26" t="s"/>
+      <x:c r="E28" s="26" t="s"/>
+      <x:c r="F28" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B29" s="25" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C29" s="26" t="s"/>
+      <x:c r="D29" s="26" t="s"/>
+      <x:c r="E29" s="26" t="s"/>
+      <x:c r="F29" s="27" t="n">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B30" s="28" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C28" s="29" t="s"/>
-      <x:c r="D28" s="29" t="s"/>
-      <x:c r="E28" s="29" t="s"/>
-      <x:c r="F28" s="30" t="n">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C30" s="29" t="s"/>
+      <x:c r="D30" s="29" t="s"/>
+      <x:c r="E30" s="29" t="s"/>
+      <x:c r="F30" s="30" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4046,12 +4147,12 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B23:F23"/>
-    <x:mergeCell ref="B24:E24"/>
-    <x:mergeCell ref="B25:E25"/>
+    <x:mergeCell ref="B25:F25"/>
     <x:mergeCell ref="B26:E26"/>
     <x:mergeCell ref="B27:E27"/>
     <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B29:E29"/>
+    <x:mergeCell ref="B30:E30"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -178,6 +178,21 @@
     <x:t>1518175</x:t>
   </x:si>
   <x:si>
+    <x:t>EMCOR INC.  (BALINGASAG BRANCH)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quezon Osmena Street, Barangay 6 Poblacion, Balingasag, Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01360</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1451-946</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518246 A</x:t>
+  </x:si>
+  <x:si>
     <x:t>EMCOR INCORPORATED</x:t>
   </x:si>
   <x:si>
@@ -221,6 +236,21 @@
   </x:si>
   <x:si>
     <x:t>1518191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORO GADGETS INC. (GRAPHIC GADGET STORES)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3E-1 THIRD LEVEL GAISANO PUERTO, PUERTO, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MP-17-04-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1446-993</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518243 A</x:t>
   </x:si>
   <x:si>
     <x:t>SOLIDMARK WEST, INC.</x:t>
@@ -2679,10 +2709,10 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46128.1699027199</x:v>
+        <x:v>46135.0684019213</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46136</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
         <x:v>55</x:v>
@@ -2691,7 +2721,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46128.349008206</x:v>
+        <x:v>46135.1975182523</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>32</x:v>
@@ -2717,10 +2747,10 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46133.2374101505</x:v>
+        <x:v>46128.1699027199</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46135</x:v>
+        <x:v>46136</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
         <x:v>60</x:v>
@@ -2729,7 +2759,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46134.0815209838</x:v>
+        <x:v>46128.349008206</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>32</x:v>
@@ -2755,10 +2785,10 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46126.2900560185</x:v>
+        <x:v>46133.2374101505</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46162</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
         <x:v>65</x:v>
@@ -2767,7 +2797,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46128.194732662</x:v>
+        <x:v>46134.0815209838</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>32</x:v>
@@ -2793,19 +2823,19 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46112.0874409838</x:v>
+        <x:v>46126.2900560185</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46134</x:v>
+        <x:v>46162</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>32</x:v>
@@ -2831,19 +2861,19 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46126.3116678125</x:v>
+        <x:v>46132.3880687384</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46196</x:v>
+        <x:v>46138</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
         <x:v>75</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46128.191368669</x:v>
+        <x:v>46135.1691307292</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>32</x:v>
@@ -2851,35 +2881,37 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D16" s="15" t="s"/>
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="E16" s="14" t="s">
-        <x:v>28</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F16" s="14" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G16" s="14" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46120.3579437153</x:v>
+        <x:v>46112.0874409838</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46120.3579643171</x:v>
+        <x:v>46134</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
-        <x:v>2790</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46132.2453653241</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>32</x:v>
@@ -2887,37 +2919,37 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>79</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G17" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46105.3461754861</x:v>
+        <x:v>46126.3116678125</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46137</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46120.2790231597</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>32</x:v>
@@ -2925,16 +2957,14 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>79</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>22</x:v>
-      </x:c>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s"/>
       <x:c r="E18" s="14" t="s">
-        <x:v>85</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
         <x:v>86</x:v>
@@ -2943,19 +2973,19 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46120.3579437153</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46224</x:v>
+        <x:v>46120.3579643171</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
         <x:v>88</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>2790</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46132.2453653241</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>32</x:v>
@@ -2963,37 +2993,37 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>79</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E19" s="14" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F19" s="14" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G19" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46125.335903912</x:v>
+        <x:v>46105.3461754861</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46203</x:v>
+        <x:v>46137</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46134.2685065741</x:v>
+        <x:v>46120.2790231597</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>32</x:v>
@@ -3001,10 +3031,10 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
-        <x:v>79</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>94</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
         <x:v>22</x:v>
@@ -3019,10 +3049,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46126.2873086111</x:v>
+        <x:v>46126.2721295949</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>46130</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
         <x:v>98</x:v>
@@ -3031,7 +3061,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
         <x:v>32</x:v>
@@ -3039,37 +3069,37 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
-        <x:v>79</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>71</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E21" s="14" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F21" s="14" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G21" s="14" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46125.335903912</x:v>
       </x:c>
       <x:c r="I21" s="16">
-        <x:v>46198</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="J21" s="15" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46134.2685065741</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>32</x:v>
@@ -3077,110 +3107,184 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
-        <x:v>79</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>71</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E22" s="14" t="s">
-        <x:v>72</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="G22" s="14" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I22" s="16">
-        <x:v>46189</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="24" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="25" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B25" s="19" t="s">
+    <x:row r="23" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B23" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C23" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="H23" s="16">
+        <x:v>46126.3215783912</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
+        <x:v>46198</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="K23" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L23" s="18">
+        <x:v>46128.1824279398</x:v>
+      </x:c>
+      <x:c r="M23" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B24" s="14" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H24" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I24" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="K24" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L24" s="18">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M24" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="19" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C25" s="20" t="s"/>
-      <x:c r="D25" s="20" t="s"/>
-      <x:c r="E25" s="21" t="s"/>
-      <x:c r="F25" s="21" t="s"/>
-    </x:row>
-    <x:row r="26" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B26" s="22" t="s">
+      <x:c r="C27" s="20" t="s"/>
+      <x:c r="D27" s="20" t="s"/>
+      <x:c r="E27" s="21" t="s"/>
+      <x:c r="F27" s="21" t="s"/>
+    </x:row>
+    <x:row r="28" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B28" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C26" s="23" t="s"/>
-      <x:c r="D26" s="23" t="s"/>
-      <x:c r="E26" s="23" t="s"/>
-      <x:c r="F26" s="24" t="s">
+      <x:c r="C28" s="23" t="s"/>
+      <x:c r="D28" s="23" t="s"/>
+      <x:c r="E28" s="23" t="s"/>
+      <x:c r="F28" s="24" t="s">
         <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B27" s="25" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C27" s="26" t="s"/>
-      <x:c r="D27" s="26" t="s"/>
-      <x:c r="E27" s="26" t="s"/>
-      <x:c r="F27" s="27" t="n">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B28" s="25" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C28" s="26" t="s"/>
-      <x:c r="D28" s="26" t="s"/>
-      <x:c r="E28" s="26" t="s"/>
-      <x:c r="F28" s="27" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:28" ht="18" customHeight="1">
       <x:c r="B29" s="25" t="s">
-        <x:v>79</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C29" s="26" t="s"/>
       <x:c r="D29" s="26" t="s"/>
       <x:c r="E29" s="26" t="s"/>
       <x:c r="F29" s="27" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B30" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C30" s="26" t="s"/>
+      <x:c r="D30" s="26" t="s"/>
+      <x:c r="E30" s="26" t="s"/>
+      <x:c r="F30" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B31" s="25" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C31" s="26" t="s"/>
+      <x:c r="D31" s="26" t="s"/>
+      <x:c r="E31" s="26" t="s"/>
+      <x:c r="F31" s="27" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B30" s="28" t="s">
+    <x:row r="32" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B32" s="28" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C30" s="29" t="s"/>
-      <x:c r="D30" s="29" t="s"/>
-      <x:c r="E30" s="29" t="s"/>
-      <x:c r="F30" s="30" t="n">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C32" s="29" t="s"/>
+      <x:c r="D32" s="29" t="s"/>
+      <x:c r="E32" s="29" t="s"/>
+      <x:c r="F32" s="30" t="n">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
     <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4147,12 +4251,12 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B25:F25"/>
-    <x:mergeCell ref="B26:E26"/>
-    <x:mergeCell ref="B27:E27"/>
+    <x:mergeCell ref="B27:F27"/>
     <x:mergeCell ref="B28:E28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
+    <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B32:E32"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -142,6 +142,18 @@
     <x:t>EMCOR INC</x:t>
   </x:si>
   <x:si>
+    <x:t>Sta cecilia National highway, Gusa, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01359</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1425-830</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518175</x:t>
+  </x:si>
+  <x:si>
     <x:t>P-3 NATIONAL HIGHWAY, POBLACION, Alubijid, Misamis Oriental</x:t>
   </x:si>
   <x:si>
@@ -166,18 +178,6 @@
     <x:t>1518230 A</x:t>
   </x:si>
   <x:si>
-    <x:t>Sta cecilia National highway, Gusa, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18-REDP-CAG-01359</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1425-830</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518175</x:t>
-  </x:si>
-  <x:si>
     <x:t>EMCOR INC.  (BALINGASAG BRANCH)</x:t>
   </x:si>
   <x:si>
@@ -281,6 +281,18 @@
   </x:si>
   <x:si>
     <x:t>1518189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Permit to POSSESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/POS-JJ-00048-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1450-116</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518256 A</x:t>
   </x:si>
   <x:si>
     <x:t>P/PUR-JJ-00018-26</x:t>
@@ -2595,7 +2607,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46132.2785644329</x:v>
+        <x:v>46125.3390388079</x:v>
       </x:c>
       <x:c r="I8" s="16">
         <x:v>46135</x:v>
@@ -2607,7 +2619,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46133.1152077083</x:v>
+        <x:v>46125.3538272917</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>32</x:v>
@@ -2633,7 +2645,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46128.2089466088</x:v>
+        <x:v>46132.2785644329</x:v>
       </x:c>
       <x:c r="I9" s="16">
         <x:v>46135</x:v>
@@ -2645,7 +2657,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46134.3002672917</x:v>
+        <x:v>46133.1152077083</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>32</x:v>
@@ -2671,7 +2683,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46125.3390388079</x:v>
+        <x:v>46128.2089466088</x:v>
       </x:c>
       <x:c r="I10" s="16">
         <x:v>46135</x:v>
@@ -2683,7 +2695,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46125.3538272917</x:v>
+        <x:v>46134.3002672917</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>32</x:v>
@@ -2957,7 +2969,7 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
         <x:v>27</x:v>
@@ -2967,25 +2979,25 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G18" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46120.3579437153</x:v>
+        <x:v>46134.1206595602</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46120.3579643171</x:v>
+        <x:v>46134.1206809375</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
-        <x:v>2790</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46132.2453653241</x:v>
+        <x:v>46139.1576734144</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>32</x:v>
@@ -2993,37 +3005,35 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>89</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s"/>
+      <x:c r="E19" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D19" s="15" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E19" s="14" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="s">
+      <x:c r="H19" s="16">
+        <x:v>46120.3579437153</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>46120.3579643171</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="G19" s="14" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46105.3461754861</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>46137</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="K19" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>2790</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46120.2790231597</x:v>
+        <x:v>46132.2453653241</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>32</x:v>
@@ -3031,10 +3041,10 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
         <x:v>22</x:v>
@@ -3049,10 +3059,10 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46105.3461754861</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>46224</x:v>
+        <x:v>46137</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
         <x:v>98</x:v>
@@ -3061,7 +3071,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46120.2790231597</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
         <x:v>32</x:v>
@@ -3069,37 +3079,37 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>99</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D21" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E21" s="14" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="s">
+      <x:c r="G21" s="14" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="G21" s="14" t="s">
+      <x:c r="H21" s="16">
+        <x:v>46126.2721295949</x:v>
+      </x:c>
+      <x:c r="I21" s="16">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="s">
         <x:v>102</x:v>
-      </x:c>
-      <x:c r="H21" s="16">
-        <x:v>46125.335903912</x:v>
-      </x:c>
-      <x:c r="I21" s="16">
-        <x:v>46203</x:v>
-      </x:c>
-      <x:c r="J21" s="15" t="s">
-        <x:v>103</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46134.2685065741</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>32</x:v>
@@ -3107,37 +3117,37 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>104</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E22" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="s">
+      <x:c r="G22" s="14" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="G22" s="14" t="s">
+      <x:c r="H22" s="16">
+        <x:v>46125.335903912</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46203</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="s">
         <x:v>107</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46126.2873086111</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46130</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="s">
-        <x:v>108</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46134.2685065741</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
         <x:v>32</x:v>
@@ -3145,10 +3155,10 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>81</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
         <x:v>22</x:v>
@@ -3163,10 +3173,10 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I23" s="16">
-        <x:v>46198</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
         <x:v>112</x:v>
@@ -3175,7 +3185,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>32</x:v>
@@ -3183,7 +3193,7 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
-        <x:v>89</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
         <x:v>81</x:v>
@@ -3192,101 +3202,148 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="E24" s="14" t="s">
-        <x:v>82</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F24" s="14" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G24" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46126.3215783912</x:v>
       </x:c>
       <x:c r="I24" s="16">
-        <x:v>46189</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="J24" s="15" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="K24" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46128.1824279398</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="25" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B25" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C25" s="14" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E25" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="G25" s="14" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="H25" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I25" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="K25" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L25" s="18">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M25" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
     <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B27" s="19" t="s">
+    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="28" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B28" s="19" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C27" s="20" t="s"/>
-      <x:c r="D27" s="20" t="s"/>
-      <x:c r="E27" s="21" t="s"/>
-      <x:c r="F27" s="21" t="s"/>
-    </x:row>
-    <x:row r="28" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B28" s="22" t="s">
+      <x:c r="C28" s="20" t="s"/>
+      <x:c r="D28" s="20" t="s"/>
+      <x:c r="E28" s="21" t="s"/>
+      <x:c r="F28" s="21" t="s"/>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B29" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C28" s="23" t="s"/>
-      <x:c r="D28" s="23" t="s"/>
-      <x:c r="E28" s="23" t="s"/>
-      <x:c r="F28" s="24" t="s">
+      <x:c r="C29" s="23" t="s"/>
+      <x:c r="D29" s="23" t="s"/>
+      <x:c r="E29" s="23" t="s"/>
+      <x:c r="F29" s="24" t="s">
         <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B29" s="25" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C29" s="26" t="s"/>
-      <x:c r="D29" s="26" t="s"/>
-      <x:c r="E29" s="26" t="s"/>
-      <x:c r="F29" s="27" t="n">
-        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:28" ht="18" customHeight="1">
       <x:c r="B30" s="25" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C30" s="26" t="s"/>
       <x:c r="D30" s="26" t="s"/>
       <x:c r="E30" s="26" t="s"/>
       <x:c r="F30" s="27" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:28" ht="18" customHeight="1">
       <x:c r="B31" s="25" t="s">
-        <x:v>89</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C31" s="26" t="s"/>
       <x:c r="D31" s="26" t="s"/>
       <x:c r="E31" s="26" t="s"/>
       <x:c r="F31" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B32" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C32" s="26" t="s"/>
+      <x:c r="D32" s="26" t="s"/>
+      <x:c r="E32" s="26" t="s"/>
+      <x:c r="F32" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B33" s="25" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C33" s="26" t="s"/>
+      <x:c r="D33" s="26" t="s"/>
+      <x:c r="E33" s="26" t="s"/>
+      <x:c r="F33" s="27" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B32" s="28" t="s">
+    <x:row r="34" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B34" s="28" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C32" s="29" t="s"/>
-      <x:c r="D32" s="29" t="s"/>
-      <x:c r="E32" s="29" t="s"/>
-      <x:c r="F32" s="30" t="n">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="34" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C34" s="29" t="s"/>
+      <x:c r="D34" s="29" t="s"/>
+      <x:c r="E34" s="29" t="s"/>
+      <x:c r="F34" s="30" t="n">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
     <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4247,16 +4304,17 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="9">
+  <x:mergeCells count="10">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B27:F27"/>
-    <x:mergeCell ref="B28:E28"/>
+    <x:mergeCell ref="B28:F28"/>
     <x:mergeCell ref="B29:E29"/>
     <x:mergeCell ref="B30:E30"/>
     <x:mergeCell ref="B31:E31"/>
     <x:mergeCell ref="B32:E32"/>
+    <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B34:E34"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -136,12 +136,69 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>Dealer Permit (NEW)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CELLTY MOBILE INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAISANO TUBOD,PABLACION,TUBOD LANAO DEL NORTE, POBLACION, Tubod (Capital), Lanao Del Norte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MPDP-ROX-08615-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1445-013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518266 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LAPTAP ENTERPRISES, INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2F, Lifestyle District Corrales Ext, Brgy. 23, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MP-ROX-08533-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1439-984</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518270 A</x:t>
+  </x:si>
+  <x:si>
     <x:t>Dealer Permit (RENEWAL)</x:t>
   </x:si>
   <x:si>
     <x:t>EMCOR INC</x:t>
   </x:si>
   <x:si>
+    <x:t>P-3 NATIONAL HIGHWAY, POBLACION, Alubijid, Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01362</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1444-814</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518210 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NADAL BDLG NATIONAL HIGHWAY, BARANGAY 3, Gingoog City, Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01361</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1436-764</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518230 A</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sta cecilia National highway, Gusa, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
   </x:si>
   <x:si>
@@ -154,30 +211,6 @@
     <x:t>1518175</x:t>
   </x:si>
   <x:si>
-    <x:t>P-3 NATIONAL HIGHWAY, POBLACION, Alubijid, Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18-REDP-CAG-01362</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1444-814</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518210 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NADAL BDLG NATIONAL HIGHWAY, BARANGAY 3, Gingoog City, Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18-REDP-CAG-01361</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1436-764</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518230 A</x:t>
-  </x:si>
-  <x:si>
     <x:t>EMCOR INC.  (BALINGASAG BRANCH)</x:t>
   </x:si>
   <x:si>
@@ -322,6 +355,21 @@
     <x:t>1518165</x:t>
   </x:si>
   <x:si>
+    <x:t>HO TSAYKI INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T-29 &amp; T-30 citymall bulua, Bulua, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-19-05-425</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1449-395</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518265 A</x:t>
+  </x:si>
+  <x:si>
     <x:t>WEST WING LKKS CENTER, Barangay 31, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
   </x:si>
   <x:si>
@@ -364,6 +412,15 @@
     <x:t>1518180</x:t>
   </x:si>
   <x:si>
+    <x:t>ROX-MRR-10-06-128</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1431-363</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518190</x:t>
+  </x:si>
+  <x:si>
     <x:t>FORTICH STREET, Barangay 04, City Of Malaybalay (Capital), Bukidnon</x:t>
   </x:si>
   <x:si>
@@ -374,15 +431,6 @@
   </x:si>
   <x:si>
     <x:t>1518188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MRR-10-06-128</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1431-363</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518190</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2595,7 +2643,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="D8" s="15" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E8" s="14" t="s">
         <x:v>39</x:v>
@@ -2607,19 +2655,19 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46125.3390388079</x:v>
+        <x:v>46132.313701713</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46135</x:v>
+        <x:v>46132.3137205208</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46125.3538272917</x:v>
+        <x:v>46139.230364294</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>32</x:v>
@@ -2630,34 +2678,34 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46132.2785644329</x:v>
+        <x:v>46129.4086055787</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46135</x:v>
+        <x:v>46129.4086256481</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>2130</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46133.1152077083</x:v>
+        <x:v>46139.3272522222</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>32</x:v>
@@ -2665,37 +2713,37 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F10" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G10" s="14" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46128.2089466088</x:v>
+        <x:v>46132.2785644329</x:v>
       </x:c>
       <x:c r="I10" s="16">
         <x:v>46135</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
-        <x:v>50</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K10" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46134.3002672917</x:v>
+        <x:v>46133.1152077083</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>32</x:v>
@@ -2703,37 +2751,37 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>51</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46135.0684019213</x:v>
+        <x:v>46128.2089466088</x:v>
       </x:c>
       <x:c r="I11" s="16">
         <x:v>46135</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46135.1975182523</x:v>
+        <x:v>46134.3002672917</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>32</x:v>
@@ -2741,37 +2789,37 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46128.1699027199</x:v>
+        <x:v>46125.3390388079</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46136</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46128.349008206</x:v>
+        <x:v>46125.3538272917</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>32</x:v>
@@ -2779,37 +2827,37 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46133.2374101505</x:v>
+        <x:v>46135.0684019213</x:v>
       </x:c>
       <x:c r="I13" s="16">
         <x:v>46135</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46134.0815209838</x:v>
+        <x:v>46135.1975182523</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>32</x:v>
@@ -2817,37 +2865,37 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F14" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G14" s="14" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H14" s="16">
-        <x:v>46126.2900560185</x:v>
+        <x:v>46128.1699027199</x:v>
       </x:c>
       <x:c r="I14" s="16">
-        <x:v>46162</x:v>
+        <x:v>46136</x:v>
       </x:c>
       <x:c r="J14" s="15" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46128.194732662</x:v>
+        <x:v>46128.349008206</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>32</x:v>
@@ -2855,37 +2903,37 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H15" s="16">
-        <x:v>46132.3880687384</x:v>
+        <x:v>46133.2374101505</x:v>
       </x:c>
       <x:c r="I15" s="16">
-        <x:v>46138</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J15" s="15" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46135.1691307292</x:v>
+        <x:v>46134.0815209838</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>32</x:v>
@@ -2893,37 +2941,37 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F16" s="14" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G16" s="14" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H16" s="16">
-        <x:v>46112.0874409838</x:v>
+        <x:v>46126.2900560185</x:v>
       </x:c>
       <x:c r="I16" s="16">
-        <x:v>46134</x:v>
+        <x:v>46162</x:v>
       </x:c>
       <x:c r="J16" s="15" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>32</x:v>
@@ -2931,37 +2979,37 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F17" s="14" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G17" s="14" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="H17" s="16">
-        <x:v>46126.3116678125</x:v>
+        <x:v>46132.3880687384</x:v>
       </x:c>
       <x:c r="I17" s="16">
-        <x:v>46196</x:v>
+        <x:v>46138</x:v>
       </x:c>
       <x:c r="J17" s="15" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46128.191368669</x:v>
+        <x:v>46135.1691307292</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>32</x:v>
@@ -2969,35 +3017,37 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>86</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s"/>
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="E18" s="14" t="s">
-        <x:v>28</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G18" s="14" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46134.1206595602</x:v>
+        <x:v>46112.0874409838</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46134.1206809375</x:v>
+        <x:v>46134</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
-        <x:v>630</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46139.1576734144</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>32</x:v>
@@ -3005,35 +3055,37 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D19" s="15" t="s"/>
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="E19" s="14" t="s">
-        <x:v>28</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F19" s="14" t="s">
-        <x:v>90</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G19" s="14" t="s">
-        <x:v>91</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46120.3579437153</x:v>
+        <x:v>46126.3116678125</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46120.3579643171</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
-        <x:v>2790</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46132.2453653241</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>32</x:v>
@@ -3041,37 +3093,35 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s">
-        <x:v>22</x:v>
-      </x:c>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s"/>
       <x:c r="E20" s="14" t="s">
-        <x:v>95</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F20" s="14" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G20" s="14" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46105.3461754861</x:v>
+        <x:v>46134.1206595602</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>46137</x:v>
+        <x:v>46134.1206809375</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46120.2790231597</x:v>
+        <x:v>46139.1576734144</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
         <x:v>32</x:v>
@@ -3079,37 +3129,35 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s">
-        <x:v>22</x:v>
-      </x:c>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s"/>
       <x:c r="E21" s="14" t="s">
-        <x:v>99</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F21" s="14" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G21" s="14" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46120.3579437153</x:v>
       </x:c>
       <x:c r="I21" s="16">
-        <x:v>46224</x:v>
+        <x:v>46120.3579643171</x:v>
       </x:c>
       <x:c r="J21" s="15" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>2790</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46132.2453653241</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>32</x:v>
@@ -3117,37 +3165,37 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D22" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E22" s="14" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
-        <x:v>105</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G22" s="14" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46125.335903912</x:v>
+        <x:v>46105.3461754861</x:v>
       </x:c>
       <x:c r="I22" s="16">
-        <x:v>46203</x:v>
+        <x:v>46137</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46134.2685065741</x:v>
+        <x:v>46120.2790231597</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
         <x:v>32</x:v>
@@ -3155,37 +3203,37 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="F23" s="14" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G23" s="14" t="s">
-        <x:v>111</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46126.2873086111</x:v>
+        <x:v>46134.0293580208</x:v>
       </x:c>
       <x:c r="I23" s="16">
-        <x:v>46130</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
-        <x:v>112</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46139.2265670718</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>32</x:v>
@@ -3193,37 +3241,37 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E24" s="14" t="s">
-        <x:v>113</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F24" s="14" t="s">
-        <x:v>114</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G24" s="14" t="s">
-        <x:v>115</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46126.2721295949</x:v>
       </x:c>
       <x:c r="I24" s="16">
-        <x:v>46198</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="J24" s="15" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="K24" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
         <x:v>32</x:v>
@@ -3231,123 +3279,244 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>81</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E25" s="14" t="s">
-        <x:v>82</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F25" s="14" t="s">
-        <x:v>117</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G25" s="14" t="s">
-        <x:v>118</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H25" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46125.335903912</x:v>
       </x:c>
       <x:c r="I25" s="16">
-        <x:v>46189</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="J25" s="15" t="s">
-        <x:v>119</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="K25" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46134.2685065741</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="27" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="26" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B26" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C26" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E26" s="14" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="G26" s="14" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H26" s="16">
+        <x:v>46126.2873086111</x:v>
+      </x:c>
+      <x:c r="I26" s="16">
+        <x:v>46130</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="K26" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L26" s="18">
+        <x:v>46127.0949605556</x:v>
+      </x:c>
+      <x:c r="M26" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B27" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C27" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E27" s="14" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="F27" s="14" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G27" s="14" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="H27" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I27" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J27" s="15" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="K27" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L27" s="18">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M27" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B28" s="19" t="s">
+      <x:c r="B28" s="14" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C28" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E28" s="14" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="F28" s="14" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="G28" s="14" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="H28" s="16">
+        <x:v>46126.3215783912</x:v>
+      </x:c>
+      <x:c r="I28" s="16">
+        <x:v>46198</x:v>
+      </x:c>
+      <x:c r="J28" s="15" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="K28" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L28" s="18">
+        <x:v>46128.1824279398</x:v>
+      </x:c>
+      <x:c r="M28" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="31" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B31" s="19" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C28" s="20" t="s"/>
-      <x:c r="D28" s="20" t="s"/>
-      <x:c r="E28" s="21" t="s"/>
-      <x:c r="F28" s="21" t="s"/>
-    </x:row>
-    <x:row r="29" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B29" s="22" t="s">
+      <x:c r="C31" s="20" t="s"/>
+      <x:c r="D31" s="20" t="s"/>
+      <x:c r="E31" s="21" t="s"/>
+      <x:c r="F31" s="21" t="s"/>
+    </x:row>
+    <x:row r="32" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B32" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C29" s="23" t="s"/>
-      <x:c r="D29" s="23" t="s"/>
-      <x:c r="E29" s="23" t="s"/>
-      <x:c r="F29" s="24" t="s">
+      <x:c r="C32" s="23" t="s"/>
+      <x:c r="D32" s="23" t="s"/>
+      <x:c r="E32" s="23" t="s"/>
+      <x:c r="F32" s="24" t="s">
         <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B30" s="25" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C30" s="26" t="s"/>
-      <x:c r="D30" s="26" t="s"/>
-      <x:c r="E30" s="26" t="s"/>
-      <x:c r="F30" s="27" t="n">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B31" s="25" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C31" s="26" t="s"/>
-      <x:c r="D31" s="26" t="s"/>
-      <x:c r="E31" s="26" t="s"/>
-      <x:c r="F31" s="27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B32" s="25" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C32" s="26" t="s"/>
-      <x:c r="D32" s="26" t="s"/>
-      <x:c r="E32" s="26" t="s"/>
-      <x:c r="F32" s="27" t="n">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:28" ht="18" customHeight="1">
       <x:c r="B33" s="25" t="s">
-        <x:v>93</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C33" s="26" t="s"/>
       <x:c r="D33" s="26" t="s"/>
       <x:c r="E33" s="26" t="s"/>
       <x:c r="F33" s="27" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B34" s="28" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B34" s="25" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C34" s="26" t="s"/>
+      <x:c r="D34" s="26" t="s"/>
+      <x:c r="E34" s="26" t="s"/>
+      <x:c r="F34" s="27" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B35" s="25" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="C35" s="26" t="s"/>
+      <x:c r="D35" s="26" t="s"/>
+      <x:c r="E35" s="26" t="s"/>
+      <x:c r="F35" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B36" s="25" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C36" s="26" t="s"/>
+      <x:c r="D36" s="26" t="s"/>
+      <x:c r="E36" s="26" t="s"/>
+      <x:c r="F36" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B37" s="25" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C37" s="26" t="s"/>
+      <x:c r="D37" s="26" t="s"/>
+      <x:c r="E37" s="26" t="s"/>
+      <x:c r="F37" s="27" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B38" s="28" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C34" s="29" t="s"/>
-      <x:c r="D34" s="29" t="s"/>
-      <x:c r="E34" s="29" t="s"/>
-      <x:c r="F34" s="30" t="n">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="36" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="37" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="38" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C38" s="29" t="s"/>
+      <x:c r="D38" s="29" t="s"/>
+      <x:c r="E38" s="29" t="s"/>
+      <x:c r="F38" s="30" t="n">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
     <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4304,17 +4473,18 @@
     <x:row r="992" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="993" spans="1:28" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:mergeCells count="10">
+  <x:mergeCells count="11">
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B28:F28"/>
-    <x:mergeCell ref="B29:E29"/>
-    <x:mergeCell ref="B30:E30"/>
-    <x:mergeCell ref="B31:E31"/>
+    <x:mergeCell ref="B31:F31"/>
     <x:mergeCell ref="B32:E32"/>
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
+    <x:mergeCell ref="B35:E35"/>
+    <x:mergeCell ref="B36:E36"/>
+    <x:mergeCell ref="B37:E37"/>
+    <x:mergeCell ref="B38:E38"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -175,6 +175,42 @@
     <x:t>EMCOR INC</x:t>
   </x:si>
   <x:si>
+    <x:t>RIZAL AVENUE, 50TH DISTRICT, Ozamis City, Misamis Occidental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01370</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1452-386</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518271 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sta cecilia National highway, Gusa, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01359</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1425-830</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NADAL BDLG NATIONAL HIGHWAY, BARANGAY 3, Gingoog City, Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01361</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1436-764</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518230 A</x:t>
+  </x:si>
+  <x:si>
     <x:t>P-3 NATIONAL HIGHWAY, POBLACION, Alubijid, Misamis Oriental</x:t>
   </x:si>
   <x:si>
@@ -187,30 +223,6 @@
     <x:t>1518210 A</x:t>
   </x:si>
   <x:si>
-    <x:t>NADAL BDLG NATIONAL HIGHWAY, BARANGAY 3, Gingoog City, Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18-REDP-CAG-01361</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1436-764</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518230 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sta cecilia National highway, Gusa, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18-REDP-CAG-01359</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1425-830</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518175</x:t>
-  </x:si>
-  <x:si>
     <x:t>EMCOR INC.  (BALINGASAG BRANCH)</x:t>
   </x:si>
   <x:si>
@@ -412,6 +424,18 @@
     <x:t>1518180</x:t>
   </x:si>
   <x:si>
+    <x:t>FORTICH STREET, Barangay 04, City Of Malaybalay (Capital), Bukidnon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-13-06-152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1433-178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518188</x:t>
+  </x:si>
+  <x:si>
     <x:t>ROX-MRR-10-06-128</x:t>
   </x:si>
   <x:si>
@@ -419,18 +443,6 @@
   </x:si>
   <x:si>
     <x:t>1518190</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTICH STREET, Barangay 04, City Of Malaybalay (Capital), Bukidnon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MRR-13-06-152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1433-178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518188</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2731,10 +2743,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46132.2785644329</x:v>
+        <x:v>46137.0314533796</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46135</x:v>
+        <x:v>46149</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
         <x:v>53</x:v>
@@ -2743,7 +2755,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46133.1152077083</x:v>
+        <x:v>46139.3366940046</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>32</x:v>
@@ -2769,7 +2781,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46128.2089466088</x:v>
+        <x:v>46125.3390388079</x:v>
       </x:c>
       <x:c r="I11" s="16">
         <x:v>46135</x:v>
@@ -2781,7 +2793,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46134.3002672917</x:v>
+        <x:v>46125.3538272917</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>32</x:v>
@@ -2807,7 +2819,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46125.3390388079</x:v>
+        <x:v>46128.2089466088</x:v>
       </x:c>
       <x:c r="I12" s="16">
         <x:v>46135</x:v>
@@ -2819,7 +2831,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46125.3538272917</x:v>
+        <x:v>46134.3002672917</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>32</x:v>
@@ -2830,34 +2842,34 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="s">
+      <x:c r="G13" s="14" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="G13" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="H13" s="16">
-        <x:v>46135.0684019213</x:v>
+        <x:v>46132.2785644329</x:v>
       </x:c>
       <x:c r="I13" s="16">
         <x:v>46135</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46135.1975182523</x:v>
+        <x:v>46133.1152077083</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>32</x:v>
@@ -2868,34 +2880,34 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>67</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="H14" s="16">
+        <x:v>46135.0684019213</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46135</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46128.1699027199</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46136</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>71</x:v>
       </x:c>
       <x:c r="K14" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46128.349008206</x:v>
+        <x:v>46135.1975182523</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>32</x:v>
@@ -2906,34 +2918,34 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D15" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="G15" s="14" t="s">
+      <x:c r="H15" s="16">
+        <x:v>46128.1699027199</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46136</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
         <x:v>75</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46133.2374101505</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46135</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>76</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46134.0815209838</x:v>
+        <x:v>46128.349008206</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>32</x:v>
@@ -2944,34 +2956,34 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D16" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E16" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="F16" s="14" t="s">
+      <x:c r="G16" s="14" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G16" s="14" t="s">
+      <x:c r="H16" s="16">
+        <x:v>46133.2374101505</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46135</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46126.2900560185</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46162</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>81</x:v>
       </x:c>
       <x:c r="K16" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46128.194732662</x:v>
+        <x:v>46134.0815209838</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>32</x:v>
@@ -2982,34 +2994,34 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D17" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E17" s="14" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="F17" s="14" t="s">
+      <x:c r="G17" s="14" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="G17" s="14" t="s">
+      <x:c r="H17" s="16">
+        <x:v>46126.2900560185</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>46162</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46132.3880687384</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46138</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
-        <x:v>86</x:v>
-      </x:c>
       <x:c r="K17" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46135.1691307292</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>32</x:v>
@@ -3020,34 +3032,34 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D18" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E18" s="14" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="F18" s="14" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="F18" s="14" t="s">
+      <x:c r="G18" s="14" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="G18" s="14" t="s">
+      <x:c r="H18" s="16">
+        <x:v>46132.3880687384</x:v>
+      </x:c>
+      <x:c r="I18" s="16">
+        <x:v>46138</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="H18" s="16">
-        <x:v>46112.0874409838</x:v>
-      </x:c>
-      <x:c r="I18" s="16">
-        <x:v>46134</x:v>
-      </x:c>
-      <x:c r="J18" s="15" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46135.1691307292</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>32</x:v>
@@ -3058,34 +3070,34 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E19" s="14" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="s">
+      <x:c r="G19" s="14" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G19" s="14" t="s">
+      <x:c r="H19" s="16">
+        <x:v>46112.0874409838</x:v>
+      </x:c>
+      <x:c r="I19" s="16">
+        <x:v>46134</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="H19" s="16">
-        <x:v>46126.3116678125</x:v>
-      </x:c>
-      <x:c r="I19" s="16">
-        <x:v>46196</x:v>
-      </x:c>
-      <x:c r="J19" s="15" t="s">
-        <x:v>96</x:v>
-      </x:c>
       <x:c r="K19" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46128.191368669</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>32</x:v>
@@ -3093,14 +3105,16 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C20" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E20" s="14" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="C20" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D20" s="15" t="s"/>
-      <x:c r="E20" s="14" t="s">
-        <x:v>28</x:v>
       </x:c>
       <x:c r="F20" s="14" t="s">
         <x:v>98</x:v>
@@ -3109,19 +3123,19 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46134.1206595602</x:v>
+        <x:v>46126.3116678125</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>46134.1206809375</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
         <x:v>100</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
-        <x:v>630</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46139.1576734144</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
         <x:v>32</x:v>
@@ -3129,7 +3143,7 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
         <x:v>27</x:v>
@@ -3139,25 +3153,25 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="F21" s="14" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G21" s="14" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46120.3579437153</x:v>
+        <x:v>46134.1206595602</x:v>
       </x:c>
       <x:c r="I21" s="16">
-        <x:v>46120.3579643171</x:v>
+        <x:v>46134.1206809375</x:v>
       </x:c>
       <x:c r="J21" s="15" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
-        <x:v>2790</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46132.2453653241</x:v>
+        <x:v>46139.1576734144</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>32</x:v>
@@ -3165,37 +3179,35 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
-        <x:v>104</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s"/>
+      <x:c r="E22" s="14" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D22" s="15" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E22" s="14" t="s">
+      <x:c r="G22" s="14" t="s">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="s">
+      <x:c r="H22" s="16">
+        <x:v>46120.3579437153</x:v>
+      </x:c>
+      <x:c r="I22" s="16">
+        <x:v>46120.3579643171</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="G22" s="14" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="H22" s="16">
-        <x:v>46105.3461754861</x:v>
-      </x:c>
-      <x:c r="I22" s="16">
-        <x:v>46137</x:v>
-      </x:c>
-      <x:c r="J22" s="15" t="s">
-        <x:v>109</x:v>
-      </x:c>
       <x:c r="K22" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>2790</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46120.2790231597</x:v>
+        <x:v>46132.2453653241</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
         <x:v>32</x:v>
@@ -3203,37 +3215,37 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
-        <x:v>104</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>110</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="F23" s="14" t="s">
+      <x:c r="G23" s="14" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="G23" s="14" t="s">
+      <x:c r="H23" s="16">
+        <x:v>46105.3461754861</x:v>
+      </x:c>
+      <x:c r="I23" s="16">
+        <x:v>46137</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="s">
         <x:v>113</x:v>
-      </x:c>
-      <x:c r="H23" s="16">
-        <x:v>46134.0293580208</x:v>
-      </x:c>
-      <x:c r="I23" s="16">
-        <x:v>46144</x:v>
-      </x:c>
-      <x:c r="J23" s="15" t="s">
-        <x:v>114</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46139.2265670718</x:v>
+        <x:v>46120.2790231597</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>32</x:v>
@@ -3241,10 +3253,10 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
-        <x:v>104</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C24" s="14" t="s">
-        <x:v>77</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D24" s="15" t="s">
         <x:v>22</x:v>
@@ -3259,10 +3271,10 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46134.0293580208</x:v>
       </x:c>
       <x:c r="I24" s="16">
-        <x:v>46224</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J24" s="15" t="s">
         <x:v>118</x:v>
@@ -3271,7 +3283,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46139.2265670718</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
         <x:v>32</x:v>
@@ -3279,37 +3291,37 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="14" t="s">
-        <x:v>104</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>119</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E25" s="14" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="F25" s="14" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="F25" s="14" t="s">
+      <x:c r="G25" s="14" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="G25" s="14" t="s">
+      <x:c r="H25" s="16">
+        <x:v>46126.2721295949</x:v>
+      </x:c>
+      <x:c r="I25" s="16">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="J25" s="15" t="s">
         <x:v>122</x:v>
-      </x:c>
-      <x:c r="H25" s="16">
-        <x:v>46125.335903912</x:v>
-      </x:c>
-      <x:c r="I25" s="16">
-        <x:v>46203</x:v>
-      </x:c>
-      <x:c r="J25" s="15" t="s">
-        <x:v>123</x:v>
       </x:c>
       <x:c r="K25" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="18">
-        <x:v>46134.2685065741</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
         <x:v>32</x:v>
@@ -3317,37 +3329,37 @@
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="14" t="s">
-        <x:v>104</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C26" s="14" t="s">
-        <x:v>124</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D26" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E26" s="14" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="F26" s="14" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="F26" s="14" t="s">
+      <x:c r="G26" s="14" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="G26" s="14" t="s">
+      <x:c r="H26" s="16">
+        <x:v>46125.335903912</x:v>
+      </x:c>
+      <x:c r="I26" s="16">
+        <x:v>46203</x:v>
+      </x:c>
+      <x:c r="J26" s="15" t="s">
         <x:v>127</x:v>
-      </x:c>
-      <x:c r="H26" s="16">
-        <x:v>46126.2873086111</x:v>
-      </x:c>
-      <x:c r="I26" s="16">
-        <x:v>46130</x:v>
-      </x:c>
-      <x:c r="J26" s="15" t="s">
-        <x:v>128</x:v>
       </x:c>
       <x:c r="K26" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L26" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46134.2685065741</x:v>
       </x:c>
       <x:c r="M26" s="14" t="s">
         <x:v>32</x:v>
@@ -3355,37 +3367,37 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="14" t="s">
-        <x:v>104</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C27" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D27" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E27" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F27" s="14" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G27" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H27" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I27" s="16">
-        <x:v>46189</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J27" s="15" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="K27" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L27" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M27" s="14" t="s">
         <x:v>32</x:v>
@@ -3393,22 +3405,22 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
       <x:c r="B28" s="14" t="s">
-        <x:v>104</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C28" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D28" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E28" s="14" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F28" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G28" s="14" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H28" s="16">
         <x:v>46126.3215783912</x:v>
@@ -3417,7 +3429,7 @@
         <x:v>46198</x:v>
       </x:c>
       <x:c r="J28" s="15" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K28" s="17" t="n">
         <x:v>3030</x:v>
@@ -3429,64 +3441,91 @@
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="29" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B29" s="14" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C29" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E29" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F29" s="14" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G29" s="14" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H29" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I29" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J29" s="15" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="K29" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L29" s="18">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M29" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
     <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="31" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B31" s="19" t="s">
+    <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="32" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B32" s="19" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C31" s="20" t="s"/>
-      <x:c r="D31" s="20" t="s"/>
-      <x:c r="E31" s="21" t="s"/>
-      <x:c r="F31" s="21" t="s"/>
-    </x:row>
-    <x:row r="32" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B32" s="22" t="s">
+      <x:c r="C32" s="20" t="s"/>
+      <x:c r="D32" s="20" t="s"/>
+      <x:c r="E32" s="21" t="s"/>
+      <x:c r="F32" s="21" t="s"/>
+    </x:row>
+    <x:row r="33" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B33" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C32" s="23" t="s"/>
-      <x:c r="D32" s="23" t="s"/>
-      <x:c r="E32" s="23" t="s"/>
-      <x:c r="F32" s="24" t="s">
+      <x:c r="C33" s="23" t="s"/>
+      <x:c r="D33" s="23" t="s"/>
+      <x:c r="E33" s="23" t="s"/>
+      <x:c r="F33" s="24" t="s">
         <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B33" s="25" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C33" s="26" t="s"/>
-      <x:c r="D33" s="26" t="s"/>
-      <x:c r="E33" s="26" t="s"/>
-      <x:c r="F33" s="27" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:28" ht="18" customHeight="1">
       <x:c r="B34" s="25" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C34" s="26" t="s"/>
       <x:c r="D34" s="26" t="s"/>
       <x:c r="E34" s="26" t="s"/>
       <x:c r="F34" s="27" t="n">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
       <x:c r="B35" s="25" t="s">
-        <x:v>97</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C35" s="26" t="s"/>
       <x:c r="D35" s="26" t="s"/>
       <x:c r="E35" s="26" t="s"/>
       <x:c r="F35" s="27" t="n">
-        <x:v>1</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
       <x:c r="B36" s="25" t="s">
-        <x:v>26</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C36" s="26" t="s"/>
       <x:c r="D36" s="26" t="s"/>
@@ -3497,27 +3536,37 @@
     </x:row>
     <x:row r="37" spans="1:28" ht="18" customHeight="1">
       <x:c r="B37" s="25" t="s">
-        <x:v>104</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C37" s="26" t="s"/>
       <x:c r="D37" s="26" t="s"/>
       <x:c r="E37" s="26" t="s"/>
       <x:c r="F37" s="27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B38" s="25" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C38" s="26" t="s"/>
+      <x:c r="D38" s="26" t="s"/>
+      <x:c r="E38" s="26" t="s"/>
+      <x:c r="F38" s="27" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B38" s="28" t="s">
+    <x:row r="39" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B39" s="28" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C38" s="29" t="s"/>
-      <x:c r="D38" s="29" t="s"/>
-      <x:c r="E38" s="29" t="s"/>
-      <x:c r="F38" s="30" t="n">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C39" s="29" t="s"/>
+      <x:c r="D39" s="29" t="s"/>
+      <x:c r="E39" s="29" t="s"/>
+      <x:c r="F39" s="30" t="n">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
     <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4477,14 +4526,14 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B31:F31"/>
-    <x:mergeCell ref="B32:E32"/>
+    <x:mergeCell ref="B32:F32"/>
     <x:mergeCell ref="B33:E33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
     <x:mergeCell ref="B37:E37"/>
     <x:mergeCell ref="B38:E38"/>
+    <x:mergeCell ref="B39:E39"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -350,6 +350,21 @@
   </x:si>
   <x:si>
     <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AJT. GADGETS SHOP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>E-1 G/F AJT Building DOLORES st. CORRALES AVE, Nazareth, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-24-11-525</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1440-123</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518280 A</x:t>
   </x:si>
   <x:si>
     <x:t>GAISANO CITY</x:t>
@@ -3233,19 +3248,19 @@
         <x:v>112</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46105.3461754861</x:v>
+        <x:v>46130.477754919</x:v>
       </x:c>
       <x:c r="I23" s="16">
-        <x:v>46137</x:v>
+        <x:v>45968</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46120.2790231597</x:v>
+        <x:v>46140.1466972338</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>32</x:v>
@@ -3271,10 +3286,10 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="H24" s="16">
-        <x:v>46134.0293580208</x:v>
+        <x:v>46105.3461754861</x:v>
       </x:c>
       <x:c r="I24" s="16">
-        <x:v>46144</x:v>
+        <x:v>46137</x:v>
       </x:c>
       <x:c r="J24" s="15" t="s">
         <x:v>118</x:v>
@@ -3283,7 +3298,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46139.2265670718</x:v>
+        <x:v>46120.2790231597</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
         <x:v>32</x:v>
@@ -3294,34 +3309,34 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>81</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E25" s="14" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F25" s="14" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G25" s="14" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H25" s="16">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46134.0293580208</x:v>
       </x:c>
       <x:c r="I25" s="16">
-        <x:v>46224</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J25" s="15" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="K25" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L25" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46139.2265670718</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
         <x:v>32</x:v>
@@ -3332,7 +3347,7 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="C26" s="14" t="s">
-        <x:v>123</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D26" s="15" t="s">
         <x:v>22</x:v>
@@ -3347,10 +3362,10 @@
         <x:v>126</x:v>
       </x:c>
       <x:c r="H26" s="16">
-        <x:v>46125.335903912</x:v>
+        <x:v>46126.2721295949</x:v>
       </x:c>
       <x:c r="I26" s="16">
-        <x:v>46203</x:v>
+        <x:v>46224</x:v>
       </x:c>
       <x:c r="J26" s="15" t="s">
         <x:v>127</x:v>
@@ -3359,7 +3374,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L26" s="18">
-        <x:v>46134.2685065741</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M26" s="14" t="s">
         <x:v>32</x:v>
@@ -3385,10 +3400,10 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="H27" s="16">
-        <x:v>46126.2873086111</x:v>
+        <x:v>46125.335903912</x:v>
       </x:c>
       <x:c r="I27" s="16">
-        <x:v>46130</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="J27" s="15" t="s">
         <x:v>132</x:v>
@@ -3397,7 +3412,7 @@
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L27" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46134.2685065741</x:v>
       </x:c>
       <x:c r="M27" s="14" t="s">
         <x:v>32</x:v>
@@ -3408,34 +3423,34 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="C28" s="14" t="s">
-        <x:v>96</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D28" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E28" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F28" s="14" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G28" s="14" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H28" s="16">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I28" s="16">
-        <x:v>46198</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J28" s="15" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="K28" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L28" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M28" s="14" t="s">
         <x:v>32</x:v>
@@ -3452,91 +3467,118 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="E29" s="14" t="s">
-        <x:v>97</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F29" s="14" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G29" s="14" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="H29" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46126.3215783912</x:v>
       </x:c>
       <x:c r="I29" s="16">
-        <x:v>46189</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="J29" s="15" t="s">
-        <x:v>139</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="K29" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L29" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46128.1824279398</x:v>
       </x:c>
       <x:c r="M29" s="14" t="s">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="30" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B30" s="14" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C30" s="14" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E30" s="14" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="F30" s="14" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G30" s="14" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H30" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I30" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J30" s="15" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="K30" s="17" t="n">
+        <x:v>3030</x:v>
+      </x:c>
+      <x:c r="L30" s="18">
+        <x:v>46128.1930397685</x:v>
+      </x:c>
+      <x:c r="M30" s="14" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
     <x:row r="31" spans="1:28" ht="15.75" customHeight="1"/>
-    <x:row r="32" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B32" s="19" t="s">
+    <x:row r="32" spans="1:28" ht="15.75" customHeight="1"/>
+    <x:row r="33" spans="1:28" ht="30" customHeight="1">
+      <x:c r="B33" s="19" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C32" s="20" t="s"/>
-      <x:c r="D32" s="20" t="s"/>
-      <x:c r="E32" s="21" t="s"/>
-      <x:c r="F32" s="21" t="s"/>
-    </x:row>
-    <x:row r="33" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B33" s="22" t="s">
+      <x:c r="C33" s="20" t="s"/>
+      <x:c r="D33" s="20" t="s"/>
+      <x:c r="E33" s="21" t="s"/>
+      <x:c r="F33" s="21" t="s"/>
+    </x:row>
+    <x:row r="34" spans="1:28" ht="22" customHeight="1">
+      <x:c r="B34" s="22" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="C33" s="23" t="s"/>
-      <x:c r="D33" s="23" t="s"/>
-      <x:c r="E33" s="23" t="s"/>
-      <x:c r="F33" s="24" t="s">
+      <x:c r="C34" s="23" t="s"/>
+      <x:c r="D34" s="23" t="s"/>
+      <x:c r="E34" s="23" t="s"/>
+      <x:c r="F34" s="24" t="s">
         <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B34" s="25" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C34" s="26" t="s"/>
-      <x:c r="D34" s="26" t="s"/>
-      <x:c r="E34" s="26" t="s"/>
-      <x:c r="F34" s="27" t="n">
-        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
       <x:c r="B35" s="25" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C35" s="26" t="s"/>
       <x:c r="D35" s="26" t="s"/>
       <x:c r="E35" s="26" t="s"/>
       <x:c r="F35" s="27" t="n">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
       <x:c r="B36" s="25" t="s">
-        <x:v>101</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C36" s="26" t="s"/>
       <x:c r="D36" s="26" t="s"/>
       <x:c r="E36" s="26" t="s"/>
       <x:c r="F36" s="27" t="n">
-        <x:v>1</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:28" ht="18" customHeight="1">
       <x:c r="B37" s="25" t="s">
-        <x:v>26</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C37" s="26" t="s"/>
       <x:c r="D37" s="26" t="s"/>
@@ -3547,27 +3589,37 @@
     </x:row>
     <x:row r="38" spans="1:28" ht="18" customHeight="1">
       <x:c r="B38" s="25" t="s">
-        <x:v>108</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C38" s="26" t="s"/>
       <x:c r="D38" s="26" t="s"/>
       <x:c r="E38" s="26" t="s"/>
       <x:c r="F38" s="27" t="n">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B39" s="28" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:28" ht="18" customHeight="1">
+      <x:c r="B39" s="25" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="C39" s="26" t="s"/>
+      <x:c r="D39" s="26" t="s"/>
+      <x:c r="E39" s="26" t="s"/>
+      <x:c r="F39" s="27" t="n">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:28" ht="28" customHeight="1">
+      <x:c r="B40" s="28" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="C39" s="29" t="s"/>
-      <x:c r="D39" s="29" t="s"/>
-      <x:c r="E39" s="29" t="s"/>
-      <x:c r="F39" s="30" t="n">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28" ht="15.75" customHeight="1"/>
+      <x:c r="C40" s="29" t="s"/>
+      <x:c r="D40" s="29" t="s"/>
+      <x:c r="E40" s="29" t="s"/>
+      <x:c r="F40" s="30" t="n">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
     <x:row r="41" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="42" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="43" spans="1:28" ht="15.75" customHeight="1"/>
@@ -4526,14 +4578,14 @@
     <x:mergeCell ref="B1:M2"/>
     <x:mergeCell ref="B3:M3"/>
     <x:mergeCell ref="B4:M4"/>
-    <x:mergeCell ref="B32:F32"/>
-    <x:mergeCell ref="B33:E33"/>
+    <x:mergeCell ref="B33:F33"/>
     <x:mergeCell ref="B34:E34"/>
     <x:mergeCell ref="B35:E35"/>
     <x:mergeCell ref="B36:E36"/>
     <x:mergeCell ref="B37:E37"/>
     <x:mergeCell ref="B38:E38"/>
     <x:mergeCell ref="B39:E39"/>
+    <x:mergeCell ref="B40:E40"/>
   </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report_cache_ServiceTracking-X-202501-202612.xlsx.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="137">
   <x:si>
     <x:t>APPLICATION SUMMARY REPORT BY SERVICE</x:t>
   </x:si>
@@ -64,18 +64,36 @@
     <x:t>BY</x:t>
   </x:si>
   <x:si>
+    <x:t>Commercial Radio Operator Certificate (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDISSA ABASTAS AMANTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brgy 4, City Of Koronadal (Capital), South Cotabato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>123456789</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1402-290</x:t>
+  </x:si>
+  <x:si>
+    <x:t>165163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cashier edge</x:t>
+  </x:si>
+  <x:si>
     <x:t>Commercial Radio Operator Certificate (NEW)</x:t>
   </x:si>
   <x:si>
-    <x:t>EDISSA ABASTAS AMANTE</x:t>
-  </x:si>
-  <x:si>
     <x:t>NEW</x:t>
   </x:si>
   <x:si>
-    <x:t>Brgy 4, City Of Koronadal (Capital), South Cotabato</x:t>
-  </x:si>
-  <x:si>
     <x:t>26-1RTG-X-06965</x:t>
   </x:si>
   <x:si>
@@ -85,24 +103,6 @@
     <x:t>125646</x:t>
   </x:si>
   <x:si>
-    <x:t>cashier edge</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Commercial Radio Operator Certificate (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>123456789</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-3-2026-1402-290</x:t>
-  </x:si>
-  <x:si>
-    <x:t>165163</x:t>
-  </x:si>
-  <x:si>
     <x:t>Permit to PURCHASE</x:t>
   </x:si>
   <x:si>
@@ -136,15 +136,258 @@
     <x:t>TOTAL</x:t>
   </x:si>
   <x:si>
+    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAISANO CITY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CM RECTO AVE., CORRALES EXTN.,, BRGY. 25, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-21-04-454</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1412-703</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518165</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dealer Permit (RENEWAL)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIDMARK WEST, INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Robinson's Place, Bagontaas, City Of Valencia, Bukidnon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-24-04-516</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-3-2026-1421-158</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMCOR INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RIZAL AVENUE, 50TH DISTRICT, Ozamis City, Misamis Occidental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01359</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1425-830</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TECHNOMART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>385 Jr Borja St. Aguinaldo, 32, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX - MRR-10 - 04 - 326</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1429-808</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518180</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNIPACE CORPORATION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORTICH STREET, Barangay 04, City Of Malaybalay (Capital), Bukidnon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-13-06-152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1433-178</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518188</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14-REDP-CAG-01347</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1432-214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518189</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-10-06-128</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1431-363</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INTERPACE CORPORATION</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14-REDP-CAG-01346</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1430-046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-10-07-135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1428-833</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518192</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMCOR INCORPORATED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JVR BLDG J.R BORJA ST., BARANGAY 32, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">18-REDP-CAG-01365 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1434-610</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518195</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/PUR-JJ-00018-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1422-426</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518202</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01362</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1444-814</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518210 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMCOR, INC.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hannah Shangrila Bldg. Zone 1B, Iponan, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19-REDP-CAG-01364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1448-935</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518223 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIDMARK WEST, INC. - ROBINSONS VALENCIA SES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-18-12-410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1424-309</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518227 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01361</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1436-764</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518230 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORO GADGETS INC. (GRAPHIC GADGET STORES)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3E-1 THIRD LEVEL GAISANO PUERTO, PUERTO, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MP-17-04-174</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1446-993</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518243 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMCOR INC.  (BALINGASAG BRANCH)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quezon Osmena Street, Barangay 6 Poblacion, Balingasag, Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18-REDP-CAG-01360</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1451-946</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518246 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Permit to POSSESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>P/POS-JJ-00048-26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1450-116</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518256 A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HO TSAYKI INC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T-29 &amp; T-30 citymall bulua, Bulua, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROX-MRR-19-05-425</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61-4-2026-1449-395</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1518265 A</x:t>
+  </x:si>
+  <x:si>
     <x:t>Dealer Permit (NEW)</x:t>
   </x:si>
   <x:si>
     <x:t>CELLTY MOBILE INC</x:t>
   </x:si>
   <x:si>
-    <x:t>GAISANO TUBOD,PABLACION,TUBOD LANAO DEL NORTE, POBLACION, Tubod (Capital), Lanao Del Norte</x:t>
-  </x:si>
-  <x:si>
     <x:t>MPDP-ROX-08615-26</x:t>
   </x:si>
   <x:si>
@@ -169,15 +412,6 @@
     <x:t>1518270 A</x:t>
   </x:si>
   <x:si>
-    <x:t>Dealer Permit (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMCOR INC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RIZAL AVENUE, 50TH DISTRICT, Ozamis City, Misamis Occidental</x:t>
-  </x:si>
-  <x:si>
     <x:t>18-REDP-CAG-01370</x:t>
   </x:si>
   <x:si>
@@ -187,171 +421,6 @@
     <x:t>1518271 A</x:t>
   </x:si>
   <x:si>
-    <x:t>Sta cecilia National highway, Gusa, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18-REDP-CAG-01359</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1425-830</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518175</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NADAL BDLG NATIONAL HIGHWAY, BARANGAY 3, Gingoog City, Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18-REDP-CAG-01361</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1436-764</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518230 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P-3 NATIONAL HIGHWAY, POBLACION, Alubijid, Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18-REDP-CAG-01362</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1444-814</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518210 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMCOR INC.  (BALINGASAG BRANCH)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Quezon Osmena Street, Barangay 6 Poblacion, Balingasag, Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18-REDP-CAG-01360</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1451-946</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518246 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMCOR INCORPORATED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JVR BLDG J.R BORJA ST., BARANGAY 32, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">18-REDP-CAG-01365 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1434-610</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518195</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMCOR, INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hannah Shangrila Bldg. Zone 1B, Iponan, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19-REDP-CAG-01364</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1448-935</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518223 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INTERPACE CORPORATION</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WEST WING LKKS CENTER, Barangay LAPASAN, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14-REDP-CAG-01346</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1430-046</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518191</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORO GADGETS INC. (GRAPHIC GADGET STORES)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3E-1 THIRD LEVEL GAISANO PUERTO, PUERTO, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MP-17-04-174</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1446-993</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518243 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOLIDMARK WEST, INC.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MVVL3 K1 3RD FLOOR GAISANO CITY, Poblacion, City Of Valencia, Bukidnon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MRR-24-04-516</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-3-2026-1421-158</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518169</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNIPACE CORPORATION</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CM RECTO AVE., CORRALES EXTN.,, Barangay 26, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14-REDP-CAG-01347</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1432-214</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518189</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Permit to POSSESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P/POS-JJ-00048-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1450-116</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518256 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>P/PUR-JJ-00018-26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1422-426</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518202</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Retailer/Reseller Permit (RENEWAL)</x:t>
-  </x:si>
-  <x:si>
     <x:t>AJT. GADGETS SHOP</x:t>
   </x:si>
   <x:si>
@@ -365,99 +434,6 @@
   </x:si>
   <x:si>
     <x:t>1518280 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAISANO CITY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CM RECTO AVE., CORRALES EXTN.,, BRGY. 25, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MRR-21-04-454</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-3-2026-1412-703</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518165</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HO TSAYKI INC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T-29 &amp; T-30 citymall bulua, Bulua, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MRR-19-05-425</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1449-395</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518265 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WEST WING LKKS CENTER, Barangay 31, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MRR-10-07-135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1428-833</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518192</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOLIDMARK WEST, INC. - ROBINSONS VALENCIA SES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Robinson's Place, Bagontaas, City Of Valencia, Bukidnon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MRR-18-12-410</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1424-309</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518227 A</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TECHNOMART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>385 Jr Borja St. Aguinaldo, 32, Cagayan De Oro City (Capital), Misamis Oriental</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX - MRR-10 - 04 - 326</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1429-808</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518180</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORTICH STREET, Barangay 04, City Of Malaybalay (Capital), Bukidnon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MRR-13-06-152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1433-178</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518188</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROX-MRR-10-06-128</x:t>
-  </x:si>
-  <x:si>
-    <x:t>61-4-2026-1431-363</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1518190</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1347,19 +1323,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46091.1148722454</x:v>
+        <x:v>46091.0595425347</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46091.1431335995</x:v>
+        <x:v>46050</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>210</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46091.1453198032</x:v>
+        <x:v>46091.0629955324</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>20</x:v>
@@ -1385,19 +1361,19 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46091.0595425347</x:v>
+        <x:v>46091.1148722454</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46050</x:v>
+        <x:v>46091.1431335995</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>300</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46091.0629955324</x:v>
+        <x:v>46091.1453198032</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>20</x:v>
@@ -1463,7 +1439,7 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="18" customHeight="1">
       <x:c r="B15" s="25" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C15" s="26" t="s"/>
       <x:c r="D15" s="26" t="s"/>
@@ -1474,7 +1450,7 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="18" customHeight="1">
       <x:c r="B16" s="25" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C16" s="26" t="s"/>
       <x:c r="D16" s="26" t="s"/>
@@ -2682,19 +2658,19 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="H8" s="16">
-        <x:v>46132.313701713</x:v>
+        <x:v>46105.3461754861</x:v>
       </x:c>
       <x:c r="I8" s="16">
-        <x:v>46132.3137205208</x:v>
+        <x:v>46137</x:v>
       </x:c>
       <x:c r="J8" s="15" t="s">
         <x:v>42</x:v>
       </x:c>
       <x:c r="K8" s="17" t="n">
-        <x:v>3530</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L8" s="18">
-        <x:v>46139.230364294</x:v>
+        <x:v>46120.2790231597</x:v>
       </x:c>
       <x:c r="M8" s="14" t="s">
         <x:v>32</x:v>
@@ -2702,37 +2678,37 @@
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
       <x:c r="B9" s="14" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D9" s="15" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H9" s="16">
-        <x:v>46129.4086055787</x:v>
+        <x:v>46112.0874409838</x:v>
       </x:c>
       <x:c r="I9" s="16">
-        <x:v>46129.4086256481</x:v>
+        <x:v>46134</x:v>
       </x:c>
       <x:c r="J9" s="15" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K9" s="17" t="n">
-        <x:v>2130</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L9" s="18">
-        <x:v>46139.3272522222</x:v>
+        <x:v>46125.1598529398</x:v>
       </x:c>
       <x:c r="M9" s="14" t="s">
         <x:v>32</x:v>
@@ -2740,13 +2716,13 @@
     </x:row>
     <x:row r="10" spans="1:28" ht="30" customHeight="1">
       <x:c r="B10" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C10" s="14" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="D10" s="15" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
         <x:v>50</x:v>
@@ -2758,10 +2734,10 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="H10" s="16">
-        <x:v>46137.0314533796</x:v>
+        <x:v>46125.3390388079</x:v>
       </x:c>
       <x:c r="I10" s="16">
-        <x:v>46149</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J10" s="15" t="s">
         <x:v>53</x:v>
@@ -2770,7 +2746,7 @@
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L10" s="18">
-        <x:v>46139.3366940046</x:v>
+        <x:v>46125.3538272917</x:v>
       </x:c>
       <x:c r="M10" s="14" t="s">
         <x:v>32</x:v>
@@ -2778,37 +2754,37 @@
     </x:row>
     <x:row r="11" spans="1:28" ht="30" customHeight="1">
       <x:c r="B11" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C11" s="14" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D11" s="15" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F11" s="14" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G11" s="14" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H11" s="16">
-        <x:v>46125.3390388079</x:v>
+        <x:v>46126.2873086111</x:v>
       </x:c>
       <x:c r="I11" s="16">
-        <x:v>46135</x:v>
+        <x:v>46130</x:v>
       </x:c>
       <x:c r="J11" s="15" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K11" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L11" s="18">
-        <x:v>46125.3538272917</x:v>
+        <x:v>46127.0949605556</x:v>
       </x:c>
       <x:c r="M11" s="14" t="s">
         <x:v>32</x:v>
@@ -2816,37 +2792,37 @@
     </x:row>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
       <x:c r="B12" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C12" s="14" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D12" s="15" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E12" s="14" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F12" s="14" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G12" s="14" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H12" s="16">
-        <x:v>46128.2089466088</x:v>
+        <x:v>46126.3215783912</x:v>
       </x:c>
       <x:c r="I12" s="16">
-        <x:v>46135</x:v>
+        <x:v>46198</x:v>
       </x:c>
       <x:c r="J12" s="15" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="K12" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L12" s="18">
-        <x:v>46134.3002672917</x:v>
+        <x:v>46128.1824279398</x:v>
       </x:c>
       <x:c r="M12" s="14" t="s">
         <x:v>32</x:v>
@@ -2854,37 +2830,37 @@
     </x:row>
     <x:row r="13" spans="1:28" ht="30" customHeight="1">
       <x:c r="B13" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C13" s="14" t="s">
-        <x:v>49</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D13" s="15" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E13" s="14" t="s">
-        <x:v>62</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F13" s="14" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G13" s="14" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H13" s="16">
-        <x:v>46132.2785644329</x:v>
+        <x:v>46126.3116678125</x:v>
       </x:c>
       <x:c r="I13" s="16">
-        <x:v>46135</x:v>
+        <x:v>46196</x:v>
       </x:c>
       <x:c r="J13" s="15" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="K13" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L13" s="18">
-        <x:v>46133.1152077083</x:v>
+        <x:v>46128.191368669</x:v>
       </x:c>
       <x:c r="M13" s="14" t="s">
         <x:v>32</x:v>
@@ -2892,37 +2868,37 @@
     </x:row>
     <x:row r="14" spans="1:28" ht="30" customHeight="1">
       <x:c r="B14" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C14" s="14" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D14" s="15" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E14" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F14" s="14" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="F14" s="14" t="s">
+      <x:c r="G14" s="14" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="G14" s="14" t="s">
+      <x:c r="H14" s="16">
+        <x:v>46126.3072273495</x:v>
+      </x:c>
+      <x:c r="I14" s="16">
+        <x:v>46189</x:v>
+      </x:c>
+      <x:c r="J14" s="15" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="H14" s="16">
-        <x:v>46135.0684019213</x:v>
-      </x:c>
-      <x:c r="I14" s="16">
-        <x:v>46135</x:v>
-      </x:c>
-      <x:c r="J14" s="15" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="K14" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L14" s="18">
-        <x:v>46135.1975182523</x:v>
+        <x:v>46128.1930397685</x:v>
       </x:c>
       <x:c r="M14" s="14" t="s">
         <x:v>32</x:v>
@@ -2930,37 +2906,37 @@
     </x:row>
     <x:row r="15" spans="1:28" ht="30" customHeight="1">
       <x:c r="B15" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E15" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="D15" s="15" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E15" s="14" t="s">
+      <x:c r="G15" s="14" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="s">
+      <x:c r="H15" s="16">
+        <x:v>46126.2900560185</x:v>
+      </x:c>
+      <x:c r="I15" s="16">
+        <x:v>46162</x:v>
+      </x:c>
+      <x:c r="J15" s="15" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="G15" s="14" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H15" s="16">
-        <x:v>46128.1699027199</x:v>
-      </x:c>
-      <x:c r="I15" s="16">
-        <x:v>46136</x:v>
-      </x:c>
-      <x:c r="J15" s="15" t="s">
-        <x:v>75</x:v>
       </x:c>
       <x:c r="K15" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L15" s="18">
-        <x:v>46128.349008206</x:v>
+        <x:v>46128.194732662</x:v>
       </x:c>
       <x:c r="M15" s="14" t="s">
         <x:v>32</x:v>
@@ -2968,37 +2944,37 @@
     </x:row>
     <x:row r="16" spans="1:28" ht="30" customHeight="1">
       <x:c r="B16" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C16" s="14" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E16" s="14" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F16" s="14" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G16" s="14" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H16" s="16">
+        <x:v>46126.2721295949</x:v>
+      </x:c>
+      <x:c r="I16" s="16">
+        <x:v>46224</x:v>
+      </x:c>
+      <x:c r="J16" s="15" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="D16" s="15" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E16" s="14" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F16" s="14" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="G16" s="14" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H16" s="16">
-        <x:v>46133.2374101505</x:v>
-      </x:c>
-      <x:c r="I16" s="16">
-        <x:v>46135</x:v>
-      </x:c>
-      <x:c r="J16" s="15" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="K16" s="17" t="n">
-        <x:v>1950</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L16" s="18">
-        <x:v>46134.0815209838</x:v>
+        <x:v>46128.1955625</x:v>
       </x:c>
       <x:c r="M16" s="14" t="s">
         <x:v>32</x:v>
@@ -3006,37 +2982,37 @@
     </x:row>
     <x:row r="17" spans="1:28" ht="30" customHeight="1">
       <x:c r="B17" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C17" s="14" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E17" s="14" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G17" s="14" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H17" s="16">
+        <x:v>46128.1699027199</x:v>
+      </x:c>
+      <x:c r="I17" s="16">
+        <x:v>46136</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="D17" s="15" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E17" s="14" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G17" s="14" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="H17" s="16">
-        <x:v>46126.2900560185</x:v>
-      </x:c>
-      <x:c r="I17" s="16">
-        <x:v>46162</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="s">
-        <x:v>85</x:v>
       </x:c>
       <x:c r="K17" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L17" s="18">
-        <x:v>46128.194732662</x:v>
+        <x:v>46128.349008206</x:v>
       </x:c>
       <x:c r="M17" s="14" t="s">
         <x:v>32</x:v>
@@ -3044,37 +3020,35 @@
     </x:row>
     <x:row r="18" spans="1:28" ht="30" customHeight="1">
       <x:c r="B18" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C18" s="14" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="D18" s="15" t="s">
-        <x:v>22</x:v>
-      </x:c>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="s"/>
       <x:c r="E18" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F18" s="14" t="s">
-        <x:v>88</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G18" s="14" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H18" s="16">
-        <x:v>46132.3880687384</x:v>
+        <x:v>46120.3579437153</x:v>
       </x:c>
       <x:c r="I18" s="16">
-        <x:v>46138</x:v>
+        <x:v>46120.3579643171</x:v>
       </x:c>
       <x:c r="J18" s="15" t="s">
-        <x:v>90</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K18" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>2790</x:v>
       </x:c>
       <x:c r="L18" s="18">
-        <x:v>46135.1691307292</x:v>
+        <x:v>46132.2453653241</x:v>
       </x:c>
       <x:c r="M18" s="14" t="s">
         <x:v>32</x:v>
@@ -3082,37 +3056,37 @@
     </x:row>
     <x:row r="19" spans="1:28" ht="30" customHeight="1">
       <x:c r="B19" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C19" s="14" t="s">
-        <x:v>91</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D19" s="15" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E19" s="14" t="s">
-        <x:v>92</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F19" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G19" s="14" t="s">
-        <x:v>94</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H19" s="16">
-        <x:v>46112.0874409838</x:v>
+        <x:v>46132.2785644329</x:v>
       </x:c>
       <x:c r="I19" s="16">
-        <x:v>46134</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J19" s="15" t="s">
-        <x:v>95</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="K19" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L19" s="18">
-        <x:v>46125.1598529398</x:v>
+        <x:v>46133.1152077083</x:v>
       </x:c>
       <x:c r="M19" s="14" t="s">
         <x:v>32</x:v>
@@ -3120,37 +3094,37 @@
     </x:row>
     <x:row r="20" spans="1:28" ht="30" customHeight="1">
       <x:c r="B20" s="14" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C20" s="14" t="s">
-        <x:v>96</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D20" s="15" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E20" s="14" t="s">
-        <x:v>97</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F20" s="14" t="s">
-        <x:v>98</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G20" s="14" t="s">
-        <x:v>99</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="H20" s="16">
-        <x:v>46126.3116678125</x:v>
+        <x:v>46133.2374101505</x:v>
       </x:c>
       <x:c r="I20" s="16">
-        <x:v>46196</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J20" s="15" t="s">
-        <x:v>100</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K20" s="17" t="n">
         <x:v>1950</x:v>
       </x:c>
       <x:c r="L20" s="18">
-        <x:v>46128.191368669</x:v>
+        <x:v>46134.0815209838</x:v>
       </x:c>
       <x:c r="M20" s="14" t="s">
         <x:v>32</x:v>
@@ -3158,35 +3132,37 @@
     </x:row>
     <x:row r="21" spans="1:28" ht="30" customHeight="1">
       <x:c r="B21" s="14" t="s">
-        <x:v>101</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C21" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D21" s="15" t="s"/>
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E21" s="14" t="s">
-        <x:v>28</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F21" s="14" t="s">
-        <x:v>102</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G21" s="14" t="s">
-        <x:v>103</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H21" s="16">
-        <x:v>46134.1206595602</x:v>
+        <x:v>46125.335903912</x:v>
       </x:c>
       <x:c r="I21" s="16">
-        <x:v>46134.1206809375</x:v>
+        <x:v>46203</x:v>
       </x:c>
       <x:c r="J21" s="15" t="s">
-        <x:v>104</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K21" s="17" t="n">
-        <x:v>630</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L21" s="18">
-        <x:v>46139.1576734144</x:v>
+        <x:v>46134.2685065741</x:v>
       </x:c>
       <x:c r="M21" s="14" t="s">
         <x:v>32</x:v>
@@ -3194,35 +3170,37 @@
     </x:row>
     <x:row r="22" spans="1:28" ht="30" customHeight="1">
       <x:c r="B22" s="14" t="s">
-        <x:v>26</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C22" s="14" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D22" s="15" t="s"/>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="E22" s="14" t="s">
-        <x:v>28</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F22" s="14" t="s">
-        <x:v>105</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G22" s="14" t="s">
-        <x:v>106</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H22" s="16">
-        <x:v>46120.3579437153</x:v>
+        <x:v>46128.2089466088</x:v>
       </x:c>
       <x:c r="I22" s="16">
-        <x:v>46120.3579643171</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J22" s="15" t="s">
-        <x:v>107</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="K22" s="17" t="n">
-        <x:v>2790</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L22" s="18">
-        <x:v>46132.2453653241</x:v>
+        <x:v>46134.3002672917</x:v>
       </x:c>
       <x:c r="M22" s="14" t="s">
         <x:v>32</x:v>
@@ -3230,37 +3208,37 @@
     </x:row>
     <x:row r="23" spans="1:28" ht="30" customHeight="1">
       <x:c r="B23" s="14" t="s">
-        <x:v>108</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C23" s="14" t="s">
-        <x:v>109</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D23" s="15" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E23" s="14" t="s">
-        <x:v>110</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F23" s="14" t="s">
-        <x:v>111</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="G23" s="14" t="s">
-        <x:v>112</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H23" s="16">
-        <x:v>46130.477754919</x:v>
+        <x:v>46132.3880687384</x:v>
       </x:c>
       <x:c r="I23" s="16">
-        <x:v>45968</x:v>
+        <x:v>46138</x:v>
       </x:c>
       <x:c r="J23" s="15" t="s">
-        <x:v>113</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="K23" s="17" t="n">
-        <x:v>3780</x:v>
+        <x:v>3030</x:v>
       </x:c>
       <x:c r="L23" s="18">
-        <x:v>46140.1466972338</x:v>
+        <x:v>46135.1691307292</x:v>
       </x:c>
       <x:c r="M23" s="14" t="s">
         <x:v>32</x:v>
@@ -3268,37 +3246,37 @@
     </x:row>
     <x:row r="24" spans="1:28" ht="30" customHeight="1">
       <x:c r="B24" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C24" s="14" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E24" s="14" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F24" s="14" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="G24" s="14" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="C24" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="D24" s="15" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E24" s="14" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F24" s="14" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="G24" s="14" t="s">
-        <x:v>117</x:v>
-      </x:c>
       <x:c r="H24" s="16">
-        <x:v>46105.3461754861</x:v>
+        <x:v>46135.0684019213</x:v>
       </x:c>
       <x:c r="I24" s="16">
-        <x:v>46137</x:v>
+        <x:v>46135</x:v>
       </x:c>
       <x:c r="J24" s="15" t="s">
-        <x:v>118</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="K24" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L24" s="18">
-        <x:v>46120.2790231597</x:v>
+        <x:v>46135.1975182523</x:v>
       </x:c>
       <x:c r="M24" s="14" t="s">
         <x:v>32</x:v>
@@ -3306,37 +3284,35 @@
     </x:row>
     <x:row r="25" spans="1:28" ht="30" customHeight="1">
       <x:c r="B25" s="14" t="s">
-        <x:v>108</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C25" s="14" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="D25" s="15" t="s">
-        <x:v>22</x:v>
-      </x:c>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="s"/>
       <x:c r="E25" s="14" t="s">
-        <x:v>120</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F25" s="14" t="s">
-        <x:v>121</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G25" s="14" t="s">
-        <x:v>122</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="H25" s="16">
-        <x:v>46134.0293580208</x:v>
+        <x:v>46134.1206595602</x:v>
       </x:c>
       <x:c r="I25" s="16">
-        <x:v>46144</x:v>
+        <x:v>46134.1206809375</x:v>
       </x:c>
       <x:c r="J25" s="15" t="s">
-        <x:v>123</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="K25" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="L25" s="18">
-        <x:v>46139.2265670718</x:v>
+        <x:v>46139.1576734144</x:v>
       </x:c>
       <x:c r="M25" s="14" t="s">
         <x:v>32</x:v>
@@ -3344,37 +3320,37 @@
     </x:row>
     <x:row r="26" spans="1:28" ht="30" customHeight="1">
       <x:c r="B26" s="14" t="s">
-        <x:v>108</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C26" s="14" t="s">
-        <x:v>81</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D26" s="15" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E26" s="14" t="s">
-        <x:v>124</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F26" s="14" t="s">
-        <x:v>125</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="G26" s="14" t="s">
-        <x:v>126</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="H26" s="16">
-        <x:v>46126.2721295949</x:v>
+        <x:v>46134.0293580208</x:v>
       </x:c>
       <x:c r="I26" s="16">
-        <x:v>46224</x:v>
+        <x:v>46144</x:v>
       </x:c>
       <x:c r="J26" s="15" t="s">
-        <x:v>127</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="K26" s="17" t="n">
         <x:v>3030</x:v>
       </x:c>
       <x:c r="L26" s="18">
-        <x:v>46128.1955625</x:v>
+        <x:v>46139.2265670718</x:v>
       </x:c>
       <x:c r="M26" s="14" t="s">
         <x:v>32</x:v>
@@ -3382,37 +3358,37 @@
     </x:row>
     <x:row r="27" spans="1:28" ht="30" customHeight="1">
       <x:c r="B27" s="14" t="s">
-        <x:v>108</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C27" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D27" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E27" s="14" t="s">
-        <x:v>129</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F27" s="14" t="s">
-        <x:v>130</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G27" s="14" t="s">
-        <x:v>131</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="H27" s="16">
-        <x:v>46125.335903912</x:v>
+        <x:v>46132.313701713</x:v>
       </x:c>
       <x:c r="I27" s="16">
-        <x:v>46203</x:v>
+        <x:v>46132.3137205208</x:v>
       </x:c>
       <x:c r="J27" s="15" t="s">
-        <x:v>132</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="K27" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3530</x:v>
       </x:c>
       <x:c r="L27" s="18">
-        <x:v>46134.2685065741</x:v>
+        <x:v>46139.230364294</x:v>
       </x:c>
       <x:c r="M27" s="14" t="s">
         <x:v>32</x:v>
@@ -3420,37 +3396,37 @@
     </x:row>
     <x:row r="28" spans="1:28" ht="30" customHeight="1">
       <x:c r="B28" s="14" t="s">
-        <x:v>108</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C28" s="14" t="s">
-        <x:v>133</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D28" s="15" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="E28" s="14" t="s">
-        <x:v>134</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F28" s="14" t="s">
-        <x:v>135</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="G28" s="14" t="s">
-        <x:v>136</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H28" s="16">
-        <x:v>46126.2873086111</x:v>
+        <x:v>46129.4086055787</x:v>
       </x:c>
       <x:c r="I28" s="16">
-        <x:v>46130</x:v>
+        <x:v>46129.4086256481</x:v>
       </x:c>
       <x:c r="J28" s="15" t="s">
-        <x:v>137</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="K28" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>2130</x:v>
       </x:c>
       <x:c r="L28" s="18">
-        <x:v>46127.0949605556</x:v>
+        <x:v>46139.3272522222</x:v>
       </x:c>
       <x:c r="M28" s="14" t="s">
         <x:v>32</x:v>
@@ -3458,37 +3434,37 @@
     </x:row>
     <x:row r="29" spans="1:28" ht="30" customHeight="1">
       <x:c r="B29" s="14" t="s">
-        <x:v>108</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C29" s="14" t="s">
-        <x:v>96</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D29" s="15" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E29" s="14" t="s">
-        <x:v>138</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F29" s="14" t="s">
-        <x:v>139</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="G29" s="14" t="s">
-        <x:v>140</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H29" s="16">
-        <x:v>46126.3215783912</x:v>
+        <x:v>46137.0314533796</x:v>
       </x:c>
       <x:c r="I29" s="16">
-        <x:v>46198</x:v>
+        <x:v>46149</x:v>
       </x:c>
       <x:c r="J29" s="15" t="s">
-        <x:v>141</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="K29" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="L29" s="18">
-        <x:v>46128.1824279398</x:v>
+        <x:v>46139.3366940046</x:v>
       </x:c>
       <x:c r="M29" s="14" t="s">
         <x:v>32</x:v>
@@ -3496,37 +3472,37 @@
     </x:row>
     <x:row r="30" spans="1:28" ht="30" customHeight="1">
       <x:c r="B30" s="14" t="s">
-        <x:v>108</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C30" s="14" t="s">
-        <x:v>96</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D30" s="15" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E30" s="14" t="s">
-        <x:v>97</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F30" s="14" t="s">
-        <x:v>142</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G30" s="14" t="s">
-        <x:v>143</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H30" s="16">
-        <x:v>46126.3072273495</x:v>
+        <x:v>46130.477754919</x:v>
       </x:c>
       <x:c r="I30" s="16">
-        <x:v>46189</x:v>
+        <x:v>45968</x:v>
       </x:c>
       <x:c r="J30" s="15" t="s">
-        <x:v>144</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="K30" s="17" t="n">
-        <x:v>3030</x:v>
+        <x:v>3780</x:v>
       </x:c>
       <x:c r="L30" s="18">
-        <x:v>46128.1930397685</x:v>
+        <x:v>46140.1466972338</x:v>
       </x:c>
       <x:c r="M30" s="14" t="s">
         <x:v>32</x:v>
@@ -3556,7 +3532,7 @@
     </x:row>
     <x:row r="35" spans="1:28" ht="18" customHeight="1">
       <x:c r="B35" s="25" t="s">
-        <x:v>37</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C35" s="26" t="s"/>
       <x:c r="D35" s="26" t="s"/>
@@ -3567,7 +3543,7 @@
     </x:row>
     <x:row r="36" spans="1:28" ht="18" customHeight="1">
       <x:c r="B36" s="25" t="s">
-        <x:v>48</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C36" s="26" t="s"/>
       <x:c r="D36" s="26" t="s"/>
@@ -3578,7 +3554,7 @@
     </x:row>
     <x:row r="37" spans="1:28" ht="18" customHeight="1">
       <x:c r="B37" s="25" t="s">
-        <x:v>101</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C37" s="26" t="s"/>
       <x:c r="D37" s="26" t="s"/>
@@ -3600,7 +3576,7 @@
     </x:row>
     <x:row r="39" spans="1:28" ht="18" customHeight="1">
       <x:c r="B39" s="25" t="s">
-        <x:v>108</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C39" s="26" t="s"/>
       <x:c r="D39" s="26" t="s"/>
